--- a/docs/package/08_Management/BrokerVerse_PH_Fit_and_ASEAN_Rollout_Assessment.xlsx
+++ b/docs/package/08_Management/BrokerVerse_PH_Fit_and_ASEAN_Rollout_Assessment.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method and Sources" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PH Process Fit'!$A$1:$L$179</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PH Process Fit'!$A$1:$L$166</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Gaps Ranked'!$A$1:$L$55</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -299,9 +299,13 @@
           </val>
         </ser>
         <dLbls>
+          <showLegendKey val="0"/>
           <showVal val="1"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
         </dLbls>
-        <gapWidth val="150"/>
+        <gapWidth val="40"/>
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
@@ -403,7 +407,11 @@
           </val>
         </ser>
         <dLbls>
+          <showLegendKey val="0"/>
           <showVal val="1"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
         </dLbls>
         <gapWidth val="150"/>
         <axId val="10"/>
@@ -443,12 +451,12 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>4</col>
+      <col>6</col>
       <colOff>0</colOff>
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6480000" cy="3960000"/>
+    <ext cx="7200000" cy="4680000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -780,10 +788,10 @@
   <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -825,11 +833,11 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.804</v>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>163 L2 processes in 15 L1 areas, weighted 1 to 3</t>
+          <t>150 L2 processes in 15 L1 areas, weighted 1 to 3</t>
         </is>
       </c>
     </row>
@@ -840,11 +848,11 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.7140000000000001</v>
+        <v>0.7070000000000001</v>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>51 regulatory L2 processes</t>
+          <t>49 regulatory L2 processes</t>
         </is>
       </c>
     </row>
@@ -855,11 +863,11 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>0.865</v>
+        <v>0.8540000000000001</v>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>112 operational L2 processes</t>
+          <t>101 operational L2 processes</t>
         </is>
       </c>
     </row>
@@ -870,7 +878,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.8059999999999999</v>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
@@ -885,7 +893,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.795</v>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
@@ -900,7 +908,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>0.853</v>
+        <v>0.8440000000000001</v>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
@@ -915,7 +923,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.6759999999999999</v>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
@@ -930,7 +938,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
@@ -976,7 +984,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>109 / 36 / 18</t>
+          <t>96 / 36 / 18</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr"/>
@@ -1027,11 +1035,11 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>0.679</v>
+        <v>0.654</v>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>8 (4 / 3 / 1)</t>
+          <t>7 (3 / 3 / 1)</t>
         </is>
       </c>
     </row>
@@ -1057,11 +1065,11 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>0.8540000000000001</v>
+        <v>0.848</v>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>11 (8 / 2 / 1)</t>
+          <t>10 (7 / 2 / 1)</t>
         </is>
       </c>
     </row>
@@ -1072,11 +1080,11 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>0.845</v>
+        <v>0.833</v>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>12 (8 / 3 / 1)</t>
+          <t>11 (7 / 3 / 1)</t>
         </is>
       </c>
     </row>
@@ -1102,11 +1110,11 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>0.9229999999999999</v>
+        <v>0.917</v>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>7 (6 / 0 / 1)</t>
+          <t>6 (5 / 0 / 1)</t>
         </is>
       </c>
     </row>
@@ -1117,11 +1125,11 @@
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>0.897</v>
+        <v>0.893</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>13 (11 / 1 / 1)</t>
+          <t>12 (10 / 1 / 1)</t>
         </is>
       </c>
     </row>
@@ -1132,11 +1140,11 @@
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>0.85</v>
+        <v>0.833</v>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>9 (7 / 0 / 2)</t>
+          <t>8 (6 / 0 / 2)</t>
         </is>
       </c>
     </row>
@@ -1147,11 +1155,11 @@
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>0.8859999999999999</v>
+        <v>0.875</v>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>10 (8 / 1 / 1)</t>
+          <t>9 (7 / 1 / 1)</t>
         </is>
       </c>
     </row>
@@ -1162,11 +1170,11 @@
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>0.857</v>
+        <v>0.8420000000000001</v>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>9 (6 / 3 / 0)</t>
+          <t>8 (5 / 3 / 0)</t>
         </is>
       </c>
     </row>
@@ -1177,11 +1185,11 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>0.963</v>
+        <v>0.96</v>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>11 (10 / 1 / 0)</t>
+          <t>10 (9 / 1 / 0)</t>
         </is>
       </c>
     </row>
@@ -1192,11 +1200,11 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>0.758</v>
+        <v>0.742</v>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>14 (7 / 6 / 1)</t>
+          <t>13 (6 / 6 / 1)</t>
         </is>
       </c>
     </row>
@@ -1207,11 +1215,11 @@
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>0.607</v>
+        <v>0.593</v>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>14 (6 / 4 / 4)</t>
+          <t>13 (5 / 4 / 4)</t>
         </is>
       </c>
     </row>
@@ -1222,11 +1230,11 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>0.857</v>
+        <v>0.8390000000000001</v>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>16 (10 / 6 / 0)</t>
+          <t>14 (8 / 6 / 0)</t>
         </is>
       </c>
     </row>
@@ -1318,15 +1326,15 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>27 to 37%</t>
+          <t>28 to 38%</t>
         </is>
       </c>
       <c r="C39" s="7" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>16 to 22</t>
+          <t>17 to 23</t>
         </is>
       </c>
       <c r="E39" s="7" t="n">
@@ -1486,7 +1494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L180"/>
+  <dimension ref="A1:L167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2122,20 +2130,20 @@
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>L1 subtotal: fit 67.9%</t>
+          <t>L1 subtotal: fit 65.4%</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr"/>
       <c r="E13" s="9" t="inlineStr"/>
       <c r="F13" s="10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G13" s="9" t="inlineStr"/>
       <c r="H13" s="10" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I13" s="10" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J13" s="9" t="inlineStr"/>
       <c r="K13" s="9" t="inlineStr"/>
@@ -2154,7 +2162,7 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Lead capture by line (motor, fire, IAR, employee benefits), retail or corporate</t>
+          <t>Lead capture by line (motor, fire, IAR, employee benefits), retail or corporate, with bulk upload</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
@@ -2183,7 +2191,7 @@
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>Sales &amp; Marketing &gt; Prospects (/agent/leadlisting); leads.test.js</t>
+          <t>Sales &amp; Marketing &gt; Prospects (/agent/leadlisting); POST /leads/bulk-upload; leads.test.js</t>
         </is>
       </c>
       <c r="K14" s="6" t="inlineStr"/>
@@ -2192,7 +2200,7 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -2202,7 +2210,7 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Bulk lead upload with row error report</t>
+          <t>Lead status pipeline and conversion funnel</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
@@ -2216,7 +2224,7 @@
         </is>
       </c>
       <c r="F15" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="12" t="n">
         <v>2</v>
@@ -2231,7 +2239,7 @@
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>POST /leads/bulk-upload; leads.test.js</t>
+          <t>Lead statuses New to Converted or Lost; Lead Conversion Funnel report; reports.test.js</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr"/>
@@ -2240,7 +2248,7 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -2250,7 +2258,7 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Lead status pipeline and conversion funnel</t>
+          <t>Sales activities: calls, meetings, follow-up tasks and reminders</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
@@ -2266,8 +2274,8 @@
       <c r="F16" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G16" s="12" t="n">
-        <v>2</v>
+      <c r="G16" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="H16" s="7">
         <f>F16*G16</f>
@@ -2279,16 +2287,24 @@
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>Lead statuses New to Converted or Lost; Lead Conversion Funnel report; reports.test.js</t>
-        </is>
-      </c>
-      <c r="K16" s="6" t="inlineStr"/>
-      <c r="L16" s="7" t="inlineStr"/>
+          <t>No activity log on leads (modules/leads); My Work inbox in development</t>
+        </is>
+      </c>
+      <c r="K16" s="6" t="inlineStr">
+        <is>
+          <t>Account executives cannot log activities or schedule follow-ups on a prospect.</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -2298,7 +2314,7 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Sales activities: calls, meetings, follow-up tasks and reminders</t>
+          <t>Lead assignment to account executives and team visibility</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
@@ -2314,8 +2330,8 @@
       <c r="F17" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G17" s="13" t="n">
-        <v>0</v>
+      <c r="G17" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="H17" s="7">
         <f>F17*G17</f>
@@ -2327,24 +2343,20 @@
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>No activity log on leads (modules/leads); My Work inbox in development</t>
+          <t>Record scope for scoped roles (security.scoped_roles); scope.test.js</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>Account executives cannot log activities or schedule follow-ups on a prospect.</t>
-        </is>
-      </c>
-      <c r="L17" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>Owner scoping exists; no assignment rules, reassignment queue or team view.</t>
+        </is>
+      </c>
+      <c r="L17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -2354,7 +2366,7 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Lead assignment to account executives and team visibility</t>
+          <t>Sales targets and sales dashboard</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
@@ -2370,8 +2382,8 @@
       <c r="F18" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G18" s="11" t="n">
-        <v>1</v>
+      <c r="G18" s="12" t="n">
+        <v>2</v>
       </c>
       <c r="H18" s="7">
         <f>F18*G18</f>
@@ -2383,20 +2395,16 @@
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>Record scope for scoped roles (security.scoped_roles); scope.test.js</t>
-        </is>
-      </c>
-      <c r="K18" s="6" t="inlineStr">
-        <is>
-          <t>Owner scoping exists; no assignment rules, reassignment queue or team view.</t>
-        </is>
-      </c>
+          <t>Dashboard &gt; Sales Dashboard; dashboard.targets; dashboard.test.js</t>
+        </is>
+      </c>
+      <c r="K18" s="6" t="inlineStr"/>
       <c r="L18" s="7" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -2406,12 +2414,12 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Sales targets and sales dashboard</t>
+          <t>Dealer, bank and affinity channel referrals (captive agency, motor dealer branches)</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Agent</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -2422,8 +2430,8 @@
       <c r="F19" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G19" s="12" t="n">
-        <v>2</v>
+      <c r="G19" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="H19" s="7">
         <f>F19*G19</f>
@@ -2435,16 +2443,20 @@
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>Dashboard &gt; Sales Dashboard; dashboard.targets; dashboard.test.js</t>
-        </is>
-      </c>
-      <c r="K19" s="6" t="inlineStr"/>
+          <t>Commission &gt; Agents/Referrer Accounts (types Agent, Sub-agent, External); commission.test.js</t>
+        </is>
+      </c>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>No dealer or dealer-branch master, channel hierarchy or dealer production report.</t>
+        </is>
+      </c>
       <c r="L19" s="7" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -2454,12 +2466,12 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Dealer, bank and affinity channel referrals (captive agency, motor dealer branches)</t>
+          <t>Marketing campaigns to consenting clients</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>Agent</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
@@ -2468,7 +2480,7 @@
         </is>
       </c>
       <c r="F20" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G20" s="11" t="n">
         <v>1</v>
@@ -2483,104 +2495,100 @@
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>Commission &gt; Agents/Referrer Accounts (types Agent, Sub-agent, External); commission.test.js</t>
+          <t>Marketing consent per purpose; Renewals &gt; Lapse Management win-back campaigns</t>
         </is>
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
-          <t>No dealer or dealer-branch master, channel hierarchy or dealer production report.</t>
+          <t>No general campaign or mass mailing module.</t>
         </is>
       </c>
       <c r="L20" s="7" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>2.08</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>Prospecting and sales pipeline</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>Marketing campaigns to consenting clients</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Quotation and insurer comparison</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>L1 subtotal: fit 89.6%</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr"/>
+      <c r="E21" s="9" t="inlineStr"/>
+      <c r="F21" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="G21" s="9" t="inlineStr"/>
+      <c r="H21" s="10" t="n">
+        <v>43</v>
+      </c>
+      <c r="I21" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="J21" s="9" t="inlineStr"/>
+      <c r="K21" s="9" t="inlineStr"/>
+      <c r="L21" s="9" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>3.01</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Quotation and insurer comparison</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Quick quote of packaged products from insurer rate tables</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>Ops</t>
         </is>
       </c>
-      <c r="F21" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" s="7">
-        <f>F21*G21</f>
-        <v/>
-      </c>
-      <c r="I21" s="7">
-        <f>2*F21</f>
-        <v/>
-      </c>
-      <c r="J21" s="6" t="inlineStr">
-        <is>
-          <t>Marketing consent per purpose; Renewals &gt; Lapse Management win-back campaigns</t>
-        </is>
-      </c>
-      <c r="K21" s="6" t="inlineStr">
-        <is>
-          <t>No general campaign or mass mailing module.</t>
-        </is>
-      </c>
-      <c r="L21" s="7" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>Quotation and insurer comparison</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>L1 subtotal: fit 89.6%</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr"/>
-      <c r="E22" s="9" t="inlineStr"/>
-      <c r="F22" s="10" t="n">
-        <v>24</v>
-      </c>
-      <c r="G22" s="9" t="inlineStr"/>
-      <c r="H22" s="10" t="n">
-        <v>43</v>
-      </c>
-      <c r="I22" s="10" t="n">
-        <v>48</v>
-      </c>
-      <c r="J22" s="9" t="inlineStr"/>
-      <c r="K22" s="9" t="inlineStr"/>
-      <c r="L22" s="9" t="inlineStr"/>
+      <c r="F22" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" s="7">
+        <f>F22*G22</f>
+        <v/>
+      </c>
+      <c r="I22" s="7">
+        <f>2*F22</f>
+        <v/>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>Sales &amp; Marketing &gt; Quick Quote; Master &gt; Finance &gt; Insurer Rate Tables; packages.test.js</t>
+        </is>
+      </c>
+      <c r="K22" s="6" t="inlineStr"/>
+      <c r="L22" s="7" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -2590,12 +2598,12 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Quick quote of packaged products from insurer rate tables</t>
+          <t>Side-by-side comparison of insurers on screen</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Broker</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
@@ -2604,7 +2612,7 @@
         </is>
       </c>
       <c r="F23" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G23" s="12" t="n">
         <v>2</v>
@@ -2619,7 +2627,7 @@
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>Sales &amp; Marketing &gt; Quick Quote; Master &gt; Finance &gt; Insurer Rate Tables; packages.test.js</t>
+          <t>Sales &amp; Marketing &gt; Compare Insurers (/sales/compare-insurers); packages.test.js</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr"/>
@@ -2628,7 +2636,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -2638,7 +2646,7 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Side-by-side comparison of insurers on screen</t>
+          <t>Client-facing comparison and recommendation report</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
@@ -2652,10 +2660,10 @@
         </is>
       </c>
       <c r="F24" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G24" s="12" t="n">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="G24" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="H24" s="7">
         <f>F24*G24</f>
@@ -2667,16 +2675,24 @@
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>Sales &amp; Marketing &gt; Compare Insurers (/sales/compare-insurers); packages.test.js</t>
-        </is>
-      </c>
-      <c r="K24" s="6" t="inlineStr"/>
-      <c r="L24" s="7" t="inlineStr"/>
+          <t>Market comparison table on slip PDFs (modules/documents/templates.js)</t>
+        </is>
+      </c>
+      <c r="K24" s="6" t="inlineStr">
+        <is>
+          <t>Printable comparison report for the client is in development.</t>
+        </is>
+      </c>
+      <c r="L24" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -2686,12 +2702,12 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Client-facing comparison and recommendation report</t>
+          <t>Motor quotation: own damage, acts of nature, VTPL BI/PD, APPA, accessories</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Broker</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
@@ -2700,10 +2716,10 @@
         </is>
       </c>
       <c r="F25" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G25" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="G25" s="12" t="n">
+        <v>2</v>
       </c>
       <c r="H25" s="7">
         <f>F25*G25</f>
@@ -2715,24 +2731,16 @@
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>Market comparison table on slip PDFs (modules/documents/templates.js)</t>
-        </is>
-      </c>
-      <c r="K25" s="6" t="inlineStr">
-        <is>
-          <t>Printable comparison report for the client is in development.</t>
-        </is>
-      </c>
-      <c r="L25" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>Sales &amp; Marketing &gt; Quotations (/agent/Quotation); quotations.test.js; motor-tariff.test.js</t>
+        </is>
+      </c>
+      <c r="K25" s="6" t="inlineStr"/>
+      <c r="L25" s="7" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -2742,7 +2750,7 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Motor quotation: own damage, acts of nature, VTPL BI/PD, APPA, accessories</t>
+          <t>Server-side pricing with premium taxes (VAT, DST, LGT, FST)</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
@@ -2752,7 +2760,7 @@
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>BIR</t>
         </is>
       </c>
       <c r="F26" s="7" t="n">
@@ -2771,7 +2779,7 @@
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>Sales &amp; Marketing &gt; Quotations (/agent/Quotation); quotations.test.js; motor-tariff.test.js</t>
+          <t>modules/premium-charges (one calculator); premium-charges.test.js; money-single-source.test.js</t>
         </is>
       </c>
       <c r="K26" s="6" t="inlineStr"/>
@@ -2780,7 +2788,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -2790,7 +2798,7 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Server-side pricing with premium taxes (VAT, DST, LGT, FST)</t>
+          <t>Quotation for non-motor lines from insurer terms</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
@@ -2800,7 +2808,7 @@
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>BIR</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="F27" s="7" t="n">
@@ -2819,7 +2827,7 @@
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>modules/premium-charges (one calculator); premium-charges.test.js; money-single-source.test.js</t>
+          <t>Quotation slip and RFQ offers (placement.journey); request-for-quotation.test.js; UAT corporate phase (fire, IAR, CAR, marine, CGL)</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr"/>
@@ -2828,7 +2836,7 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -2838,7 +2846,7 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Quotation for non-motor lines from insurer terms</t>
+          <t>Discount control taken from broker commission</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
@@ -2852,7 +2860,7 @@
         </is>
       </c>
       <c r="F28" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G28" s="12" t="n">
         <v>2</v>
@@ -2867,7 +2875,7 @@
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>Quotation slip and RFQ offers (placement.journey); request-for-quotation.test.js; UAT corporate phase (fire, IAR, CAR, marine, CGL)</t>
+          <t>Quotation order summary (discount up to 30%); quotations.test.js</t>
         </is>
       </c>
       <c r="K28" s="6" t="inlineStr"/>
@@ -2876,7 +2884,7 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
@@ -2886,7 +2894,7 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Discount control taken from broker commission</t>
+          <t>Online client approval of the quotation</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
@@ -2915,16 +2923,20 @@
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>Quotation order summary (discount up to 30%); quotations.test.js</t>
-        </is>
-      </c>
-      <c r="K29" s="6" t="inlineStr"/>
+          <t>Send for Customer Approval (signed link 168 hours); customer-response.test.js</t>
+        </is>
+      </c>
+      <c r="K29" s="6" t="inlineStr">
+        <is>
+          <t>Approval through the live e-mail link blocked in the test environment (no SMTP); recorded responses tested.</t>
+        </is>
+      </c>
       <c r="L29" s="7" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
@@ -2934,7 +2946,7 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Online client approval of the quotation</t>
+          <t>Quotation validity, expiry and maker-checker</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
@@ -2948,7 +2960,7 @@
         </is>
       </c>
       <c r="F30" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>2</v>
@@ -2963,20 +2975,16 @@
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>Send for Customer Approval (signed link 168 hours); customer-response.test.js</t>
-        </is>
-      </c>
-      <c r="K30" s="6" t="inlineStr">
-        <is>
-          <t>Approval through the live e-mail link blocked in the test environment (no SMTP); recorded responses tested.</t>
-        </is>
-      </c>
+          <t>limits.quote_validity_days; Quotation expiry job; workflow.quote_maker_checker; quotations.test.js</t>
+        </is>
+      </c>
+      <c r="K30" s="6" t="inlineStr"/>
       <c r="L30" s="7" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -2986,7 +2994,7 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Quotation validity, expiry and maker-checker</t>
+          <t>Electronic signature of proposal and acceptance</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
@@ -3002,8 +3010,8 @@
       <c r="F31" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G31" s="12" t="n">
-        <v>2</v>
+      <c r="G31" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="H31" s="7">
         <f>F31*G31</f>
@@ -3015,16 +3023,24 @@
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>limits.quote_validity_days; Quotation expiry job; workflow.quote_maker_checker; quotations.test.js</t>
-        </is>
-      </c>
-      <c r="K31" s="6" t="inlineStr"/>
-      <c r="L31" s="7" t="inlineStr"/>
+          <t>Approval link records acceptance; Signatories master</t>
+        </is>
+      </c>
+      <c r="K31" s="6" t="inlineStr">
+        <is>
+          <t>E-signature on documents is in development.</t>
+        </is>
+      </c>
+      <c r="L31" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
@@ -3034,7 +3050,7 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Electronic signature of proposal and acceptance</t>
+          <t>Product rules from the Product Configurator drive the quotation</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
@@ -3048,7 +3064,7 @@
         </is>
       </c>
       <c r="F32" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G32" s="11" t="n">
         <v>1</v>
@@ -3063,12 +3079,12 @@
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>Approval link records acceptance; Signatories master</t>
+          <t>Product Configurator &gt; Product Templates (MOT-003-2025 CTPL and APPA tariff used); product-configurator.test.js</t>
         </is>
       </c>
       <c r="K32" s="6" t="inlineStr">
         <is>
-          <t>E-signature on documents is in development.</t>
+          <t>Only the motor tariff feeds quotations; coverage, acceptance and document rules are not yet connected (in development).</t>
         </is>
       </c>
       <c r="L32" s="7" t="inlineStr">
@@ -3078,97 +3094,89 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>3.11</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>Quotation and insurer comparison</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>Product rules from the Product Configurator drive the quotation</t>
-        </is>
-      </c>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="E33" s="7" t="inlineStr">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>RFQ, placement, co-insurance and reinsurance</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>L1 subtotal: fit 84.8%</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr"/>
+      <c r="E33" s="9" t="inlineStr"/>
+      <c r="F33" s="10" t="n">
+        <v>23</v>
+      </c>
+      <c r="G33" s="9" t="inlineStr"/>
+      <c r="H33" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="I33" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="J33" s="9" t="inlineStr"/>
+      <c r="K33" s="9" t="inlineStr"/>
+      <c r="L33" s="9" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>4.01</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>RFQ, placement, co-insurance and reinsurance</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>Request for Quotation (broker slip) to several insurers by e-mail</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>Broker</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
         <is>
           <t>Ops</t>
         </is>
       </c>
-      <c r="F33" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G33" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H33" s="7">
-        <f>F33*G33</f>
-        <v/>
-      </c>
-      <c r="I33" s="7">
-        <f>2*F33</f>
-        <v/>
-      </c>
-      <c r="J33" s="6" t="inlineStr">
-        <is>
-          <t>Product Configurator &gt; Product Templates (MOT-003-2025 CTPL and APPA tariff used); product-configurator.test.js</t>
-        </is>
-      </c>
-      <c r="K33" s="6" t="inlineStr">
-        <is>
-          <t>Only the motor tariff feeds quotations; coverage, acceptance and document rules are not yet connected (in development).</t>
-        </is>
-      </c>
-      <c r="L33" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>RFQ, placement, co-insurance and reinsurance</t>
-        </is>
-      </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>L1 subtotal: fit 85.4%</t>
-        </is>
-      </c>
-      <c r="D34" s="9" t="inlineStr"/>
-      <c r="E34" s="9" t="inlineStr"/>
-      <c r="F34" s="10" t="n">
-        <v>24</v>
-      </c>
-      <c r="G34" s="9" t="inlineStr"/>
-      <c r="H34" s="10" t="n">
-        <v>41</v>
-      </c>
-      <c r="I34" s="10" t="n">
-        <v>48</v>
-      </c>
-      <c r="J34" s="9" t="inlineStr"/>
-      <c r="K34" s="9" t="inlineStr"/>
-      <c r="L34" s="9" t="inlineStr"/>
+      <c r="F34" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G34" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H34" s="7">
+        <f>F34*G34</f>
+        <v/>
+      </c>
+      <c r="I34" s="7">
+        <f>2*F34</f>
+        <v/>
+      </c>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>Sales &amp; Marketing &gt; Request for Quotation (/placement/broker-slips); request-for-quotation.test.js</t>
+        </is>
+      </c>
+      <c r="K34" s="6" t="inlineStr"/>
+      <c r="L34" s="7" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
@@ -3178,7 +3186,7 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Request for Quotation (broker slip) to several insurers by e-mail</t>
+          <t>Record insurer offers and declines with terms</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
@@ -3207,7 +3215,7 @@
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>Sales &amp; Marketing &gt; Request for Quotation (/placement/broker-slips); request-for-quotation.test.js</t>
+          <t>Broker slip offers (Offered, Declined, Pending); request-for-quotation.test.js</t>
         </is>
       </c>
       <c r="K35" s="6" t="inlineStr"/>
@@ -3216,7 +3224,7 @@
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
@@ -3226,7 +3234,7 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Record insurer offers and declines with terms</t>
+          <t>Compare offers, best offer, market capacity and hit ratio per insurer</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
@@ -3255,7 +3263,7 @@
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
-          <t>Broker slip offers (Offered, Declined, Pending); request-for-quotation.test.js</t>
+          <t>Request for Quotation &gt; Compare offers; Market Response and Placement Pipeline reports; request-for-quotation.test.js; reports.test.js</t>
         </is>
       </c>
       <c r="K36" s="6" t="inlineStr"/>
@@ -3264,7 +3272,7 @@
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
@@ -3274,7 +3282,7 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Compare offers, best offer and market capacity</t>
+          <t>Placement slip to lead and co-insurers with confirmation per insurer</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
@@ -3303,7 +3311,7 @@
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>Request for Quotation &gt; Compare offers; request-for-quotation.test.js</t>
+          <t>Sales &amp; Marketing &gt; Placement Slips (/placement/placement-slips); placement.test.js</t>
         </is>
       </c>
       <c r="K37" s="6" t="inlineStr"/>
@@ -3312,7 +3320,7 @@
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
@@ -3322,7 +3330,7 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Placement slip to lead and co-insurers with confirmation per insurer</t>
+          <t>Co-insurance shares, payables and taxes split per participant</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
@@ -3351,7 +3359,7 @@
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>Sales &amp; Marketing &gt; Placement Slips (/placement/placement-slips); placement.test.js</t>
+          <t>Co-insurance Register; Due to Insurers by Co-insurer; placement.test.js; remittance.test.js</t>
         </is>
       </c>
       <c r="K38" s="6" t="inlineStr"/>
@@ -3360,7 +3368,7 @@
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
@@ -3370,7 +3378,7 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Co-insurance shares, payables and taxes split per participant</t>
+          <t>Placement journey rules per line of business</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
@@ -3384,7 +3392,7 @@
         </is>
       </c>
       <c r="F39" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G39" s="12" t="n">
         <v>2</v>
@@ -3399,7 +3407,7 @@
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>Co-insurance Register; Due to Insurers by Co-insurer; placement.test.js; remittance.test.js</t>
+          <t>placement.journey (Master &gt; Configuration); modules/placement/journey.js; placement.test.js</t>
         </is>
       </c>
       <c r="K39" s="6" t="inlineStr"/>
@@ -3408,7 +3416,7 @@
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
@@ -3418,12 +3426,12 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Placement journey rules per line of business</t>
+          <t>Cover note or binder while the policy is pending</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>Broker</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
@@ -3434,8 +3442,8 @@
       <c r="F40" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G40" s="12" t="n">
-        <v>2</v>
+      <c r="G40" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="H40" s="7">
         <f>F40*G40</f>
@@ -3447,16 +3455,20 @@
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
-          <t>placement.journey (Master &gt; Configuration); modules/placement/journey.js; placement.test.js</t>
-        </is>
-      </c>
-      <c r="K40" s="6" t="inlineStr"/>
+          <t>None found (grep cover note / binder returns nothing)</t>
+        </is>
+      </c>
+      <c r="K40" s="6" t="inlineStr">
+        <is>
+          <t>No cover note document or temporary cover record.</t>
+        </is>
+      </c>
       <c r="L40" s="7" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
@@ -3466,7 +3478,7 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>Cover note or binder while the policy is pending</t>
+          <t>Placement only with insurers authorised by the IC</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
@@ -3476,14 +3488,14 @@
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>IC</t>
         </is>
       </c>
       <c r="F41" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G41" s="13" t="n">
-        <v>0</v>
+      <c r="G41" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="H41" s="7">
         <f>F41*G41</f>
@@ -3495,20 +3507,24 @@
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>None found (grep cover note / binder returns nothing)</t>
+          <t>Master &gt; Generals &gt; Insurance Management &gt; Insurance Company</t>
         </is>
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>No cover note document or temporary cover record.</t>
-        </is>
-      </c>
-      <c r="L41" s="7" t="inlineStr"/>
+          <t>No certificate of authority number or expiry check; IC non-life insurer list is in development.</t>
+        </is>
+      </c>
+      <c r="L41" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
@@ -3518,21 +3534,21 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>Placement only with insurers authorised by the IC</t>
+          <t>Facultative reinsurance placement (where the broker acts as reinsurance broker)</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Broker</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="F42" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G42" s="11" t="n">
         <v>1</v>
@@ -3547,24 +3563,20 @@
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
-          <t>Master &gt; Generals &gt; Insurance Management &gt; Insurance Company</t>
+          <t>Reinsurance &gt; Treaty Dashboard, Cession Tracking; reinsurance.test.js</t>
         </is>
       </c>
       <c r="K42" s="6" t="inlineStr">
         <is>
-          <t>No certificate of authority number or expiry check; IC non-life insurer list is in development.</t>
-        </is>
-      </c>
-      <c r="L42" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>The module records treaties and cessions from the cedant side; there is no facultative reinsurance slip workflow.</t>
+        </is>
+      </c>
+      <c r="L42" s="7" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
@@ -3574,7 +3586,7 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>Market response analytics (hit ratio per insurer)</t>
+          <t>Reinsurance recoveries and reinsurer statement reconciliation</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
@@ -3603,83 +3615,63 @@
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>Market Response and Placement Pipeline reports; reports.test.js</t>
+          <t>Reinsurance &gt; Claims Recovery, Reconciliation; reinsurance.test.js</t>
         </is>
       </c>
       <c r="K43" s="6" t="inlineStr"/>
       <c r="L43" s="7" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
-        <is>
-          <t>RFQ, placement, co-insurance and reinsurance</t>
-        </is>
-      </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>Facultative reinsurance placement (where the broker acts as reinsurance broker)</t>
-        </is>
-      </c>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>Broker</t>
-        </is>
-      </c>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
-          <t>Ops</t>
-        </is>
-      </c>
-      <c r="F44" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44" s="7">
-        <f>F44*G44</f>
-        <v/>
-      </c>
-      <c r="I44" s="7">
-        <f>2*F44</f>
-        <v/>
-      </c>
-      <c r="J44" s="6" t="inlineStr">
-        <is>
-          <t>Reinsurance &gt; Treaty Dashboard, Cession Tracking; reinsurance.test.js</t>
-        </is>
-      </c>
-      <c r="K44" s="6" t="inlineStr">
-        <is>
-          <t>The module records treaties and cessions from the cedant side; there is no facultative reinsurance slip workflow.</t>
-        </is>
-      </c>
-      <c r="L44" s="7" t="inlineStr"/>
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>Policy issuance, documents and motor (CTPL, LTO)</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>L1 subtotal: fit 83.3%</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr"/>
+      <c r="E44" s="9" t="inlineStr"/>
+      <c r="F44" s="10" t="n">
+        <v>27</v>
+      </c>
+      <c r="G44" s="9" t="inlineStr"/>
+      <c r="H44" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="I44" s="10" t="n">
+        <v>54</v>
+      </c>
+      <c r="J44" s="9" t="inlineStr"/>
+      <c r="K44" s="9" t="inlineStr"/>
+      <c r="L44" s="9" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>RFQ, placement, co-insurance and reinsurance</t>
+          <t>Policy issuance, documents and motor (CTPL, LTO)</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Reinsurance recoveries and reinsurer statement reconciliation</t>
+          <t>Issue policy from bound placement or accepted quotation, create client, bill premium; policy statuses</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Broker</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
@@ -3688,7 +3680,7 @@
         </is>
       </c>
       <c r="F45" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G45" s="12" t="n">
         <v>2</v>
@@ -3703,48 +3695,64 @@
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>Reinsurance &gt; Claims Recovery, Reconciliation; reinsurance.test.js</t>
+          <t>Operations &gt; Policy; quote-to-policy.test.js; policies.test.js; UAT scenario 371 steps passed</t>
         </is>
       </c>
       <c r="K45" s="6" t="inlineStr"/>
       <c r="L45" s="7" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B46" s="9" t="inlineStr">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>5.02</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
         <is>
           <t>Policy issuance, documents and motor (CTPL, LTO)</t>
         </is>
       </c>
-      <c r="C46" s="9" t="inlineStr">
-        <is>
-          <t>L1 subtotal: fit 84.5%</t>
-        </is>
-      </c>
-      <c r="D46" s="9" t="inlineStr"/>
-      <c r="E46" s="9" t="inlineStr"/>
-      <c r="F46" s="10" t="n">
-        <v>29</v>
-      </c>
-      <c r="G46" s="9" t="inlineStr"/>
-      <c r="H46" s="10" t="n">
-        <v>49</v>
-      </c>
-      <c r="I46" s="10" t="n">
-        <v>58</v>
-      </c>
-      <c r="J46" s="9" t="inlineStr"/>
-      <c r="K46" s="9" t="inlineStr"/>
-      <c r="L46" s="9" t="inlineStr"/>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>Record a policy already issued by the insurer</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G46" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H46" s="7">
+        <f>F46*G46</f>
+        <v/>
+      </c>
+      <c r="I46" s="7">
+        <f>2*F46</f>
+        <v/>
+      </c>
+      <c r="J46" s="6" t="inlineStr">
+        <is>
+          <t>Placement Slips &gt; Record Issued Policy; placement.test.js</t>
+        </is>
+      </c>
+      <c r="K46" s="6" t="inlineStr"/>
+      <c r="L46" s="7" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
@@ -3754,7 +3762,7 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Issue policy from bound placement or accepted quotation, create client, bill premium</t>
+          <t>Policy schedule and documents generated and e-mailed to the client</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
@@ -3783,7 +3791,7 @@
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>Operations &gt; Policy; quote-to-policy.test.js; policies.test.js; UAT scenario 371 steps passed</t>
+          <t>Policy issued e-mail with schedule PDF; printing.test.js; email-documents.test.js</t>
         </is>
       </c>
       <c r="K47" s="6" t="inlineStr"/>
@@ -3792,7 +3800,7 @@
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
@@ -3802,7 +3810,7 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>Record a policy already issued by the insurer</t>
+          <t>Upload of the insurer policy document and attachments</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
@@ -3816,7 +3824,7 @@
         </is>
       </c>
       <c r="F48" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G48" s="12" t="n">
         <v>2</v>
@@ -3831,7 +3839,7 @@
       </c>
       <c r="J48" s="6" t="inlineStr">
         <is>
-          <t>Placement Slips &gt; Record Issued Policy; placement.test.js</t>
+          <t>Policy details &gt; documents (PDF or image, 10 MB); policies.test.js</t>
         </is>
       </c>
       <c r="K48" s="6" t="inlineStr"/>
@@ -3840,7 +3848,7 @@
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
@@ -3850,7 +3858,7 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Policy schedule and documents generated and e-mailed to the client</t>
+          <t>Motor details: chassis, motor, plate or MV file number, mortgagee, photos</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
@@ -3879,7 +3887,7 @@
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>Policy issued e-mail with schedule PDF; printing.test.js; email-documents.test.js</t>
+          <t>Motor policy issue (policy.kyc_required_fields); policies.test.js</t>
         </is>
       </c>
       <c r="K49" s="6" t="inlineStr"/>
@@ -3888,7 +3896,7 @@
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
@@ -3898,7 +3906,7 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>Upload of the insurer policy document and attachments</t>
+          <t>CTPL tariff per vehicle class, 1-year and 3-year, never discounted</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
@@ -3908,11 +3916,11 @@
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>IC</t>
         </is>
       </c>
       <c r="F50" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G50" s="12" t="n">
         <v>2</v>
@@ -3927,7 +3935,7 @@
       </c>
       <c r="J50" s="6" t="inlineStr">
         <is>
-          <t>Policy details &gt; documents (PDF or image, 10 MB); policies.test.js</t>
+          <t>Product Configurator MOT-003-2025 CTPL &amp; Auto PA tab; motor-tariff.test.js</t>
         </is>
       </c>
       <c r="K50" s="6" t="inlineStr"/>
@@ -3936,7 +3944,7 @@
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>5.07</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
@@ -3946,7 +3954,7 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>Motor details: chassis, motor, plate or MV file number, mortgagee, photos</t>
+          <t>CTPL certificate of cover authentication with the IC-accredited system and LTO</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
@@ -3956,14 +3964,14 @@
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>IC</t>
         </is>
       </c>
       <c r="F51" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G51" s="12" t="n">
-        <v>2</v>
+      <c r="G51" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="H51" s="7">
         <f>F51*G51</f>
@@ -3975,16 +3983,20 @@
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
-          <t>Motor policy issue (policy.kyc_required_fields); policies.test.js</t>
-        </is>
-      </c>
-      <c r="K51" s="6" t="inlineStr"/>
+          <t>Policy fields Cert Number and Authen Code (recorded by hand)</t>
+        </is>
+      </c>
+      <c r="K51" s="6" t="inlineStr">
+        <is>
+          <t>No integration with the authentication provider or LTO; done in the insurer or government portal.</t>
+        </is>
+      </c>
       <c r="L51" s="7" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
@@ -3994,24 +4006,24 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>CTPL tariff per vehicle class, 1-year and 3-year, never discounted</t>
+          <t>Brand-new vehicle programme: dealer sale, financing bank mortgagee clause, free first-year cover</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Agent</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="F52" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G52" s="12" t="n">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="G52" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="H52" s="7">
         <f>F52*G52</f>
@@ -4023,16 +4035,20 @@
       </c>
       <c r="J52" s="6" t="inlineStr">
         <is>
-          <t>Product Configurator MOT-003-2025 CTPL &amp; Auto PA tab; motor-tariff.test.js</t>
-        </is>
-      </c>
-      <c r="K52" s="6" t="inlineStr"/>
+          <t>Mortgagee field on motor policy; 3-year CTPL for brand-new vehicles</t>
+        </is>
+      </c>
+      <c r="K52" s="6" t="inlineStr">
+        <is>
+          <t>No dealer or financing-bank programme set-up, bulk dealer upload or bank endorsement letters.</t>
+        </is>
+      </c>
       <c r="L52" s="7" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.09</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
@@ -4042,7 +4058,7 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>CTPL certificate of cover authentication with the IC-accredited system and LTO</t>
+          <t>Bulk issuance: fleet schedules and group policies</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
@@ -4052,11 +4068,11 @@
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="F53" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G53" s="11" t="n">
         <v>1</v>
@@ -4071,12 +4087,12 @@
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>Policy fields Cert Number and Authen Code (recorded by hand)</t>
+          <t>Policy bulk upload for new business and in-force book; upload-templates.test.js</t>
         </is>
       </c>
       <c r="K53" s="6" t="inlineStr">
         <is>
-          <t>No integration with the authentication provider or LTO; done in the insurer or government portal.</t>
+          <t>No fleet schedule with per-vehicle premium inside one policy.</t>
         </is>
       </c>
       <c r="L53" s="7" t="inlineStr"/>
@@ -4084,7 +4100,7 @@
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
@@ -4094,12 +4110,12 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>Brand-new vehicle programme: dealer sale, financing bank mortgagee clause, free first-year cover</t>
+          <t>Lines placed: motor, fire, IAR, CAR, EAR, marine, CGL, money, PA, travel, EB, surety</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>Agent</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
@@ -4110,8 +4126,8 @@
       <c r="F54" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G54" s="11" t="n">
-        <v>1</v>
+      <c r="G54" s="12" t="n">
+        <v>2</v>
       </c>
       <c r="H54" s="7">
         <f>F54*G54</f>
@@ -4123,20 +4139,16 @@
       </c>
       <c r="J54" s="6" t="inlineStr">
         <is>
-          <t>Mortgagee field on motor policy; 3-year CTPL for brand-new vehicles</t>
-        </is>
-      </c>
-      <c r="K54" s="6" t="inlineStr">
-        <is>
-          <t>No dealer or financing-bank programme set-up, bulk dealer upload or bank endorsement letters.</t>
-        </is>
-      </c>
+          <t>UAT data set issued 62 new policies across these lines (test-summary.md, UAT data set)</t>
+        </is>
+      </c>
+      <c r="K54" s="6" t="inlineStr"/>
       <c r="L54" s="7" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>5.09</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
@@ -4146,12 +4158,12 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>Bulk issuance: fleet schedules and group policies</t>
+          <t>Marine open cover with certificates and declarations</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Broker</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
@@ -4160,10 +4172,10 @@
         </is>
       </c>
       <c r="F55" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G55" s="11" t="n">
         <v>1</v>
+      </c>
+      <c r="G55" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="H55" s="7">
         <f>F55*G55</f>
@@ -4175,78 +4187,62 @@
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
-          <t>Policy bulk upload for new business and in-force book; upload-templates.test.js</t>
+          <t>None found</t>
         </is>
       </c>
       <c r="K55" s="6" t="inlineStr">
         <is>
-          <t>No fleet schedule with per-vehicle premium inside one policy.</t>
+          <t>No open cover or declaration processing.</t>
         </is>
       </c>
       <c r="L55" s="7" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="7" t="inlineStr">
-        <is>
-          <t>5.10</t>
-        </is>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t>Policy issuance, documents and motor (CTPL, LTO)</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>Policy life cycle statuses and payment statuses</t>
-        </is>
-      </c>
-      <c r="D56" s="7" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="E56" s="7" t="inlineStr">
-        <is>
-          <t>Ops</t>
-        </is>
-      </c>
-      <c r="F56" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G56" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="H56" s="7">
-        <f>F56*G56</f>
-        <v/>
-      </c>
-      <c r="I56" s="7">
-        <f>2*F56</f>
-        <v/>
-      </c>
-      <c r="J56" s="6" t="inlineStr">
-        <is>
-          <t>Policy statuses Active, Expired, Renewed, Lapsed, Cancelled; policies.test.js</t>
-        </is>
-      </c>
-      <c r="K56" s="6" t="inlineStr"/>
-      <c r="L56" s="7" t="inlineStr"/>
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>Endorsements and cancellations</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>L1 subtotal: fit 81.6%</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="inlineStr"/>
+      <c r="E56" s="9" t="inlineStr"/>
+      <c r="F56" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="G56" s="9" t="inlineStr"/>
+      <c r="H56" s="10" t="n">
+        <v>31</v>
+      </c>
+      <c r="I56" s="10" t="n">
+        <v>38</v>
+      </c>
+      <c r="J56" s="9" t="inlineStr"/>
+      <c r="K56" s="9" t="inlineStr"/>
+      <c r="L56" s="9" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>Policy issuance, documents and motor (CTPL, LTO)</t>
+          <t>Endorsements and cancellations</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>Lines placed: motor, fire, IAR, CAR, EAR, marine, CGL, money, PA, travel, EB, surety</t>
+          <t>Motor endorsements: personal details, motor details, coverage change, extension</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
@@ -4260,7 +4256,7 @@
         </is>
       </c>
       <c r="F57" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G57" s="12" t="n">
         <v>2</v>
@@ -4275,7 +4271,7 @@
       </c>
       <c r="J57" s="6" t="inlineStr">
         <is>
-          <t>UAT data set issued 62 new policies across these lines (test-summary.md, UAT data set)</t>
+          <t>Operations &gt; Policy &gt; Endorsement; endorsements.test.js</t>
         </is>
       </c>
       <c r="K57" s="6" t="inlineStr"/>
@@ -4284,22 +4280,22 @@
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>Policy issuance, documents and motor (CTPL, LTO)</t>
+          <t>Endorsements and cancellations</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>Marine open cover with certificates and declarations</t>
+          <t>Non-motor endorsements: premium change</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>Broker</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
@@ -4308,10 +4304,10 @@
         </is>
       </c>
       <c r="F58" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G58" s="13" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="G58" s="12" t="n">
+        <v>2</v>
       </c>
       <c r="H58" s="7">
         <f>F58*G58</f>
@@ -4323,52 +4319,64 @@
       </c>
       <c r="J58" s="6" t="inlineStr">
         <is>
-          <t>None found</t>
-        </is>
-      </c>
-      <c r="K58" s="6" t="inlineStr">
-        <is>
-          <t>No open cover or declaration processing.</t>
-        </is>
-      </c>
+          <t>Fire and allied perils Regular / Premium Change; endorsements.test.js</t>
+        </is>
+      </c>
+      <c r="K58" s="6" t="inlineStr"/>
       <c r="L58" s="7" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B59" s="9" t="inlineStr">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>6.03</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
         <is>
           <t>Endorsements and cancellations</t>
         </is>
       </c>
-      <c r="C59" s="9" t="inlineStr">
-        <is>
-          <t>L1 subtotal: fit 81.6%</t>
-        </is>
-      </c>
-      <c r="D59" s="9" t="inlineStr"/>
-      <c r="E59" s="9" t="inlineStr"/>
-      <c r="F59" s="10" t="n">
-        <v>19</v>
-      </c>
-      <c r="G59" s="9" t="inlineStr"/>
-      <c r="H59" s="10" t="n">
-        <v>31</v>
-      </c>
-      <c r="I59" s="10" t="n">
-        <v>38</v>
-      </c>
-      <c r="J59" s="9" t="inlineStr"/>
-      <c r="K59" s="9" t="inlineStr"/>
-      <c r="L59" s="9" t="inlineStr"/>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>Re-pricing of coverage change with taxes on the server</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G59" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H59" s="7">
+        <f>F59*G59</f>
+        <v/>
+      </c>
+      <c r="I59" s="7">
+        <f>2*F59</f>
+        <v/>
+      </c>
+      <c r="J59" s="6" t="inlineStr">
+        <is>
+          <t>endorsements.test.js (premium delta priced on the server; refuses a mismatched delta)</t>
+        </is>
+      </c>
+      <c r="K59" s="6" t="inlineStr"/>
+      <c r="L59" s="7" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
@@ -4378,7 +4386,7 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>Motor endorsements: personal details, motor details, coverage change, extension</t>
+          <t>Cancellation full, partial or pro-rata with return premium computed</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
@@ -4394,8 +4402,8 @@
       <c r="F60" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G60" s="12" t="n">
-        <v>2</v>
+      <c r="G60" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="H60" s="7">
         <f>F60*G60</f>
@@ -4407,16 +4415,20 @@
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
-          <t>Operations &gt; Policy &gt; Endorsement; endorsements.test.js</t>
-        </is>
-      </c>
-      <c r="K60" s="6" t="inlineStr"/>
+          <t>Cancellation endorsement (cancellationType); endorsements.test.js; package sections pro rata (packages.endorsement_prorata)</t>
+        </is>
+      </c>
+      <c r="K60" s="6" t="inlineStr">
+        <is>
+          <t>For regular policies the return premium of a cancellation is entered by the user, not computed from days left.</t>
+        </is>
+      </c>
       <c r="L60" s="7" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>6.05</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
@@ -4426,7 +4438,7 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>Non-motor endorsements: premium change</t>
+          <t>Short-period rate scale when the insured cancels</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
@@ -4442,8 +4454,8 @@
       <c r="F61" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G61" s="12" t="n">
-        <v>2</v>
+      <c r="G61" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="H61" s="7">
         <f>F61*G61</f>
@@ -4455,16 +4467,20 @@
       </c>
       <c r="J61" s="6" t="inlineStr">
         <is>
-          <t>Fire and allied perils Regular / Premium Change; endorsements.test.js</t>
-        </is>
-      </c>
-      <c r="K61" s="6" t="inlineStr"/>
+          <t>None found (grep short period returns nothing)</t>
+        </is>
+      </c>
+      <c r="K61" s="6" t="inlineStr">
+        <is>
+          <t>No short-period table or computation.</t>
+        </is>
+      </c>
       <c r="L61" s="7" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
@@ -4474,7 +4490,7 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>Re-pricing of coverage change with taxes on the server</t>
+          <t>Return premium: refund to client, netting on insurer remittance, commission clawback</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
@@ -4488,7 +4504,7 @@
         </is>
       </c>
       <c r="F62" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G62" s="12" t="n">
         <v>2</v>
@@ -4503,7 +4519,7 @@
       </c>
       <c r="J62" s="6" t="inlineStr">
         <is>
-          <t>endorsements.test.js (premium delta priced on the server; refuses a mismatched delta)</t>
+          <t>endorsements.test.js; remittance.test.js; commission.test.js (clawback)</t>
         </is>
       </c>
       <c r="K62" s="6" t="inlineStr"/>
@@ -4512,7 +4528,7 @@
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
@@ -4522,7 +4538,7 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>Cancellation full, partial or pro-rata with return premium computed</t>
+          <t>Completion with insurer endorsement document and client notice</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
@@ -4536,10 +4552,10 @@
         </is>
       </c>
       <c r="F63" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G63" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="G63" s="12" t="n">
+        <v>2</v>
       </c>
       <c r="H63" s="7">
         <f>F63*G63</f>
@@ -4551,20 +4567,16 @@
       </c>
       <c r="J63" s="6" t="inlineStr">
         <is>
-          <t>Cancellation endorsement (cancellationType); endorsements.test.js; package sections pro rata (packages.endorsement_prorata)</t>
-        </is>
-      </c>
-      <c r="K63" s="6" t="inlineStr">
-        <is>
-          <t>For regular policies the return premium of a cancellation is entered by the user, not computed from days left.</t>
-        </is>
-      </c>
+          <t>Endorsement completion upload; e-mail on completion; endorsements.test.js</t>
+        </is>
+      </c>
+      <c r="K63" s="6" t="inlineStr"/>
       <c r="L63" s="7" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>6.08</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
@@ -4574,7 +4586,7 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>Short-period rate scale when the insured cancels</t>
+          <t>Cancellation for non-payment from the premium warranty monitor</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
@@ -4584,14 +4596,14 @@
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>IC</t>
         </is>
       </c>
       <c r="F64" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G64" s="13" t="n">
-        <v>0</v>
+      <c r="G64" s="12" t="n">
+        <v>2</v>
       </c>
       <c r="H64" s="7">
         <f>F64*G64</f>
@@ -4603,78 +4615,58 @@
       </c>
       <c r="J64" s="6" t="inlineStr">
         <is>
-          <t>None found (grep short period returns nothing)</t>
-        </is>
-      </c>
-      <c r="K64" s="6" t="inlineStr">
-        <is>
-          <t>No short-period table or computation.</t>
-        </is>
-      </c>
+          <t>Accounts &gt; Credit Control &gt; Premium Warranty Monitor (draft cancellation endorsement); credit-control.test.js</t>
+        </is>
+      </c>
+      <c r="K64" s="6" t="inlineStr"/>
       <c r="L64" s="7" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="7" t="inlineStr">
-        <is>
-          <t>6.06</t>
-        </is>
-      </c>
-      <c r="B65" s="6" t="inlineStr">
-        <is>
-          <t>Endorsements and cancellations</t>
-        </is>
-      </c>
-      <c r="C65" s="6" t="inlineStr">
-        <is>
-          <t>Return premium: refund to client, netting on insurer remittance, commission clawback</t>
-        </is>
-      </c>
-      <c r="D65" s="7" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="E65" s="7" t="inlineStr">
-        <is>
-          <t>Ops</t>
-        </is>
-      </c>
-      <c r="F65" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G65" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="H65" s="7">
-        <f>F65*G65</f>
-        <v/>
-      </c>
-      <c r="I65" s="7">
-        <f>2*F65</f>
-        <v/>
-      </c>
-      <c r="J65" s="6" t="inlineStr">
-        <is>
-          <t>endorsements.test.js; remittance.test.js; commission.test.js (clawback)</t>
-        </is>
-      </c>
-      <c r="K65" s="6" t="inlineStr"/>
-      <c r="L65" s="7" t="inlineStr"/>
+      <c r="A65" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B65" s="9" t="inlineStr">
+        <is>
+          <t>Renewals and retention</t>
+        </is>
+      </c>
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>L1 subtotal: fit 91.7%</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="inlineStr"/>
+      <c r="E65" s="9" t="inlineStr"/>
+      <c r="F65" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="G65" s="9" t="inlineStr"/>
+      <c r="H65" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="I65" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="J65" s="9" t="inlineStr"/>
+      <c r="K65" s="9" t="inlineStr"/>
+      <c r="L65" s="9" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>Endorsements and cancellations</t>
+          <t>Renewals and retention</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>Completion with insurer endorsement document and client notice</t>
+          <t>Renewal pipeline 90 days before expiry, notices at 60, 30 and 15 days</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
@@ -4688,7 +4680,7 @@
         </is>
       </c>
       <c r="F66" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G66" s="12" t="n">
         <v>2</v>
@@ -4703,7 +4695,7 @@
       </c>
       <c r="J66" s="6" t="inlineStr">
         <is>
-          <t>Endorsement completion upload; e-mail on completion; endorsements.test.js</t>
+          <t>Renewals &gt; Renewal Queue; renewals.pipeline_days; renewals.test.js</t>
         </is>
       </c>
       <c r="K66" s="6" t="inlineStr"/>
@@ -4712,17 +4704,17 @@
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>6.08</t>
+          <t>7.02</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>Endorsements and cancellations</t>
+          <t>Renewals and retention</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>Cancellation for non-payment from the premium warranty monitor</t>
+          <t>Renewal re-rating, negotiation with the insurer and renewal quotation</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
@@ -4732,11 +4724,11 @@
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="F67" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G67" s="12" t="n">
         <v>2</v>
@@ -4751,48 +4743,64 @@
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
-          <t>Accounts &gt; Credit Control &gt; Premium Warranty Monitor (draft cancellation endorsement); credit-control.test.js</t>
+          <t>Renewals &gt; Negotiations; renewals.test.js; money-single-source.test.js</t>
         </is>
       </c>
       <c r="K67" s="6" t="inlineStr"/>
       <c r="L67" s="7" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B68" s="9" t="inlineStr">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t>7.03</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
         <is>
           <t>Renewals and retention</t>
         </is>
       </c>
-      <c r="C68" s="9" t="inlineStr">
-        <is>
-          <t>L1 subtotal: fit 92.3%</t>
-        </is>
-      </c>
-      <c r="D68" s="9" t="inlineStr"/>
-      <c r="E68" s="9" t="inlineStr"/>
-      <c r="F68" s="10" t="n">
-        <v>13</v>
-      </c>
-      <c r="G68" s="9" t="inlineStr"/>
-      <c r="H68" s="10" t="n">
-        <v>24</v>
-      </c>
-      <c r="I68" s="10" t="n">
-        <v>26</v>
-      </c>
-      <c r="J68" s="9" t="inlineStr"/>
-      <c r="K68" s="9" t="inlineStr"/>
-      <c r="L68" s="9" t="inlineStr"/>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>Renewal batch (up to 500 policies)</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G68" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H68" s="7">
+        <f>F68*G68</f>
+        <v/>
+      </c>
+      <c r="I68" s="7">
+        <f>2*F68</f>
+        <v/>
+      </c>
+      <c r="J68" s="6" t="inlineStr">
+        <is>
+          <t>Renewals &gt; Renewal Batch; renewals.test.js</t>
+        </is>
+      </c>
+      <c r="K68" s="6" t="inlineStr"/>
+      <c r="L68" s="7" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>7.04</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
@@ -4802,7 +4810,7 @@
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>Renewal pipeline 90 days before expiry, notices at 60, 30 and 15 days</t>
+          <t>At-risk scoring, retention analytics, lapse management and win-back</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
@@ -4816,7 +4824,7 @@
         </is>
       </c>
       <c r="F69" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G69" s="12" t="n">
         <v>2</v>
@@ -4831,7 +4839,7 @@
       </c>
       <c r="J69" s="6" t="inlineStr">
         <is>
-          <t>Renewals &gt; Renewal Queue; renewals.pipeline_days; renewals.test.js</t>
+          <t>Renewals &gt; At-Risk Policies, Retention Analytics, Lapse Management, Performance; renewals.grace_period_days; renewals.test.js</t>
         </is>
       </c>
       <c r="K69" s="6" t="inlineStr"/>
@@ -4840,7 +4848,7 @@
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
@@ -4850,12 +4858,12 @@
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>Renewal re-rating, negotiation with the insurer and renewal quotation</t>
+          <t>Renewal of placed and co-insured risks through the placement journey</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Broker</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
@@ -4864,7 +4872,7 @@
         </is>
       </c>
       <c r="F70" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G70" s="12" t="n">
         <v>2</v>
@@ -4879,7 +4887,7 @@
       </c>
       <c r="J70" s="6" t="inlineStr">
         <is>
-          <t>Renewals &gt; Negotiations; renewals.test.js; money-single-source.test.js</t>
+          <t>placement.journey_applies_to_renewals; placement.test.js</t>
         </is>
       </c>
       <c r="K70" s="6" t="inlineStr"/>
@@ -4888,7 +4896,7 @@
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
@@ -4898,7 +4906,7 @@
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>Renewal batch (up to 500 policies)</t>
+          <t>Renewal notices by SMS or messaging app</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
@@ -4912,10 +4920,10 @@
         </is>
       </c>
       <c r="F71" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G71" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="G71" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="H71" s="7">
         <f>F71*G71</f>
@@ -4927,74 +4935,62 @@
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
-          <t>Renewals &gt; Renewal Batch; renewals.test.js</t>
-        </is>
-      </c>
-      <c r="K71" s="6" t="inlineStr"/>
+          <t>E-mail and in-app only (product functionality checklist item 59)</t>
+        </is>
+      </c>
+      <c r="K71" s="6" t="inlineStr">
+        <is>
+          <t>No SMS or Viber gateway.</t>
+        </is>
+      </c>
       <c r="L71" s="7" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="7" t="inlineStr">
-        <is>
-          <t>7.04</t>
-        </is>
-      </c>
-      <c r="B72" s="6" t="inlineStr">
-        <is>
-          <t>Renewals and retention</t>
-        </is>
-      </c>
-      <c r="C72" s="6" t="inlineStr">
-        <is>
-          <t>At-risk scoring, retention analytics and performance</t>
-        </is>
-      </c>
-      <c r="D72" s="7" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="E72" s="7" t="inlineStr">
-        <is>
-          <t>Ops</t>
-        </is>
-      </c>
-      <c r="F72" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G72" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="H72" s="7">
-        <f>F72*G72</f>
-        <v/>
-      </c>
-      <c r="I72" s="7">
-        <f>2*F72</f>
-        <v/>
-      </c>
-      <c r="J72" s="6" t="inlineStr">
-        <is>
-          <t>Renewals &gt; At-Risk Policies, Retention Analytics, Performance; renewals.test.js</t>
-        </is>
-      </c>
-      <c r="K72" s="6" t="inlineStr"/>
-      <c r="L72" s="7" t="inlineStr"/>
+      <c r="A72" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B72" s="9" t="inlineStr">
+        <is>
+          <t>Billing, collection, credit control and receipts</t>
+        </is>
+      </c>
+      <c r="C72" s="9" t="inlineStr">
+        <is>
+          <t>L1 subtotal: fit 89.3%</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="inlineStr"/>
+      <c r="E72" s="9" t="inlineStr"/>
+      <c r="F72" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="G72" s="9" t="inlineStr"/>
+      <c r="H72" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I72" s="10" t="n">
+        <v>56</v>
+      </c>
+      <c r="J72" s="9" t="inlineStr"/>
+      <c r="K72" s="9" t="inlineStr"/>
+      <c r="L72" s="9" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>Renewals and retention</t>
+          <t>Billing, collection, credit control and receipts</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>Lapse management and win-back</t>
+          <t>Premium bill on issue, endorsement and renewal; invoice e-mailed</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
@@ -5008,7 +5004,7 @@
         </is>
       </c>
       <c r="F73" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G73" s="12" t="n">
         <v>2</v>
@@ -5023,7 +5019,7 @@
       </c>
       <c r="J73" s="6" t="inlineStr">
         <is>
-          <t>Renewals &gt; Lapse Management; renewals.grace_period_days; renewals.test.js</t>
+          <t>INV series; E-mail invoice; receipts.test.js; email-documents.test.js</t>
         </is>
       </c>
       <c r="K73" s="6" t="inlineStr"/>
@@ -5032,22 +5028,22 @@
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>Renewals and retention</t>
+          <t>Billing, collection, credit control and receipts</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>Renewal of placed and co-insured risks through the placement journey</t>
+          <t>Payment capture (cash, cheque, transfer, online) with proof for verification</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>Broker</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
@@ -5056,7 +5052,7 @@
         </is>
       </c>
       <c r="F74" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G74" s="12" t="n">
         <v>2</v>
@@ -5071,7 +5067,7 @@
       </c>
       <c r="J74" s="6" t="inlineStr">
         <is>
-          <t>placement.journey_applies_to_renewals; placement.test.js</t>
+          <t>Operations &gt; Payments; payments.test.js; policy-payments.test.js; payment-segregation.test.js</t>
         </is>
       </c>
       <c r="K74" s="6" t="inlineStr"/>
@@ -5080,17 +5076,17 @@
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>8.03</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>Renewals and retention</t>
+          <t>Billing, collection, credit control and receipts</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>Renewal notices by SMS or messaging app</t>
+          <t>Official receipt posting by Accounting, partial payments, bulk upload and bulk print</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
@@ -5104,10 +5100,10 @@
         </is>
       </c>
       <c r="F75" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G75" s="13" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="G75" s="12" t="n">
+        <v>2</v>
       </c>
       <c r="H75" s="7">
         <f>F75*G75</f>
@@ -5119,52 +5115,64 @@
       </c>
       <c r="J75" s="6" t="inlineStr">
         <is>
-          <t>E-mail and in-app only (product functionality checklist item 59)</t>
-        </is>
-      </c>
-      <c r="K75" s="6" t="inlineStr">
-        <is>
-          <t>No SMS or Viber gateway.</t>
-        </is>
-      </c>
+          <t>Accounts &gt; Receipts; receipts bulk upload (1,000 rows) and Bulk Print; receipts.test.js</t>
+        </is>
+      </c>
+      <c r="K75" s="6" t="inlineStr"/>
       <c r="L75" s="7" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B76" s="9" t="inlineStr">
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t>8.04</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
         <is>
           <t>Billing, collection, credit control and receipts</t>
         </is>
       </c>
-      <c r="C76" s="9" t="inlineStr">
-        <is>
-          <t>L1 subtotal: fit 89.7%</t>
-        </is>
-      </c>
-      <c r="D76" s="9" t="inlineStr"/>
-      <c r="E76" s="9" t="inlineStr"/>
-      <c r="F76" s="10" t="n">
-        <v>29</v>
-      </c>
-      <c r="G76" s="9" t="inlineStr"/>
-      <c r="H76" s="10" t="n">
-        <v>52</v>
-      </c>
-      <c r="I76" s="10" t="n">
-        <v>58</v>
-      </c>
-      <c r="J76" s="9" t="inlineStr"/>
-      <c r="K76" s="9" t="inlineStr"/>
-      <c r="L76" s="9" t="inlineStr"/>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>Receipt numbering continuity and printing on letterhead with TIN</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>BIR</t>
+        </is>
+      </c>
+      <c r="F76" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G76" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H76" s="7">
+        <f>F76*G76</f>
+        <v/>
+      </c>
+      <c r="I76" s="7">
+        <f>2*F76</f>
+        <v/>
+      </c>
+      <c r="J76" s="6" t="inlineStr">
+        <is>
+          <t>Master &gt; Document Numbering (61 series); numbering.test.js; printing.test.js</t>
+        </is>
+      </c>
+      <c r="K76" s="6" t="inlineStr"/>
+      <c r="L76" s="7" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
@@ -5174,7 +5182,7 @@
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>Premium bill on issue, endorsement and renewal; invoice e-mailed</t>
+          <t>Returned cheques (DAIF, DAUD) cancel the receipt and reopen the bill</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
@@ -5188,7 +5196,7 @@
         </is>
       </c>
       <c r="F77" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G77" s="12" t="n">
         <v>2</v>
@@ -5203,7 +5211,7 @@
       </c>
       <c r="J77" s="6" t="inlineStr">
         <is>
-          <t>INV series; E-mail invoice; receipts.test.js; email-documents.test.js</t>
+          <t>Bank transaction types; receipts.test.js; bank-reconciliation.test.js</t>
         </is>
       </c>
       <c r="K77" s="6" t="inlineStr"/>
@@ -5212,7 +5220,7 @@
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>8.06</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
@@ -5222,7 +5230,7 @@
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>Payment capture (cash, cheque, transfer, online) with proof for verification</t>
+          <t>Online payment links with automatic receipt</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
@@ -5236,7 +5244,7 @@
         </is>
       </c>
       <c r="F78" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G78" s="12" t="n">
         <v>2</v>
@@ -5251,16 +5259,20 @@
       </c>
       <c r="J78" s="6" t="inlineStr">
         <is>
-          <t>Operations &gt; Payments; payments.test.js; policy-payments.test.js; payment-segregation.test.js</t>
-        </is>
-      </c>
-      <c r="K78" s="6" t="inlineStr"/>
+          <t>Payment links (PayMongo, Dragonpay, sandbox provider); payments.test.js</t>
+        </is>
+      </c>
+      <c r="K78" s="6" t="inlineStr">
+        <is>
+          <t>Tested with the sandbox provider only; live keys are a go-live task.</t>
+        </is>
+      </c>
       <c r="L78" s="7" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>8.07</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
@@ -5270,7 +5282,7 @@
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>Official receipt posting by Accounting, partial payments</t>
+          <t>Receivables ageing and automatic collection reminders</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
@@ -5299,7 +5311,7 @@
       </c>
       <c r="J79" s="6" t="inlineStr">
         <is>
-          <t>Accounts &gt; Receipts; receipts.test.js</t>
+          <t>Accounts &gt; Collections; Collection reminders job; collections.test.js</t>
         </is>
       </c>
       <c r="K79" s="6" t="inlineStr"/>
@@ -5308,7 +5320,7 @@
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>8.04</t>
+          <t>8.08</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
@@ -5318,7 +5330,7 @@
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>Receipt numbering continuity and printing on letterhead with TIN</t>
+          <t>Premium payment warranty and credit terms per insurer (Insurance Code, IC rules)</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
@@ -5328,11 +5340,11 @@
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>BIR</t>
+          <t>IC</t>
         </is>
       </c>
       <c r="F80" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G80" s="12" t="n">
         <v>2</v>
@@ -5347,7 +5359,7 @@
       </c>
       <c r="J80" s="6" t="inlineStr">
         <is>
-          <t>Master &gt; Document Numbering (61 series); numbering.test.js; printing.test.js</t>
+          <t>Insurance Company &gt; Premium Payment Warranty; Premium Warranty Monitor; claims.block_unpaid_premium; credit-control.test.js</t>
         </is>
       </c>
       <c r="K80" s="6" t="inlineStr"/>
@@ -5356,7 +5368,7 @@
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.09</t>
         </is>
       </c>
       <c r="B81" s="6" t="inlineStr">
@@ -5366,7 +5378,7 @@
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>Returned cheques (DAIF, DAUD) cancel the receipt and reopen the bill</t>
+          <t>Instalment billing with separate instalment invoices</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
@@ -5382,8 +5394,8 @@
       <c r="F81" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G81" s="12" t="n">
-        <v>2</v>
+      <c r="G81" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="H81" s="7">
         <f>F81*G81</f>
@@ -5395,16 +5407,20 @@
       </c>
       <c r="J81" s="6" t="inlineStr">
         <is>
-          <t>Bank transaction types; receipts.test.js; bank-reconciliation.test.js</t>
-        </is>
-      </c>
-      <c r="K81" s="6" t="inlineStr"/>
+          <t>Accounts &gt; Credit Control &gt; Instalment Plans; credit-control.test.js</t>
+        </is>
+      </c>
+      <c r="K81" s="6" t="inlineStr">
+        <is>
+          <t>Plans split the follow-up of a bill without changing the ledger; no invoice per instalment.</t>
+        </is>
+      </c>
       <c r="L81" s="7" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>8.10</t>
         </is>
       </c>
       <c r="B82" s="6" t="inlineStr">
@@ -5414,7 +5430,7 @@
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>Online payment links with automatic receipt</t>
+          <t>Client credit limits with exception notice</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
@@ -5428,7 +5444,7 @@
         </is>
       </c>
       <c r="F82" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G82" s="12" t="n">
         <v>2</v>
@@ -5443,20 +5459,16 @@
       </c>
       <c r="J82" s="6" t="inlineStr">
         <is>
-          <t>Payment links (PayMongo, Dragonpay, sandbox provider); payments.test.js</t>
-        </is>
-      </c>
-      <c r="K82" s="6" t="inlineStr">
-        <is>
-          <t>Tested with the sandbox provider only; live keys are a go-live task.</t>
-        </is>
-      </c>
+          <t>Accounts &gt; Credit Control &gt; Client Credit Limits; credit-control.test.js</t>
+        </is>
+      </c>
+      <c r="K82" s="6" t="inlineStr"/>
       <c r="L82" s="7" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>8.11</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
@@ -5466,7 +5478,7 @@
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>Receivables ageing and automatic collection reminders</t>
+          <t>Collection follow-up log, commitments and escalation</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
@@ -5480,7 +5492,7 @@
         </is>
       </c>
       <c r="F83" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G83" s="12" t="n">
         <v>2</v>
@@ -5495,7 +5507,7 @@
       </c>
       <c r="J83" s="6" t="inlineStr">
         <is>
-          <t>Accounts &gt; Collections; Collection reminders job; collections.test.js</t>
+          <t>Collection items; collections.test.js</t>
         </is>
       </c>
       <c r="K83" s="6" t="inlineStr"/>
@@ -5504,7 +5516,7 @@
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>8.08</t>
+          <t>8.12</t>
         </is>
       </c>
       <c r="B84" s="6" t="inlineStr">
@@ -5514,7 +5526,7 @@
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>Premium payment warranty and credit terms per insurer (Insurance Code, IC rules)</t>
+          <t>Post-dated cheque register and deposit on due date</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
@@ -5524,14 +5536,14 @@
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="F84" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G84" s="12" t="n">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="G84" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="H84" s="7">
         <f>F84*G84</f>
@@ -5543,78 +5555,62 @@
       </c>
       <c r="J84" s="6" t="inlineStr">
         <is>
-          <t>Insurance Company &gt; Premium Payment Warranty; Premium Warranty Monitor; claims.block_unpaid_premium; credit-control.test.js</t>
-        </is>
-      </c>
-      <c r="K84" s="6" t="inlineStr"/>
+          <t>Not found as a register (cheque date handling in disbursements only)</t>
+        </is>
+      </c>
+      <c r="K84" s="6" t="inlineStr">
+        <is>
+          <t>Post-dated cheques received from clients are not tracked until deposit.</t>
+        </is>
+      </c>
       <c r="L84" s="7" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="7" t="inlineStr">
-        <is>
-          <t>8.09</t>
-        </is>
-      </c>
-      <c r="B85" s="6" t="inlineStr">
-        <is>
-          <t>Billing, collection, credit control and receipts</t>
-        </is>
-      </c>
-      <c r="C85" s="6" t="inlineStr">
-        <is>
-          <t>Instalment billing with separate instalment invoices</t>
-        </is>
-      </c>
-      <c r="D85" s="7" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="E85" s="7" t="inlineStr">
-        <is>
-          <t>Ops</t>
-        </is>
-      </c>
-      <c r="F85" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G85" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H85" s="7">
-        <f>F85*G85</f>
-        <v/>
-      </c>
-      <c r="I85" s="7">
-        <f>2*F85</f>
-        <v/>
-      </c>
-      <c r="J85" s="6" t="inlineStr">
-        <is>
-          <t>Accounts &gt; Credit Control &gt; Instalment Plans; credit-control.test.js</t>
-        </is>
-      </c>
-      <c r="K85" s="6" t="inlineStr">
-        <is>
-          <t>Plans split the follow-up of a bill without changing the ledger; no invoice per instalment.</t>
-        </is>
-      </c>
-      <c r="L85" s="7" t="inlineStr"/>
+      <c r="A85" s="9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B85" s="9" t="inlineStr">
+        <is>
+          <t>Remittance, direct bill and insurer reconciliation</t>
+        </is>
+      </c>
+      <c r="C85" s="9" t="inlineStr">
+        <is>
+          <t>L1 subtotal: fit 83.3%</t>
+        </is>
+      </c>
+      <c r="D85" s="9" t="inlineStr"/>
+      <c r="E85" s="9" t="inlineStr"/>
+      <c r="F85" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="G85" s="9" t="inlineStr"/>
+      <c r="H85" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="I85" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="J85" s="9" t="inlineStr"/>
+      <c r="K85" s="9" t="inlineStr"/>
+      <c r="L85" s="9" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>8.10</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>Billing, collection, credit control and receipts</t>
+          <t>Remittance, direct bill and insurer reconciliation</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>Client credit limits with exception notice</t>
+          <t>Remittance per insurer net of commission, by co-insurer share</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
@@ -5624,11 +5620,11 @@
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>IC</t>
         </is>
       </c>
       <c r="F86" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G86" s="12" t="n">
         <v>2</v>
@@ -5643,7 +5639,7 @@
       </c>
       <c r="J86" s="6" t="inlineStr">
         <is>
-          <t>Accounts &gt; Credit Control &gt; Client Credit Limits; credit-control.test.js</t>
+          <t>Accounts &gt; Remittance &gt; Automated Processing; remittance.test.js</t>
         </is>
       </c>
       <c r="K86" s="6" t="inlineStr"/>
@@ -5652,17 +5648,17 @@
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>8.11</t>
+          <t>9.02</t>
         </is>
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>Billing, collection, credit control and receipts</t>
+          <t>Remittance, direct bill and insurer reconciliation</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>Collection follow-up log, commitments and escalation</t>
+          <t>Remittance terms per insurer, due dates and remittance ageing</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
@@ -5672,11 +5668,11 @@
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>IC</t>
         </is>
       </c>
       <c r="F87" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G87" s="12" t="n">
         <v>2</v>
@@ -5691,7 +5687,7 @@
       </c>
       <c r="J87" s="6" t="inlineStr">
         <is>
-          <t>Collection items; collections.test.js</t>
+          <t>Insurance Company &gt; Remittance Terms; Credit Control &gt; Remittance Ageing; remittance.test.js</t>
         </is>
       </c>
       <c r="K87" s="6" t="inlineStr"/>
@@ -5700,17 +5696,17 @@
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>9.03</t>
         </is>
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>Billing, collection, credit control and receipts</t>
+          <t>Remittance, direct bill and insurer reconciliation</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>Post-dated cheque register and deposit on due date</t>
+          <t>Remittance approval within Authority Matrix limits and settlement by payment voucher</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
@@ -5726,8 +5722,8 @@
       <c r="F88" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G88" s="13" t="n">
-        <v>0</v>
+      <c r="G88" s="12" t="n">
+        <v>2</v>
       </c>
       <c r="H88" s="7">
         <f>F88*G88</f>
@@ -5739,30 +5735,26 @@
       </c>
       <c r="J88" s="6" t="inlineStr">
         <is>
-          <t>Not found as a register (cheque date handling in disbursements only)</t>
-        </is>
-      </c>
-      <c r="K88" s="6" t="inlineStr">
-        <is>
-          <t>Post-dated cheques received from clients are not tracked until deposit.</t>
-        </is>
-      </c>
+          <t>Remittance &gt; Approval Workflow, Settlement, Electronic Transfer; Authority Matrix; consolidation.test.js; remittance.test.js; disbursements.test.js</t>
+        </is>
+      </c>
+      <c r="K88" s="6" t="inlineStr"/>
       <c r="L88" s="7" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="7" t="inlineStr">
         <is>
-          <t>8.13</t>
+          <t>9.05</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>Billing, collection, credit control and receipts</t>
+          <t>Remittance, direct bill and insurer reconciliation</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>Bulk receipt upload and bulk print</t>
+          <t>Bank payment file (InstaPay, PESONet, bulk credit) for insurers and referrers</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
@@ -5776,10 +5768,10 @@
         </is>
       </c>
       <c r="F89" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G89" s="12" t="n">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="G89" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="H89" s="7">
         <f>F89*G89</f>
@@ -5791,48 +5783,68 @@
       </c>
       <c r="J89" s="6" t="inlineStr">
         <is>
-          <t>Receipts bulk upload (1,000 rows) and Bulk Print; receipts.test.js</t>
-        </is>
-      </c>
-      <c r="K89" s="6" t="inlineStr"/>
+          <t>Transfers recorded only (checklist item 58)</t>
+        </is>
+      </c>
+      <c r="K89" s="6" t="inlineStr">
+        <is>
+          <t>No bank upload file; payments keyed in the bank portal.</t>
+        </is>
+      </c>
       <c r="L89" s="7" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="9" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B90" s="9" t="inlineStr">
+      <c r="A90" s="7" t="inlineStr">
+        <is>
+          <t>9.06</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
         <is>
           <t>Remittance, direct bill and insurer reconciliation</t>
         </is>
       </c>
-      <c r="C90" s="9" t="inlineStr">
-        <is>
-          <t>L1 subtotal: fit 85.0%</t>
-        </is>
-      </c>
-      <c r="D90" s="9" t="inlineStr"/>
-      <c r="E90" s="9" t="inlineStr"/>
-      <c r="F90" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="G90" s="9" t="inlineStr"/>
-      <c r="H90" s="10" t="n">
-        <v>34</v>
-      </c>
-      <c r="I90" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="J90" s="9" t="inlineStr"/>
-      <c r="K90" s="9" t="inlineStr"/>
-      <c r="L90" s="9" t="inlineStr"/>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>Direct bill commission debit notes with VAT and EWT</t>
+        </is>
+      </c>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>BIR</t>
+        </is>
+      </c>
+      <c r="F90" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G90" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H90" s="7">
+        <f>F90*G90</f>
+        <v/>
+      </c>
+      <c r="I90" s="7">
+        <f>2*F90</f>
+        <v/>
+      </c>
+      <c r="J90" s="6" t="inlineStr">
+        <is>
+          <t>Remittance &gt; Direct Bill Processing; direct-bill.test.js; direct-bill-client-payments.test.js</t>
+        </is>
+      </c>
+      <c r="K90" s="6" t="inlineStr"/>
+      <c r="L90" s="7" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="7" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>9.07</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
@@ -5842,21 +5854,21 @@
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>Remittance per insurer net of commission, by co-insurer share</t>
+          <t>Agency bill processing</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Agent</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="F91" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G91" s="12" t="n">
         <v>2</v>
@@ -5871,7 +5883,7 @@
       </c>
       <c r="J91" s="6" t="inlineStr">
         <is>
-          <t>Accounts &gt; Remittance &gt; Automated Processing; remittance.test.js</t>
+          <t>Remittance &gt; Agency Bill Processing (/finance/remittance/agencybill); remittance.test.js</t>
         </is>
       </c>
       <c r="K91" s="6" t="inlineStr"/>
@@ -5880,7 +5892,7 @@
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>9.02</t>
+          <t>9.08</t>
         </is>
       </c>
       <c r="B92" s="6" t="inlineStr">
@@ -5890,7 +5902,7 @@
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>Remittance terms per insurer, due dates and remittance ageing</t>
+          <t>Insurer statement of account import, matching and differences</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
@@ -5900,11 +5912,11 @@
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="F92" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G92" s="12" t="n">
         <v>2</v>
@@ -5919,7 +5931,7 @@
       </c>
       <c r="J92" s="6" t="inlineStr">
         <is>
-          <t>Insurance Company &gt; Remittance Terms; Credit Control &gt; Remittance Ageing; remittance.test.js</t>
+          <t>Accounts &gt; Insurer Reconciliation &gt; Insurer Statements; insurer-reconciliation.test.js</t>
         </is>
       </c>
       <c r="K92" s="6" t="inlineStr"/>
@@ -5928,7 +5940,7 @@
     <row r="93">
       <c r="A93" s="7" t="inlineStr">
         <is>
-          <t>9.03</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="B93" s="6" t="inlineStr">
@@ -5938,7 +5950,7 @@
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>Remittance approval within Authority Matrix limits</t>
+          <t>Insurer system integration (policy, premium, claims data by API)</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
@@ -5952,10 +5964,10 @@
         </is>
       </c>
       <c r="F93" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G93" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="G93" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="H93" s="7">
         <f>F93*G93</f>
@@ -5967,74 +5979,62 @@
       </c>
       <c r="J93" s="6" t="inlineStr">
         <is>
-          <t>Remittance &gt; Approval Workflow; Authority Matrix; consolidation.test.js; remittance.test.js</t>
-        </is>
-      </c>
-      <c r="K93" s="6" t="inlineStr"/>
+          <t>Files and e-mail only (checklist item 57)</t>
+        </is>
+      </c>
+      <c r="K93" s="6" t="inlineStr">
+        <is>
+          <t>No insurer API connector.</t>
+        </is>
+      </c>
       <c r="L93" s="7" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="7" t="inlineStr">
-        <is>
-          <t>9.04</t>
-        </is>
-      </c>
-      <c r="B94" s="6" t="inlineStr">
-        <is>
-          <t>Remittance, direct bill and insurer reconciliation</t>
-        </is>
-      </c>
-      <c r="C94" s="6" t="inlineStr">
-        <is>
-          <t>Settlement by payment voucher and electronic transfer record</t>
-        </is>
-      </c>
-      <c r="D94" s="7" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="E94" s="7" t="inlineStr">
-        <is>
-          <t>Ops</t>
-        </is>
-      </c>
-      <c r="F94" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G94" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="H94" s="7">
-        <f>F94*G94</f>
-        <v/>
-      </c>
-      <c r="I94" s="7">
-        <f>2*F94</f>
-        <v/>
-      </c>
-      <c r="J94" s="6" t="inlineStr">
-        <is>
-          <t>Remittance &gt; Settlement, Electronic Transfer; disbursements.test.js</t>
-        </is>
-      </c>
-      <c r="K94" s="6" t="inlineStr"/>
-      <c r="L94" s="7" t="inlineStr"/>
+      <c r="A94" s="9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B94" s="9" t="inlineStr">
+        <is>
+          <t>Commission, referrers and incentives</t>
+        </is>
+      </c>
+      <c r="C94" s="9" t="inlineStr">
+        <is>
+          <t>L1 subtotal: fit 87.5%</t>
+        </is>
+      </c>
+      <c r="D94" s="9" t="inlineStr"/>
+      <c r="E94" s="9" t="inlineStr"/>
+      <c r="F94" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="G94" s="9" t="inlineStr"/>
+      <c r="H94" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="I94" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="J94" s="9" t="inlineStr"/>
+      <c r="K94" s="9" t="inlineStr"/>
+      <c r="L94" s="9" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="7" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>10.01</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>Remittance, direct bill and insurer reconciliation</t>
+          <t>Commission, referrers and incentives</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>Bank payment file (InstaPay, PESONet, bulk credit) for insurers and referrers</t>
+          <t>Commission rate matrix by insurer, product, line and policy type with dates</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
@@ -6048,10 +6048,10 @@
         </is>
       </c>
       <c r="F95" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G95" s="13" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="G95" s="12" t="n">
+        <v>2</v>
       </c>
       <c r="H95" s="7">
         <f>F95*G95</f>
@@ -6063,30 +6063,26 @@
       </c>
       <c r="J95" s="6" t="inlineStr">
         <is>
-          <t>Transfers recorded only (checklist item 58)</t>
-        </is>
-      </c>
-      <c r="K95" s="6" t="inlineStr">
-        <is>
-          <t>No bank upload file; payments keyed in the bank portal.</t>
-        </is>
-      </c>
+          <t>Master &gt; Finance &gt; Commission Rate Matrix; commission.test.js</t>
+        </is>
+      </c>
+      <c r="K95" s="6" t="inlineStr"/>
       <c r="L95" s="7" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t>9.06</t>
+          <t>10.02</t>
         </is>
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>Remittance, direct bill and insurer reconciliation</t>
+          <t>Commission, referrers and incentives</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>Direct bill commission debit notes with VAT and EWT</t>
+          <t>Brokerage or agency commission income per insurer per policy</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
@@ -6096,7 +6092,7 @@
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
-          <t>BIR</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="F96" s="7" t="n">
@@ -6115,7 +6111,7 @@
       </c>
       <c r="J96" s="6" t="inlineStr">
         <is>
-          <t>Remittance &gt; Direct Bill Processing; direct-bill.test.js; direct-bill-client-payments.test.js</t>
+          <t>Posting rule policy issue; accounting.test.js; commission.test.js</t>
         </is>
       </c>
       <c r="K96" s="6" t="inlineStr"/>
@@ -6124,22 +6120,22 @@
     <row r="97">
       <c r="A97" s="7" t="inlineStr">
         <is>
-          <t>9.07</t>
+          <t>10.03</t>
         </is>
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>Remittance, direct bill and insurer reconciliation</t>
+          <t>Commission, referrers and incentives</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>Agency bill processing</t>
+          <t>Referrer and sub-agent commission chain, payable on full collection</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>Agent</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
@@ -6148,7 +6144,7 @@
         </is>
       </c>
       <c r="F97" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G97" s="12" t="n">
         <v>2</v>
@@ -6163,7 +6159,7 @@
       </c>
       <c r="J97" s="6" t="inlineStr">
         <is>
-          <t>Remittance &gt; Agency Bill Processing (/finance/remittance/agencybill); remittance.test.js</t>
+          <t>commission.require_full_payment; Agents/Referrer Accounts; commission.test.js</t>
         </is>
       </c>
       <c r="K97" s="6" t="inlineStr"/>
@@ -6172,17 +6168,17 @@
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>9.08</t>
+          <t>10.04</t>
         </is>
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>Remittance, direct bill and insurer reconciliation</t>
+          <t>Commission, referrers and incentives</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>Insurer statement of account import, matching and differences</t>
+          <t>Withholding tax on commission paid, by payee type and ATC</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
@@ -6192,11 +6188,11 @@
       </c>
       <c r="E98" s="7" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>BIR</t>
         </is>
       </c>
       <c r="F98" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G98" s="12" t="n">
         <v>2</v>
@@ -6211,7 +6207,7 @@
       </c>
       <c r="J98" s="6" t="inlineStr">
         <is>
-          <t>Accounts &gt; Insurer Reconciliation &gt; Insurer Statements; insurer-reconciliation.test.js</t>
+          <t>commission.wht_code_by_type; bir.atc_by_payee; commission-taxes.test.js</t>
         </is>
       </c>
       <c r="K98" s="6" t="inlineStr"/>
@@ -6220,17 +6216,17 @@
     <row r="99">
       <c r="A99" s="7" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>10.05</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>Remittance, direct bill and insurer reconciliation</t>
+          <t>Commission, referrers and incentives</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>Insurer system integration (policy, premium, claims data by API)</t>
+          <t>Commission payout by voucher and bulk disbursement</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
@@ -6244,10 +6240,10 @@
         </is>
       </c>
       <c r="F99" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G99" s="13" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="G99" s="12" t="n">
+        <v>2</v>
       </c>
       <c r="H99" s="7">
         <f>F99*G99</f>
@@ -6259,52 +6255,64 @@
       </c>
       <c r="J99" s="6" t="inlineStr">
         <is>
-          <t>Files and e-mail only (checklist item 57)</t>
-        </is>
-      </c>
-      <c r="K99" s="6" t="inlineStr">
-        <is>
-          <t>No insurer API connector.</t>
-        </is>
-      </c>
+          <t>Generate payout; Disbursement &gt; Bulk Disburse; disbursements.test.js</t>
+        </is>
+      </c>
+      <c r="K99" s="6" t="inlineStr"/>
       <c r="L99" s="7" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B100" s="9" t="inlineStr">
+      <c r="A100" s="7" t="inlineStr">
+        <is>
+          <t>10.07</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
         <is>
           <t>Commission, referrers and incentives</t>
         </is>
       </c>
-      <c r="C100" s="9" t="inlineStr">
-        <is>
-          <t>L1 subtotal: fit 88.6%</t>
-        </is>
-      </c>
-      <c r="D100" s="9" t="inlineStr"/>
-      <c r="E100" s="9" t="inlineStr"/>
-      <c r="F100" s="10" t="n">
-        <v>22</v>
-      </c>
-      <c r="G100" s="9" t="inlineStr"/>
-      <c r="H100" s="10" t="n">
-        <v>39</v>
-      </c>
-      <c r="I100" s="10" t="n">
-        <v>44</v>
-      </c>
-      <c r="J100" s="9" t="inlineStr"/>
-      <c r="K100" s="9" t="inlineStr"/>
-      <c r="L100" s="9" t="inlineStr"/>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>Commission statements for referrers and the broker</t>
+        </is>
+      </c>
+      <c r="D100" s="7" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E100" s="7" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+      <c r="F100" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G100" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H100" s="7">
+        <f>F100*G100</f>
+        <v/>
+      </c>
+      <c r="I100" s="7">
+        <f>2*F100</f>
+        <v/>
+      </c>
+      <c r="J100" s="6" t="inlineStr">
+        <is>
+          <t>Broker Commission Statement; Commission Dashboard; reports.test.js</t>
+        </is>
+      </c>
+      <c r="K100" s="6" t="inlineStr"/>
+      <c r="L100" s="7" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="7" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="B101" s="6" t="inlineStr">
@@ -6314,7 +6322,7 @@
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>Commission rate matrix by insurer, product, line and policy type with dates</t>
+          <t>Incentive programmes for account executives</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
@@ -6328,7 +6336,7 @@
         </is>
       </c>
       <c r="F101" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G101" s="12" t="n">
         <v>2</v>
@@ -6343,7 +6351,7 @@
       </c>
       <c r="J101" s="6" t="inlineStr">
         <is>
-          <t>Master &gt; Finance &gt; Commission Rate Matrix; commission.test.js</t>
+          <t>Incentive &gt; My Programs, Calculations, Approvals, Statement; incentive.test.js</t>
         </is>
       </c>
       <c r="K101" s="6" t="inlineStr"/>
@@ -6352,7 +6360,7 @@
     <row r="102">
       <c r="A102" s="7" t="inlineStr">
         <is>
-          <t>10.02</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="B102" s="6" t="inlineStr">
@@ -6362,7 +6370,7 @@
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>Brokerage or agency commission income per insurer per policy</t>
+          <t>Licence check of agents and sub-agents before paying commission</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
@@ -6372,14 +6380,14 @@
       </c>
       <c r="E102" s="7" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>IC</t>
         </is>
       </c>
       <c r="F102" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G102" s="12" t="n">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="G102" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="H102" s="7">
         <f>F102*G102</f>
@@ -6391,16 +6399,20 @@
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
-          <t>Posting rule policy issue; accounting.test.js; commission.test.js</t>
-        </is>
-      </c>
-      <c r="K102" s="6" t="inlineStr"/>
+          <t>No licence number or expiry on referrer accounts (grep licence: company master only)</t>
+        </is>
+      </c>
+      <c r="K102" s="6" t="inlineStr">
+        <is>
+          <t>Commission can be paid to a referrer without a valid IC licence where one is required.</t>
+        </is>
+      </c>
       <c r="L102" s="7" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="7" t="inlineStr">
         <is>
-          <t>10.03</t>
+          <t>10.10</t>
         </is>
       </c>
       <c r="B103" s="6" t="inlineStr">
@@ -6410,7 +6422,7 @@
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>Referrer and sub-agent commission chain, payable on full collection</t>
+          <t>Overriding, profit and contingent commission from insurers</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
@@ -6424,10 +6436,10 @@
         </is>
       </c>
       <c r="F103" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G103" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="G103" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="H103" s="7">
         <f>F103*G103</f>
@@ -6439,74 +6451,62 @@
       </c>
       <c r="J103" s="6" t="inlineStr">
         <is>
-          <t>commission.require_full_payment; Agents/Referrer Accounts; commission.test.js</t>
-        </is>
-      </c>
-      <c r="K103" s="6" t="inlineStr"/>
+          <t>Journal Voucher (manual)</t>
+        </is>
+      </c>
+      <c r="K103" s="6" t="inlineStr">
+        <is>
+          <t>No computation; booked by journal voucher.</t>
+        </is>
+      </c>
       <c r="L103" s="7" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="7" t="inlineStr">
-        <is>
-          <t>10.04</t>
-        </is>
-      </c>
-      <c r="B104" s="6" t="inlineStr">
-        <is>
-          <t>Commission, referrers and incentives</t>
-        </is>
-      </c>
-      <c r="C104" s="6" t="inlineStr">
-        <is>
-          <t>Withholding tax on commission paid, by payee type and ATC</t>
-        </is>
-      </c>
-      <c r="D104" s="7" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="E104" s="7" t="inlineStr">
-        <is>
-          <t>BIR</t>
-        </is>
-      </c>
-      <c r="F104" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G104" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="H104" s="7">
-        <f>F104*G104</f>
-        <v/>
-      </c>
-      <c r="I104" s="7">
-        <f>2*F104</f>
-        <v/>
-      </c>
-      <c r="J104" s="6" t="inlineStr">
-        <is>
-          <t>commission.wht_code_by_type; bir.atc_by_payee; commission-taxes.test.js</t>
-        </is>
-      </c>
-      <c r="K104" s="6" t="inlineStr"/>
-      <c r="L104" s="7" t="inlineStr"/>
+      <c r="A104" s="9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B104" s="9" t="inlineStr">
+        <is>
+          <t>Claims assistance</t>
+        </is>
+      </c>
+      <c r="C104" s="9" t="inlineStr">
+        <is>
+          <t>L1 subtotal: fit 84.2%</t>
+        </is>
+      </c>
+      <c r="D104" s="9" t="inlineStr"/>
+      <c r="E104" s="9" t="inlineStr"/>
+      <c r="F104" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="G104" s="9" t="inlineStr"/>
+      <c r="H104" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="I104" s="10" t="n">
+        <v>38</v>
+      </c>
+      <c r="J104" s="9" t="inlineStr"/>
+      <c r="K104" s="9" t="inlineStr"/>
+      <c r="L104" s="9" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="7" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>11.01</t>
         </is>
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>Commission, referrers and incentives</t>
+          <t>Claims assistance</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>Commission payout by voucher and bulk disbursement</t>
+          <t>Claim registration with incident, driver, third party and documents</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
@@ -6520,7 +6520,7 @@
         </is>
       </c>
       <c r="F105" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G105" s="12" t="n">
         <v>2</v>
@@ -6535,7 +6535,7 @@
       </c>
       <c r="J105" s="6" t="inlineStr">
         <is>
-          <t>Generate payout; Disbursement &gt; Bulk Disburse; disbursements.test.js</t>
+          <t>Operations &gt; Claims (/agent/claim); claims.test.js</t>
         </is>
       </c>
       <c r="K105" s="6" t="inlineStr"/>
@@ -6544,17 +6544,17 @@
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t>10.06</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>Commission, referrers and incentives</t>
+          <t>Claims assistance</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>Commission clawback on return premium</t>
+          <t>Preliminary loss advice to the insurer by e-mail</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
@@ -6568,7 +6568,7 @@
         </is>
       </c>
       <c r="F106" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G106" s="12" t="n">
         <v>2</v>
@@ -6583,7 +6583,7 @@
       </c>
       <c r="J106" s="6" t="inlineStr">
         <is>
-          <t>Commission line status Reversed; commission.test.js</t>
+          <t>Claim registration e-mail to insurer claims address; claims.test.js</t>
         </is>
       </c>
       <c r="K106" s="6" t="inlineStr"/>
@@ -6592,17 +6592,17 @@
     <row r="107">
       <c r="A107" s="7" t="inlineStr">
         <is>
-          <t>10.07</t>
+          <t>11.03</t>
         </is>
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>Commission, referrers and incentives</t>
+          <t>Claims assistance</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>Commission statements for referrers and the broker</t>
+          <t>Claim document checklist per line and missing document follow-up</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
@@ -6618,8 +6618,8 @@
       <c r="F107" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G107" s="12" t="n">
-        <v>2</v>
+      <c r="G107" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="H107" s="7">
         <f>F107*G107</f>
@@ -6631,26 +6631,30 @@
       </c>
       <c r="J107" s="6" t="inlineStr">
         <is>
-          <t>Broker Commission Statement; Commission Dashboard; reports.test.js</t>
-        </is>
-      </c>
-      <c r="K107" s="6" t="inlineStr"/>
+          <t>Claim documents upload; causes of loss per line (GET /claims/config)</t>
+        </is>
+      </c>
+      <c r="K107" s="6" t="inlineStr">
+        <is>
+          <t>No required-document checklist or reminder to the claimant.</t>
+        </is>
+      </c>
       <c r="L107" s="7" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>Commission, referrers and incentives</t>
+          <t>Claims assistance</t>
         </is>
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>Incentive programmes for account executives</t>
+          <t>Adjuster, insurer claim number, status tracking, handling time and claims reports</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
@@ -6664,7 +6668,7 @@
         </is>
       </c>
       <c r="F108" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G108" s="12" t="n">
         <v>2</v>
@@ -6679,7 +6683,7 @@
       </c>
       <c r="J108" s="6" t="inlineStr">
         <is>
-          <t>Incentive &gt; My Programs, Calculations, Approvals, Statement; incentive.test.js</t>
+          <t>Claim statuses; claims.sla_days 20; Claims Dashboard; Claims Position, Claims Ageing; claims.test.js; reports.test.js</t>
         </is>
       </c>
       <c r="K108" s="6" t="inlineStr"/>
@@ -6688,17 +6692,17 @@
     <row r="109">
       <c r="A109" s="7" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>Commission, referrers and incentives</t>
+          <t>Claims assistance</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>Licence check of agents and sub-agents before paying commission</t>
+          <t>Settlement approval by a second user and claim letters (discharge voucher)</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
@@ -6708,14 +6712,14 @@
       </c>
       <c r="E109" s="7" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="F109" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G109" s="13" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="G109" s="12" t="n">
+        <v>2</v>
       </c>
       <c r="H109" s="7">
         <f>F109*G109</f>
@@ -6727,30 +6731,26 @@
       </c>
       <c r="J109" s="6" t="inlineStr">
         <is>
-          <t>No licence number or expiry on referrer accounts (grep licence: company master only)</t>
-        </is>
-      </c>
-      <c r="K109" s="6" t="inlineStr">
-        <is>
-          <t>Commission can be paid to a referrer without a valid IC licence where one is required.</t>
-        </is>
-      </c>
+          <t>claims.settlement_maker_checker; Claims Discharge Voucher PDF; claims.test.js</t>
+        </is>
+      </c>
+      <c r="K109" s="6" t="inlineStr"/>
       <c r="L109" s="7" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="7" t="inlineStr">
         <is>
-          <t>10.10</t>
+          <t>11.06</t>
         </is>
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>Commission, referrers and incentives</t>
+          <t>Claims assistance</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>Overriding, profit and contingent commission from insurers</t>
+          <t>Claims paid through the broker: funds received and paid to claimant</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
@@ -6764,7 +6764,7 @@
         </is>
       </c>
       <c r="F110" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G110" s="11" t="n">
         <v>1</v>
@@ -6779,52 +6779,68 @@
       </c>
       <c r="J110" s="6" t="inlineStr">
         <is>
-          <t>Journal Voucher (manual)</t>
+          <t>Settlement cash panel (POST /claims/:id/settlement-cash/...); claims.test.js</t>
         </is>
       </c>
       <c r="K110" s="6" t="inlineStr">
         <is>
-          <t>No computation; booked by journal voucher.</t>
+          <t>Panel is on the claim screens; Accounting menu not extended, so the System Administrator records it (known limitation).</t>
         </is>
       </c>
       <c r="L110" s="7" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="9" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B111" s="9" t="inlineStr">
+      <c r="A111" s="7" t="inlineStr">
+        <is>
+          <t>11.07</t>
+        </is>
+      </c>
+      <c r="B111" s="6" t="inlineStr">
         <is>
           <t>Claims assistance</t>
         </is>
       </c>
-      <c r="C111" s="9" t="inlineStr">
-        <is>
-          <t>L1 subtotal: fit 85.7%</t>
-        </is>
-      </c>
-      <c r="D111" s="9" t="inlineStr"/>
-      <c r="E111" s="9" t="inlineStr"/>
-      <c r="F111" s="10" t="n">
-        <v>21</v>
-      </c>
-      <c r="G111" s="9" t="inlineStr"/>
-      <c r="H111" s="10" t="n">
-        <v>36</v>
-      </c>
-      <c r="I111" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="J111" s="9" t="inlineStr"/>
-      <c r="K111" s="9" t="inlineStr"/>
-      <c r="L111" s="9" t="inlineStr"/>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>Co-insurer shares of claims and settlements</t>
+        </is>
+      </c>
+      <c r="D111" s="7" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E111" s="7" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+      <c r="F111" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G111" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H111" s="7">
+        <f>F111*G111</f>
+        <v/>
+      </c>
+      <c r="I111" s="7">
+        <f>2*F111</f>
+        <v/>
+      </c>
+      <c r="J111" s="6" t="inlineStr">
+        <is>
+          <t>Claim screens show each insurer share; claims.test.js</t>
+        </is>
+      </c>
+      <c r="K111" s="6" t="inlineStr"/>
+      <c r="L111" s="7" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="7" t="inlineStr">
         <is>
-          <t>11.01</t>
+          <t>11.08</t>
         </is>
       </c>
       <c r="B112" s="6" t="inlineStr">
@@ -6834,7 +6850,7 @@
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>Claim registration with incident, driver, third party and documents</t>
+          <t>Motor claims: repair shop, estimate and letter of authority</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
@@ -6848,10 +6864,10 @@
         </is>
       </c>
       <c r="F112" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G112" s="12" t="n">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="G112" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="H112" s="7">
         <f>F112*G112</f>
@@ -6863,74 +6879,62 @@
       </c>
       <c r="J112" s="6" t="inlineStr">
         <is>
-          <t>Operations &gt; Claims (/agent/claim); claims.test.js</t>
-        </is>
-      </c>
-      <c r="K112" s="6" t="inlineStr"/>
+          <t>Repair shop on settlement (migration 0216)</t>
+        </is>
+      </c>
+      <c r="K112" s="6" t="inlineStr">
+        <is>
+          <t>No estimate approval or letter of authority workflow.</t>
+        </is>
+      </c>
       <c r="L112" s="7" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="7" t="inlineStr">
-        <is>
-          <t>11.02</t>
-        </is>
-      </c>
-      <c r="B113" s="6" t="inlineStr">
-        <is>
-          <t>Claims assistance</t>
-        </is>
-      </c>
-      <c r="C113" s="6" t="inlineStr">
-        <is>
-          <t>Preliminary loss advice to the insurer by e-mail</t>
-        </is>
-      </c>
-      <c r="D113" s="7" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="E113" s="7" t="inlineStr">
-        <is>
-          <t>Ops</t>
-        </is>
-      </c>
-      <c r="F113" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G113" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="H113" s="7">
-        <f>F113*G113</f>
-        <v/>
-      </c>
-      <c r="I113" s="7">
-        <f>2*F113</f>
-        <v/>
-      </c>
-      <c r="J113" s="6" t="inlineStr">
-        <is>
-          <t>Claim registration e-mail to insurer claims address; claims.test.js</t>
-        </is>
-      </c>
-      <c r="K113" s="6" t="inlineStr"/>
-      <c r="L113" s="7" t="inlineStr"/>
+      <c r="A113" s="9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B113" s="9" t="inlineStr">
+        <is>
+          <t>Accounting, general ledger, period end and audit</t>
+        </is>
+      </c>
+      <c r="C113" s="9" t="inlineStr">
+        <is>
+          <t>L1 subtotal: fit 96.0%</t>
+        </is>
+      </c>
+      <c r="D113" s="9" t="inlineStr"/>
+      <c r="E113" s="9" t="inlineStr"/>
+      <c r="F113" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="G113" s="9" t="inlineStr"/>
+      <c r="H113" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="I113" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="J113" s="9" t="inlineStr"/>
+      <c r="K113" s="9" t="inlineStr"/>
+      <c r="L113" s="9" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="7" t="inlineStr">
         <is>
-          <t>11.03</t>
+          <t>12.01</t>
         </is>
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>Claims assistance</t>
+          <t>Accounting, general ledger, period end and audit</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>Claim document checklist per line and missing document follow-up</t>
+          <t>Double-entry general ledger fed by posting rules, each journal traced to its source</t>
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr">
@@ -6944,10 +6948,10 @@
         </is>
       </c>
       <c r="F114" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G114" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="G114" s="12" t="n">
+        <v>2</v>
       </c>
       <c r="H114" s="7">
         <f>F114*G114</f>
@@ -6959,30 +6963,26 @@
       </c>
       <c r="J114" s="6" t="inlineStr">
         <is>
-          <t>Claim documents upload; causes of loss per line (GET /claims/config)</t>
-        </is>
-      </c>
-      <c r="K114" s="6" t="inlineStr">
-        <is>
-          <t>No required-document checklist or reminder to the claimant.</t>
-        </is>
-      </c>
+          <t>Master &gt; Finance &gt; Posting Rules, Account Determination; General Ledger Detail, Journal Register; posting-rules.test.js; accounting-flow.test.js</t>
+        </is>
+      </c>
+      <c r="K114" s="6" t="inlineStr"/>
       <c r="L114" s="7" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="7" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>Claims assistance</t>
+          <t>Accounting, general ledger, period end and audit</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>Adjuster, insurer claim number, status tracking and handling time</t>
+          <t>Philippine broker chart of accounts with premium trust account</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
@@ -7011,7 +7011,7 @@
       </c>
       <c r="J115" s="6" t="inlineStr">
         <is>
-          <t>Claim statuses; claims.sla_days 20; Claims Dashboard; claims.test.js</t>
+          <t>Main Account, Sub Account masters; chart-of-accounts.test.js</t>
         </is>
       </c>
       <c r="K115" s="6" t="inlineStr"/>
@@ -7020,17 +7020,17 @@
     <row r="116">
       <c r="A116" s="7" t="inlineStr">
         <is>
-          <t>11.05</t>
+          <t>12.03</t>
         </is>
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>Claims assistance</t>
+          <t>Accounting, general ledger, period end and audit</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>Settlement approval by a second user and claim letters (discharge voucher)</t>
+          <t>Journal, correction and reversal vouchers with approval</t>
         </is>
       </c>
       <c r="D116" s="7" t="inlineStr">
@@ -7059,7 +7059,7 @@
       </c>
       <c r="J116" s="6" t="inlineStr">
         <is>
-          <t>claims.settlement_maker_checker; Claims Discharge Voucher PDF; claims.test.js</t>
+          <t>Accounts &gt; Journal Voucher, Correction JV, Reversal JV; journal.test.js</t>
         </is>
       </c>
       <c r="K116" s="6" t="inlineStr"/>
@@ -7068,17 +7068,17 @@
     <row r="117">
       <c r="A117" s="7" t="inlineStr">
         <is>
-          <t>11.06</t>
+          <t>12.04</t>
         </is>
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>Claims assistance</t>
+          <t>Accounting, general ledger, period end and audit</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>Claims paid through the broker: funds received and paid to claimant</t>
+          <t>Payment vouchers, cheques and petty cash</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
@@ -7092,10 +7092,10 @@
         </is>
       </c>
       <c r="F117" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G117" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="G117" s="12" t="n">
+        <v>2</v>
       </c>
       <c r="H117" s="7">
         <f>F117*G117</f>
@@ -7107,30 +7107,26 @@
       </c>
       <c r="J117" s="6" t="inlineStr">
         <is>
-          <t>Settlement cash panel (POST /claims/:id/settlement-cash/...); claims.test.js</t>
-        </is>
-      </c>
-      <c r="K117" s="6" t="inlineStr">
-        <is>
-          <t>Panel is on the claim screens; Accounting menu not extended, so the System Administrator records it (known limitation).</t>
-        </is>
-      </c>
+          <t>Accounts &gt; Disbursement, Petty Cash; disbursements.test.js</t>
+        </is>
+      </c>
+      <c r="K117" s="6" t="inlineStr"/>
       <c r="L117" s="7" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="7" t="inlineStr">
         <is>
-          <t>11.07</t>
+          <t>12.05</t>
         </is>
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>Claims assistance</t>
+          <t>Accounting, general ledger, period end and audit</t>
         </is>
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>Co-insurer shares of claims and settlements</t>
+          <t>Bank statement import, auto-match and reconciliation statement</t>
         </is>
       </c>
       <c r="D118" s="7" t="inlineStr">
@@ -7144,7 +7140,7 @@
         </is>
       </c>
       <c r="F118" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G118" s="12" t="n">
         <v>2</v>
@@ -7159,7 +7155,7 @@
       </c>
       <c r="J118" s="6" t="inlineStr">
         <is>
-          <t>Claim screens show each insurer share; claims.test.js</t>
+          <t>Accounts &gt; Bank Reconciliation; bank-reconciliation.test.js</t>
         </is>
       </c>
       <c r="K118" s="6" t="inlineStr"/>
@@ -7168,17 +7164,17 @@
     <row r="119">
       <c r="A119" s="7" t="inlineStr">
         <is>
-          <t>11.08</t>
+          <t>12.06</t>
         </is>
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>Claims assistance</t>
+          <t>Accounting, general ledger, period end and audit</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>Motor claims: repair shop, estimate and letter of authority</t>
+          <t>Month-end close with checklist, accruals and recurring journals</t>
         </is>
       </c>
       <c r="D119" s="7" t="inlineStr">
@@ -7192,10 +7188,10 @@
         </is>
       </c>
       <c r="F119" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G119" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="G119" s="12" t="n">
+        <v>2</v>
       </c>
       <c r="H119" s="7">
         <f>F119*G119</f>
@@ -7207,30 +7203,26 @@
       </c>
       <c r="J119" s="6" t="inlineStr">
         <is>
-          <t>Repair shop on settlement (migration 0216)</t>
-        </is>
-      </c>
-      <c r="K119" s="6" t="inlineStr">
-        <is>
-          <t>No estimate approval or letter of authority workflow.</t>
-        </is>
-      </c>
+          <t>Accounts &gt; Period End &gt; Month-End Close; period-end.test.js; period-end-calendar.test.js</t>
+        </is>
+      </c>
+      <c r="K119" s="6" t="inlineStr"/>
       <c r="L119" s="7" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="7" t="inlineStr">
         <is>
-          <t>11.09</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>Claims assistance</t>
+          <t>Accounting, general ledger, period end and audit</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>Claims position and ageing reports</t>
+          <t>Year-end close and opening balances</t>
         </is>
       </c>
       <c r="D120" s="7" t="inlineStr">
@@ -7259,48 +7251,64 @@
       </c>
       <c r="J120" s="6" t="inlineStr">
         <is>
-          <t>Claims Position, Claims Ageing; reports.test.js</t>
+          <t>Accounts &gt; Period End &gt; Year-End Close; period-end.test.js</t>
         </is>
       </c>
       <c r="K120" s="6" t="inlineStr"/>
       <c r="L120" s="7" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="9" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B121" s="9" t="inlineStr">
+      <c r="A121" s="7" t="inlineStr">
+        <is>
+          <t>12.08</t>
+        </is>
+      </c>
+      <c r="B121" s="6" t="inlineStr">
         <is>
           <t>Accounting, general ledger, period end and audit</t>
         </is>
       </c>
-      <c r="C121" s="9" t="inlineStr">
-        <is>
-          <t>L1 subtotal: fit 96.3%</t>
-        </is>
-      </c>
-      <c r="D121" s="9" t="inlineStr"/>
-      <c r="E121" s="9" t="inlineStr"/>
-      <c r="F121" s="10" t="n">
-        <v>27</v>
-      </c>
-      <c r="G121" s="9" t="inlineStr"/>
-      <c r="H121" s="10" t="n">
-        <v>52</v>
-      </c>
-      <c r="I121" s="10" t="n">
-        <v>54</v>
-      </c>
-      <c r="J121" s="9" t="inlineStr"/>
-      <c r="K121" s="9" t="inlineStr"/>
-      <c r="L121" s="9" t="inlineStr"/>
+      <c r="C121" s="6" t="inlineStr">
+        <is>
+          <t>Financial statements: income statement, balance sheet, trial balance</t>
+        </is>
+      </c>
+      <c r="D121" s="7" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E121" s="7" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+      <c r="F121" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G121" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H121" s="7">
+        <f>F121*G121</f>
+        <v/>
+      </c>
+      <c r="I121" s="7">
+        <f>2*F121</f>
+        <v/>
+      </c>
+      <c r="J121" s="6" t="inlineStr">
+        <is>
+          <t>Accounts &gt; Period End &gt; Financial Statements; reports.test.js</t>
+        </is>
+      </c>
+      <c r="K121" s="6" t="inlineStr"/>
+      <c r="L121" s="7" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="7" t="inlineStr">
         <is>
-          <t>12.01</t>
+          <t>12.09</t>
         </is>
       </c>
       <c r="B122" s="6" t="inlineStr">
@@ -7310,7 +7318,7 @@
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>Double-entry general ledger fed by posting rules</t>
+          <t>Multi-currency transactions and FX revaluation</t>
         </is>
       </c>
       <c r="D122" s="7" t="inlineStr">
@@ -7324,7 +7332,7 @@
         </is>
       </c>
       <c r="F122" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G122" s="12" t="n">
         <v>2</v>
@@ -7339,7 +7347,7 @@
       </c>
       <c r="J122" s="6" t="inlineStr">
         <is>
-          <t>Master &gt; Finance &gt; Posting Rules, Account Determination; posting-rules.test.js; accounting-flow.test.js</t>
+          <t>Master &gt; Finance &gt; Currency, Exchange Rate (migration 0235); period-end.test.js</t>
         </is>
       </c>
       <c r="K122" s="6" t="inlineStr"/>
@@ -7348,7 +7356,7 @@
     <row r="123">
       <c r="A123" s="7" t="inlineStr">
         <is>
-          <t>12.02</t>
+          <t>12.10</t>
         </is>
       </c>
       <c r="B123" s="6" t="inlineStr">
@@ -7358,7 +7366,7 @@
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>Philippine broker chart of accounts with premium trust account</t>
+          <t>Supplier invoices, input VAT, fixed assets and depreciation</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
@@ -7374,8 +7382,8 @@
       <c r="F123" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G123" s="12" t="n">
-        <v>2</v>
+      <c r="G123" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="H123" s="7">
         <f>F123*G123</f>
@@ -7387,74 +7395,62 @@
       </c>
       <c r="J123" s="6" t="inlineStr">
         <is>
-          <t>Main Account, Sub Account masters; chart-of-accounts.test.js</t>
-        </is>
-      </c>
-      <c r="K123" s="6" t="inlineStr"/>
+          <t>Supplier payment vouchers with withholding; input VAT tax code</t>
+        </is>
+      </c>
+      <c r="K123" s="6" t="inlineStr">
+        <is>
+          <t>No supplier invoice register (accounts payable sub-ledger) or fixed asset register.</t>
+        </is>
+      </c>
       <c r="L123" s="7" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="7" t="inlineStr">
-        <is>
-          <t>12.03</t>
-        </is>
-      </c>
-      <c r="B124" s="6" t="inlineStr">
-        <is>
-          <t>Accounting, general ledger, period end and audit</t>
-        </is>
-      </c>
-      <c r="C124" s="6" t="inlineStr">
-        <is>
-          <t>Journal, correction and reversal vouchers with approval</t>
-        </is>
-      </c>
-      <c r="D124" s="7" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="E124" s="7" t="inlineStr">
-        <is>
-          <t>Ops</t>
-        </is>
-      </c>
-      <c r="F124" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G124" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="H124" s="7">
-        <f>F124*G124</f>
-        <v/>
-      </c>
-      <c r="I124" s="7">
-        <f>2*F124</f>
-        <v/>
-      </c>
-      <c r="J124" s="6" t="inlineStr">
-        <is>
-          <t>Accounts &gt; Journal Voucher, Correction JV, Reversal JV; journal.test.js</t>
-        </is>
-      </c>
-      <c r="K124" s="6" t="inlineStr"/>
-      <c r="L124" s="7" t="inlineStr"/>
+      <c r="A124" s="9" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B124" s="9" t="inlineStr">
+        <is>
+          <t>Taxes and BIR compliance</t>
+        </is>
+      </c>
+      <c r="C124" s="9" t="inlineStr">
+        <is>
+          <t>L1 subtotal: fit 74.2%</t>
+        </is>
+      </c>
+      <c r="D124" s="9" t="inlineStr"/>
+      <c r="E124" s="9" t="inlineStr"/>
+      <c r="F124" s="10" t="n">
+        <v>31</v>
+      </c>
+      <c r="G124" s="9" t="inlineStr"/>
+      <c r="H124" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="I124" s="10" t="n">
+        <v>62</v>
+      </c>
+      <c r="J124" s="9" t="inlineStr"/>
+      <c r="K124" s="9" t="inlineStr"/>
+      <c r="L124" s="9" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="7" t="inlineStr">
         <is>
-          <t>12.04</t>
+          <t>13.01</t>
         </is>
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>Accounting, general ledger, period end and audit</t>
+          <t>Taxes and BIR compliance</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>Payment vouchers, cheques and petty cash</t>
+          <t>Premium taxes: DST (NIRC s.184), VAT 12% or premium tax per product regime, LGT by LGU, FST 2%</t>
         </is>
       </c>
       <c r="D125" s="7" t="inlineStr">
@@ -7464,7 +7460,7 @@
       </c>
       <c r="E125" s="7" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>BIR</t>
         </is>
       </c>
       <c r="F125" s="7" t="n">
@@ -7483,26 +7479,30 @@
       </c>
       <c r="J125" s="6" t="inlineStr">
         <is>
-          <t>Accounts &gt; Disbursement, Petty Cash; disbursements.test.js</t>
-        </is>
-      </c>
-      <c r="K125" s="6" t="inlineStr"/>
+          <t>Master &gt; Finance &gt; Premium Taxes &amp; LGU Rates; Product master premium_tax_regime; premium-charges.test.js</t>
+        </is>
+      </c>
+      <c r="K125" s="6" t="inlineStr">
+        <is>
+          <t>DST rule delivered as 12.5% of premium; the per-unit option (PHP 0.50 per PHP 4.00, fraction rounded up) is available.</t>
+        </is>
+      </c>
       <c r="L125" s="7" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="7" t="inlineStr">
         <is>
-          <t>12.05</t>
+          <t>13.03</t>
         </is>
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>Accounting, general ledger, period end and audit</t>
+          <t>Taxes and BIR compliance</t>
         </is>
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>Bank statement import, auto-match and reconciliation statement</t>
+          <t>Output VAT on commission and VAT Summary (2550Q working paper)</t>
         </is>
       </c>
       <c r="D126" s="7" t="inlineStr">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="E126" s="7" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>BIR</t>
         </is>
       </c>
       <c r="F126" s="7" t="n">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="J126" s="6" t="inlineStr">
         <is>
-          <t>Accounts &gt; Bank Reconciliation; bank-reconciliation.test.js</t>
+          <t>Accounts &gt; Tax &gt; VAT Summary; commission-taxes.test.js</t>
         </is>
       </c>
       <c r="K126" s="6" t="inlineStr"/>
@@ -7540,17 +7540,17 @@
     <row r="127">
       <c r="A127" s="7" t="inlineStr">
         <is>
-          <t>12.06</t>
+          <t>13.04</t>
         </is>
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>Accounting, general ledger, period end and audit</t>
+          <t>Taxes and BIR compliance</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>Month-end close with checklist, accruals and recurring journals</t>
+          <t>Percentage tax for a non-VAT broker or agent (2551Q)</t>
         </is>
       </c>
       <c r="D127" s="7" t="inlineStr">
@@ -7560,14 +7560,14 @@
       </c>
       <c r="E127" s="7" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>BIR</t>
         </is>
       </c>
       <c r="F127" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G127" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="G127" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="H127" s="7">
         <f>F127*G127</f>
@@ -7579,26 +7579,30 @@
       </c>
       <c r="J127" s="6" t="inlineStr">
         <is>
-          <t>Accounts &gt; Period End &gt; Month-End Close; period-end.test.js; period-end-calendar.test.js</t>
-        </is>
-      </c>
-      <c r="K127" s="6" t="inlineStr"/>
+          <t>direct_bill.broker_vat_registered switch</t>
+        </is>
+      </c>
+      <c r="K127" s="6" t="inlineStr">
+        <is>
+          <t>No percentage tax working paper.</t>
+        </is>
+      </c>
       <c r="L127" s="7" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="7" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>13.05</t>
         </is>
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>Accounting, general ledger, period end and audit</t>
+          <t>Taxes and BIR compliance</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>Year-end close and opening balances</t>
+          <t>EWT on payments and BIR Form 2307 issued</t>
         </is>
       </c>
       <c r="D128" s="7" t="inlineStr">
@@ -7608,11 +7612,11 @@
       </c>
       <c r="E128" s="7" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>BIR</t>
         </is>
       </c>
       <c r="F128" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G128" s="12" t="n">
         <v>2</v>
@@ -7627,7 +7631,7 @@
       </c>
       <c r="J128" s="6" t="inlineStr">
         <is>
-          <t>Accounts &gt; Period End &gt; Year-End Close; period-end.test.js</t>
+          <t>Accounts &gt; Tax &gt; BIR Form 2307 (Issued by us); commission-taxes.test.js</t>
         </is>
       </c>
       <c r="K128" s="6" t="inlineStr"/>
@@ -7636,17 +7640,17 @@
     <row r="129">
       <c r="A129" s="7" t="inlineStr">
         <is>
-          <t>12.08</t>
+          <t>13.06</t>
         </is>
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>Accounting, general ledger, period end and audit</t>
+          <t>Taxes and BIR compliance</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>Financial statements: income statement, balance sheet, trial balance</t>
+          <t>CWT withheld by insurers, BIR Form 2307 received and SAWT</t>
         </is>
       </c>
       <c r="D129" s="7" t="inlineStr">
@@ -7656,7 +7660,7 @@
       </c>
       <c r="E129" s="7" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>BIR</t>
         </is>
       </c>
       <c r="F129" s="7" t="n">
@@ -7675,7 +7679,7 @@
       </c>
       <c r="J129" s="6" t="inlineStr">
         <is>
-          <t>Accounts &gt; Period End &gt; Financial Statements; reports.test.js</t>
+          <t>BIR Form 2307 (Received); SAWT; direct-bill.test.js</t>
         </is>
       </c>
       <c r="K129" s="6" t="inlineStr"/>
@@ -7684,17 +7688,17 @@
     <row r="130">
       <c r="A130" s="7" t="inlineStr">
         <is>
-          <t>12.09</t>
+          <t>13.07</t>
         </is>
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>Accounting, general ledger, period end and audit</t>
+          <t>Taxes and BIR compliance</t>
         </is>
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
-          <t>Multi-currency transactions and FX revaluation</t>
+          <t>Monthly and quarterly EWT returns (0619-E, 1601-EQ) with QAP</t>
         </is>
       </c>
       <c r="D130" s="7" t="inlineStr">
@@ -7704,14 +7708,14 @@
       </c>
       <c r="E130" s="7" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>BIR</t>
         </is>
       </c>
       <c r="F130" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G130" s="11" t="n">
         <v>1</v>
-      </c>
-      <c r="G130" s="12" t="n">
-        <v>2</v>
       </c>
       <c r="H130" s="7">
         <f>F130*G130</f>
@@ -7723,26 +7727,30 @@
       </c>
       <c r="J130" s="6" t="inlineStr">
         <is>
-          <t>Master &gt; Finance &gt; Currency, Exchange Rate (migration 0235); period-end.test.js</t>
-        </is>
-      </c>
-      <c r="K130" s="6" t="inlineStr"/>
+          <t>Accounts &gt; Tax &gt; QAP</t>
+        </is>
+      </c>
+      <c r="K130" s="6" t="inlineStr">
+        <is>
+          <t>QAP is delivered; the return figures per ATC are not laid out as the 0619-E / 1601-EQ forms.</t>
+        </is>
+      </c>
       <c r="L130" s="7" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="7" t="inlineStr">
         <is>
-          <t>12.10</t>
+          <t>13.08</t>
         </is>
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>Accounting, general ledger, period end and audit</t>
+          <t>Taxes and BIR compliance</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>Supplier invoices, input VAT, fixed assets and depreciation</t>
+          <t>Annual information return and alphalist (1604-E)</t>
         </is>
       </c>
       <c r="D131" s="7" t="inlineStr">
@@ -7752,7 +7760,7 @@
       </c>
       <c r="E131" s="7" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>BIR</t>
         </is>
       </c>
       <c r="F131" s="7" t="n">
@@ -7771,12 +7779,12 @@
       </c>
       <c r="J131" s="6" t="inlineStr">
         <is>
-          <t>Supplier payment vouchers with withholding; input VAT tax code</t>
+          <t>QAP run for a full year range (generic date criteria)</t>
         </is>
       </c>
       <c r="K131" s="6" t="inlineStr">
         <is>
-          <t>No supplier invoice register (accounts payable sub-ledger) or fixed asset register.</t>
+          <t>No 1604-E alphalist layout.</t>
         </is>
       </c>
       <c r="L131" s="7" t="inlineStr"/>
@@ -7784,17 +7792,17 @@
     <row r="132">
       <c r="A132" s="7" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>13.09</t>
         </is>
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>Accounting, general ledger, period end and audit</t>
+          <t>Taxes and BIR compliance</t>
         </is>
       </c>
       <c r="C132" s="6" t="inlineStr">
         <is>
-          <t>Audit support: GL detail, journal register, source document trace</t>
+          <t>SLSP sales and purchases</t>
         </is>
       </c>
       <c r="D132" s="7" t="inlineStr">
@@ -7804,7 +7812,7 @@
       </c>
       <c r="E132" s="7" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>BIR</t>
         </is>
       </c>
       <c r="F132" s="7" t="n">
@@ -7823,48 +7831,68 @@
       </c>
       <c r="J132" s="6" t="inlineStr">
         <is>
-          <t>General Ledger Detail, Journal Register; each journal points to its source; journal.test.js</t>
+          <t>Accounts &gt; Tax &gt; SLSP Sales, SLSP Purchases (BIR column order)</t>
         </is>
       </c>
       <c r="K132" s="6" t="inlineStr"/>
       <c r="L132" s="7" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" s="9" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B133" s="9" t="inlineStr">
+      <c r="A133" s="7" t="inlineStr">
+        <is>
+          <t>13.10</t>
+        </is>
+      </c>
+      <c r="B133" s="6" t="inlineStr">
         <is>
           <t>Taxes and BIR compliance</t>
         </is>
       </c>
-      <c r="C133" s="9" t="inlineStr">
-        <is>
-          <t>L1 subtotal: fit 75.8%</t>
-        </is>
-      </c>
-      <c r="D133" s="9" t="inlineStr"/>
-      <c r="E133" s="9" t="inlineStr"/>
-      <c r="F133" s="10" t="n">
-        <v>33</v>
-      </c>
-      <c r="G133" s="9" t="inlineStr"/>
-      <c r="H133" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="I133" s="10" t="n">
-        <v>66</v>
-      </c>
-      <c r="J133" s="9" t="inlineStr"/>
-      <c r="K133" s="9" t="inlineStr"/>
-      <c r="L133" s="9" t="inlineStr"/>
+      <c r="C133" s="6" t="inlineStr">
+        <is>
+          <t>Invoices under the EOPT Act and RR 7-2024 (invoice as primary document, required fields)</t>
+        </is>
+      </c>
+      <c r="D133" s="7" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E133" s="7" t="inlineStr">
+        <is>
+          <t>BIR</t>
+        </is>
+      </c>
+      <c r="F133" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G133" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H133" s="7">
+        <f>F133*G133</f>
+        <v/>
+      </c>
+      <c r="I133" s="7">
+        <f>2*F133</f>
+        <v/>
+      </c>
+      <c r="J133" s="6" t="inlineStr">
+        <is>
+          <t>INV, OR and DN series on letterhead with TIN; compliance matrix (Invoices and receipts)</t>
+        </is>
+      </c>
+      <c r="K133" s="6" t="inlineStr">
+        <is>
+          <t>Which document is the registered invoice and its printed fields are not fixed in the product; layout changes are outside OOTB.</t>
+        </is>
+      </c>
+      <c r="L133" s="7" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="B134" s="6" t="inlineStr">
@@ -7874,7 +7902,7 @@
       </c>
       <c r="C134" s="6" t="inlineStr">
         <is>
-          <t>Premium taxes: DST (NIRC s.184), VAT 12%, LGT by LGU, FST 2%</t>
+          <t>Computerized accounting system registration support (books, outputs, controls)</t>
         </is>
       </c>
       <c r="D134" s="7" t="inlineStr">
@@ -7890,8 +7918,8 @@
       <c r="F134" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G134" s="12" t="n">
-        <v>2</v>
+      <c r="G134" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="H134" s="7">
         <f>F134*G134</f>
@@ -7903,12 +7931,12 @@
       </c>
       <c r="J134" s="6" t="inlineStr">
         <is>
-          <t>Master &gt; Finance &gt; Premium Taxes &amp; LGU Rates; premium-charges.test.js</t>
+          <t>Journals, ledgers, audit trail, period locks, number series; documentation pack</t>
         </is>
       </c>
       <c r="K134" s="6" t="inlineStr">
         <is>
-          <t>DST rule delivered as 12.5% of premium; the per-unit option (PHP 0.50 per PHP 4.00, fraction rounded up) is available.</t>
+          <t>No loose-leaf books print set or CAS output pack; registration is with the broker.</t>
         </is>
       </c>
       <c r="L134" s="7" t="inlineStr"/>
@@ -7916,7 +7944,7 @@
     <row r="135">
       <c r="A135" s="7" t="inlineStr">
         <is>
-          <t>13.02</t>
+          <t>13.12</t>
         </is>
       </c>
       <c r="B135" s="6" t="inlineStr">
@@ -7926,7 +7954,7 @@
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>Premium tax regime per product (VAT or premium tax)</t>
+          <t>Electronic invoicing and sales data transmission to BIR (EIS)</t>
         </is>
       </c>
       <c r="D135" s="7" t="inlineStr">
@@ -7940,10 +7968,10 @@
         </is>
       </c>
       <c r="F135" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G135" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="G135" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="H135" s="7">
         <f>F135*G135</f>
@@ -7955,16 +7983,20 @@
       </c>
       <c r="J135" s="6" t="inlineStr">
         <is>
-          <t>Product master premium_tax_regime; premium-charges.test.js</t>
-        </is>
-      </c>
-      <c r="K135" s="6" t="inlineStr"/>
+          <t>None found</t>
+        </is>
+      </c>
+      <c r="K135" s="6" t="inlineStr">
+        <is>
+          <t>No EIS connector (not yet mandatory for most brokers; to verify).</t>
+        </is>
+      </c>
       <c r="L135" s="7" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="7" t="inlineStr">
         <is>
-          <t>13.03</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="B136" s="6" t="inlineStr">
@@ -7974,7 +8006,7 @@
       </c>
       <c r="C136" s="6" t="inlineStr">
         <is>
-          <t>Output VAT on commission and VAT Summary (2550Q working paper)</t>
+          <t>BIR validation files (DAT) for alphalists and SLSP</t>
         </is>
       </c>
       <c r="D136" s="7" t="inlineStr">
@@ -7988,10 +8020,10 @@
         </is>
       </c>
       <c r="F136" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G136" s="12" t="n">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="G136" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="H136" s="7">
         <f>F136*G136</f>
@@ -8003,16 +8035,20 @@
       </c>
       <c r="J136" s="6" t="inlineStr">
         <is>
-          <t>Accounts &gt; Tax &gt; VAT Summary; commission-taxes.test.js</t>
-        </is>
-      </c>
-      <c r="K136" s="6" t="inlineStr"/>
+          <t>SAWT, QAP, SLSP as CSV or Excel in BIR column order</t>
+        </is>
+      </c>
+      <c r="K136" s="6" t="inlineStr">
+        <is>
+          <t>Files are re-keyed or imported into the BIR tools; no DAT file.</t>
+        </is>
+      </c>
       <c r="L136" s="7" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="7" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="B137" s="6" t="inlineStr">
@@ -8022,7 +8058,7 @@
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>Percentage tax for a non-VAT broker or agent (2551Q)</t>
+          <t>Tax codes with ATC, rates, GL account and effective dates</t>
         </is>
       </c>
       <c r="D137" s="7" t="inlineStr">
@@ -8036,10 +8072,10 @@
         </is>
       </c>
       <c r="F137" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G137" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="G137" s="12" t="n">
+        <v>2</v>
       </c>
       <c r="H137" s="7">
         <f>F137*G137</f>
@@ -8051,78 +8087,58 @@
       </c>
       <c r="J137" s="6" t="inlineStr">
         <is>
-          <t>direct_bill.broker_vat_registered switch</t>
-        </is>
-      </c>
-      <c r="K137" s="6" t="inlineStr">
-        <is>
-          <t>No percentage tax working paper.</t>
-        </is>
-      </c>
+          <t>Master &gt; Finance &gt; Taxation; commission-taxes.test.js</t>
+        </is>
+      </c>
+      <c r="K137" s="6" t="inlineStr"/>
       <c r="L137" s="7" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="7" t="inlineStr">
-        <is>
-          <t>13.05</t>
-        </is>
-      </c>
-      <c r="B138" s="6" t="inlineStr">
-        <is>
-          <t>Taxes and BIR compliance</t>
-        </is>
-      </c>
-      <c r="C138" s="6" t="inlineStr">
-        <is>
-          <t>EWT on payments and BIR Form 2307 issued</t>
-        </is>
-      </c>
-      <c r="D138" s="7" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="E138" s="7" t="inlineStr">
-        <is>
-          <t>BIR</t>
-        </is>
-      </c>
-      <c r="F138" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G138" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="H138" s="7">
-        <f>F138*G138</f>
-        <v/>
-      </c>
-      <c r="I138" s="7">
-        <f>2*F138</f>
-        <v/>
-      </c>
-      <c r="J138" s="6" t="inlineStr">
-        <is>
-          <t>Accounts &gt; Tax &gt; BIR Form 2307 (Issued by us); commission-taxes.test.js</t>
-        </is>
-      </c>
-      <c r="K138" s="6" t="inlineStr"/>
-      <c r="L138" s="7" t="inlineStr"/>
+      <c r="A138" s="9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B138" s="9" t="inlineStr">
+        <is>
+          <t>Insurance Commission and Data Privacy compliance</t>
+        </is>
+      </c>
+      <c r="C138" s="9" t="inlineStr">
+        <is>
+          <t>L1 subtotal: fit 59.3%</t>
+        </is>
+      </c>
+      <c r="D138" s="9" t="inlineStr"/>
+      <c r="E138" s="9" t="inlineStr"/>
+      <c r="F138" s="10" t="n">
+        <v>27</v>
+      </c>
+      <c r="G138" s="9" t="inlineStr"/>
+      <c r="H138" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="I138" s="10" t="n">
+        <v>54</v>
+      </c>
+      <c r="J138" s="9" t="inlineStr"/>
+      <c r="K138" s="9" t="inlineStr"/>
+      <c r="L138" s="9" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="7" t="inlineStr">
         <is>
-          <t>13.06</t>
+          <t>14.02</t>
         </is>
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>Taxes and BIR compliance</t>
+          <t>Insurance Commission and Data Privacy compliance</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>CWT withheld by insurers, BIR Form 2307 received and SAWT</t>
+          <t>Licence renewal tracking of the firm and licensed individuals</t>
         </is>
       </c>
       <c r="D139" s="7" t="inlineStr">
@@ -8132,14 +8148,14 @@
       </c>
       <c r="E139" s="7" t="inlineStr">
         <is>
-          <t>BIR</t>
+          <t>IC</t>
         </is>
       </c>
       <c r="F139" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G139" s="12" t="n">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="G139" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="H139" s="7">
         <f>F139*G139</f>
@@ -8151,26 +8167,30 @@
       </c>
       <c r="J139" s="6" t="inlineStr">
         <is>
-          <t>BIR Form 2307 (Received); SAWT; direct-bill.test.js</t>
-        </is>
-      </c>
-      <c r="K139" s="6" t="inlineStr"/>
+          <t>None found</t>
+        </is>
+      </c>
+      <c r="K139" s="6" t="inlineStr">
+        <is>
+          <t>No licence expiry calendar for the firm, its officers or solicitors.</t>
+        </is>
+      </c>
       <c r="L139" s="7" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="7" t="inlineStr">
         <is>
-          <t>13.07</t>
+          <t>14.03</t>
         </is>
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>Taxes and BIR compliance</t>
+          <t>Insurance Commission and Data Privacy compliance</t>
         </is>
       </c>
       <c r="C140" s="6" t="inlineStr">
         <is>
-          <t>Monthly and quarterly EWT returns (0619-E, 1601-EQ) with QAP</t>
+          <t>Fit and proper records of directors and officers</t>
         </is>
       </c>
       <c r="D140" s="7" t="inlineStr">
@@ -8180,14 +8200,14 @@
       </c>
       <c r="E140" s="7" t="inlineStr">
         <is>
-          <t>BIR</t>
+          <t>IC</t>
         </is>
       </c>
       <c r="F140" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G140" s="11" t="n">
         <v>1</v>
+      </c>
+      <c r="G140" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="H140" s="7">
         <f>F140*G140</f>
@@ -8199,12 +8219,12 @@
       </c>
       <c r="J140" s="6" t="inlineStr">
         <is>
-          <t>Accounts &gt; Tax &gt; QAP</t>
+          <t>None found</t>
         </is>
       </c>
       <c r="K140" s="6" t="inlineStr">
         <is>
-          <t>QAP is delivered; the return figures per ATC are not laid out as the 0619-E / 1601-EQ forms.</t>
+          <t>Kept outside the system.</t>
         </is>
       </c>
       <c r="L140" s="7" t="inlineStr"/>
@@ -8212,17 +8232,17 @@
     <row r="141">
       <c r="A141" s="7" t="inlineStr">
         <is>
-          <t>13.08</t>
+          <t>14.04</t>
         </is>
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>Taxes and BIR compliance</t>
+          <t>Insurance Commission and Data Privacy compliance</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>Annual information return and alphalist (1604-E)</t>
+          <t>IC annual statement and financial reports in the IC format</t>
         </is>
       </c>
       <c r="D141" s="7" t="inlineStr">
@@ -8232,11 +8252,11 @@
       </c>
       <c r="E141" s="7" t="inlineStr">
         <is>
-          <t>BIR</t>
+          <t>IC</t>
         </is>
       </c>
       <c r="F141" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G141" s="11" t="n">
         <v>1</v>
@@ -8251,12 +8271,12 @@
       </c>
       <c r="J141" s="6" t="inlineStr">
         <is>
-          <t>QAP run for a full year range (generic date criteria)</t>
+          <t>Financial Statements; Trial Balance (figures only)</t>
         </is>
       </c>
       <c r="K141" s="6" t="inlineStr">
         <is>
-          <t>No 1604-E alphalist layout.</t>
+          <t>No IC-format report (checklist item 60).</t>
         </is>
       </c>
       <c r="L141" s="7" t="inlineStr"/>
@@ -8264,17 +8284,17 @@
     <row r="142">
       <c r="A142" s="7" t="inlineStr">
         <is>
-          <t>13.09</t>
+          <t>14.05</t>
         </is>
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>Taxes and BIR compliance</t>
+          <t>Insurance Commission and Data Privacy compliance</t>
         </is>
       </c>
       <c r="C142" s="6" t="inlineStr">
         <is>
-          <t>SLSP sales and purchases</t>
+          <t>IC production and business reports (premium placed by insurer and line)</t>
         </is>
       </c>
       <c r="D142" s="7" t="inlineStr">
@@ -8284,14 +8304,14 @@
       </c>
       <c r="E142" s="7" t="inlineStr">
         <is>
-          <t>BIR</t>
+          <t>IC</t>
         </is>
       </c>
       <c r="F142" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G142" s="12" t="n">
-        <v>2</v>
+      <c r="G142" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="H142" s="7">
         <f>F142*G142</f>
@@ -8303,26 +8323,30 @@
       </c>
       <c r="J142" s="6" t="inlineStr">
         <is>
-          <t>Accounts &gt; Tax &gt; SLSP Sales, SLSP Purchases (BIR column order)</t>
-        </is>
-      </c>
-      <c r="K142" s="6" t="inlineStr"/>
+          <t>Production Register; Premium by Product / Month / Insurer</t>
+        </is>
+      </c>
+      <c r="K142" s="6" t="inlineStr">
+        <is>
+          <t>Figures available; IC layout not produced.</t>
+        </is>
+      </c>
       <c r="L142" s="7" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="7" t="inlineStr">
         <is>
-          <t>13.10</t>
+          <t>14.06</t>
         </is>
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>Taxes and BIR compliance</t>
+          <t>Insurance Commission and Data Privacy compliance</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>Invoices under the EOPT Act and RR 7-2024 (invoice as primary document, required fields)</t>
+          <t>Records of business available for IC examination, licence number on documents</t>
         </is>
       </c>
       <c r="D143" s="7" t="inlineStr">
@@ -8332,14 +8356,14 @@
       </c>
       <c r="E143" s="7" t="inlineStr">
         <is>
-          <t>BIR</t>
+          <t>IC</t>
         </is>
       </c>
       <c r="F143" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G143" s="11" t="n">
-        <v>1</v>
+      <c r="G143" s="12" t="n">
+        <v>2</v>
       </c>
       <c r="H143" s="7">
         <f>F143*G143</f>
@@ -8351,30 +8375,26 @@
       </c>
       <c r="J143" s="6" t="inlineStr">
         <is>
-          <t>INV, OR and DN series on letterhead with TIN; compliance matrix (Invoices and receipts)</t>
-        </is>
-      </c>
-      <c r="K143" s="6" t="inlineStr">
-        <is>
-          <t>Which document is the registered invoice and its printed fields are not fixed in the product; layout changes are outside OOTB.</t>
-        </is>
-      </c>
+          <t>Numbered placement trail RFQ to policy to receipt; reports; audit log; Company master IC licence number on letterhead (printing.test.js)</t>
+        </is>
+      </c>
+      <c r="K143" s="6" t="inlineStr"/>
       <c r="L143" s="7" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="7" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>14.07</t>
         </is>
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>Taxes and BIR compliance</t>
+          <t>Insurance Commission and Data Privacy compliance</t>
         </is>
       </c>
       <c r="C144" s="6" t="inlineStr">
         <is>
-          <t>Computerized accounting system registration support (books, outputs, controls)</t>
+          <t>Premium held in trust for insurers, apart from own funds</t>
         </is>
       </c>
       <c r="D144" s="7" t="inlineStr">
@@ -8384,14 +8404,14 @@
       </c>
       <c r="E144" s="7" t="inlineStr">
         <is>
-          <t>BIR</t>
+          <t>IC</t>
         </is>
       </c>
       <c r="F144" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G144" s="11" t="n">
-        <v>1</v>
+      <c r="G144" s="12" t="n">
+        <v>2</v>
       </c>
       <c r="H144" s="7">
         <f>F144*G144</f>
@@ -8403,30 +8423,26 @@
       </c>
       <c r="J144" s="6" t="inlineStr">
         <is>
-          <t>Journals, ledgers, audit trail, period locks, number series; documentation pack</t>
-        </is>
-      </c>
-      <c r="K144" s="6" t="inlineStr">
-        <is>
-          <t>No loose-leaf books print set or CAS output pack; registration is with the broker.</t>
-        </is>
-      </c>
+          <t>Premiums Payable to Insurers per insurer; Premium Trust Account; payment-segregation.test.js</t>
+        </is>
+      </c>
+      <c r="K144" s="6" t="inlineStr"/>
       <c r="L144" s="7" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="7" t="inlineStr">
         <is>
-          <t>13.12</t>
+          <t>14.08</t>
         </is>
       </c>
       <c r="B145" s="6" t="inlineStr">
         <is>
-          <t>Taxes and BIR compliance</t>
+          <t>Insurance Commission and Data Privacy compliance</t>
         </is>
       </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
-          <t>Electronic invoicing and sales data transmission to BIR (EIS)</t>
+          <t>Complaints handling and financial consumer protection (RA 11765)</t>
         </is>
       </c>
       <c r="D145" s="7" t="inlineStr">
@@ -8436,11 +8452,11 @@
       </c>
       <c r="E145" s="7" t="inlineStr">
         <is>
-          <t>BIR</t>
+          <t>IC</t>
         </is>
       </c>
       <c r="F145" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G145" s="13" t="n">
         <v>0</v>
@@ -8455,12 +8471,12 @@
       </c>
       <c r="J145" s="6" t="inlineStr">
         <is>
-          <t>None found</t>
+          <t>None found (grep complaint returns nothing)</t>
         </is>
       </c>
       <c r="K145" s="6" t="inlineStr">
         <is>
-          <t>No EIS connector (not yet mandatory for most brokers; to verify).</t>
+          <t>No complaints register or response time tracking.</t>
         </is>
       </c>
       <c r="L145" s="7" t="inlineStr"/>
@@ -8468,17 +8484,17 @@
     <row r="146">
       <c r="A146" s="7" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>14.09</t>
         </is>
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>Taxes and BIR compliance</t>
+          <t>Insurance Commission and Data Privacy compliance</t>
         </is>
       </c>
       <c r="C146" s="6" t="inlineStr">
         <is>
-          <t>BIR validation files (DAT) for alphalists and SLSP</t>
+          <t>Data subject requests, export and anonymisation</t>
         </is>
       </c>
       <c r="D146" s="7" t="inlineStr">
@@ -8488,14 +8504,14 @@
       </c>
       <c r="E146" s="7" t="inlineStr">
         <is>
-          <t>BIR</t>
+          <t>NPC</t>
         </is>
       </c>
       <c r="F146" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G146" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="G146" s="12" t="n">
+        <v>2</v>
       </c>
       <c r="H146" s="7">
         <f>F146*G146</f>
@@ -8507,30 +8523,26 @@
       </c>
       <c r="J146" s="6" t="inlineStr">
         <is>
-          <t>SAWT, QAP, SLSP as CSV or Excel in BIR column order</t>
-        </is>
-      </c>
-      <c r="K146" s="6" t="inlineStr">
-        <is>
-          <t>Files are re-keyed or imported into the BIR tools; no DAT file.</t>
-        </is>
-      </c>
+          <t>Master &gt; Data Privacy &gt; Data Subject Requests; privacy.test.js</t>
+        </is>
+      </c>
+      <c r="K146" s="6" t="inlineStr"/>
       <c r="L146" s="7" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="7" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>14.10</t>
         </is>
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>Taxes and BIR compliance</t>
+          <t>Insurance Commission and Data Privacy compliance</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>Tax codes with ATC, rates, GL account and effective dates</t>
+          <t>Retention and disposal of personal data</t>
         </is>
       </c>
       <c r="D147" s="7" t="inlineStr">
@@ -8540,7 +8552,7 @@
       </c>
       <c r="E147" s="7" t="inlineStr">
         <is>
-          <t>BIR</t>
+          <t>NPC</t>
         </is>
       </c>
       <c r="F147" s="7" t="n">
@@ -8559,48 +8571,68 @@
       </c>
       <c r="J147" s="6" t="inlineStr">
         <is>
-          <t>Master &gt; Finance &gt; Taxation; commission-taxes.test.js</t>
+          <t>privacy.retention_years; housekeeping.* settings; privacy.test.js</t>
         </is>
       </c>
       <c r="K147" s="6" t="inlineStr"/>
       <c r="L147" s="7" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" s="9" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="B148" s="9" t="inlineStr">
+      <c r="A148" s="7" t="inlineStr">
+        <is>
+          <t>14.11</t>
+        </is>
+      </c>
+      <c r="B148" s="6" t="inlineStr">
         <is>
           <t>Insurance Commission and Data Privacy compliance</t>
         </is>
       </c>
-      <c r="C148" s="9" t="inlineStr">
-        <is>
-          <t>L1 subtotal: fit 60.7%</t>
-        </is>
-      </c>
-      <c r="D148" s="9" t="inlineStr"/>
-      <c r="E148" s="9" t="inlineStr"/>
-      <c r="F148" s="10" t="n">
-        <v>28</v>
-      </c>
-      <c r="G148" s="9" t="inlineStr"/>
-      <c r="H148" s="10" t="n">
-        <v>34</v>
-      </c>
-      <c r="I148" s="10" t="n">
-        <v>56</v>
-      </c>
-      <c r="J148" s="9" t="inlineStr"/>
-      <c r="K148" s="9" t="inlineStr"/>
-      <c r="L148" s="9" t="inlineStr"/>
+      <c r="C148" s="6" t="inlineStr">
+        <is>
+          <t>Breach detection support and breach register</t>
+        </is>
+      </c>
+      <c r="D148" s="7" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E148" s="7" t="inlineStr">
+        <is>
+          <t>NPC</t>
+        </is>
+      </c>
+      <c r="F148" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G148" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H148" s="7">
+        <f>F148*G148</f>
+        <v/>
+      </c>
+      <c r="I148" s="7">
+        <f>2*F148</f>
+        <v/>
+      </c>
+      <c r="J148" s="6" t="inlineStr">
+        <is>
+          <t>Login history, audit log, failed sign-in alarms</t>
+        </is>
+      </c>
+      <c r="K148" s="6" t="inlineStr">
+        <is>
+          <t>No breach register or 72-hour notification tracker.</t>
+        </is>
+      </c>
+      <c r="L148" s="7" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="7" t="inlineStr">
         <is>
-          <t>14.01</t>
+          <t>14.12</t>
         </is>
       </c>
       <c r="B149" s="6" t="inlineStr">
@@ -8610,7 +8642,7 @@
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
-          <t>IC licence number on company master and documents</t>
+          <t>Masking of personal data on screens and exports by role</t>
         </is>
       </c>
       <c r="D149" s="7" t="inlineStr">
@@ -8620,14 +8652,14 @@
       </c>
       <c r="E149" s="7" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>NPC</t>
         </is>
       </c>
       <c r="F149" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G149" s="12" t="n">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="G149" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="H149" s="7">
         <f>F149*G149</f>
@@ -8639,16 +8671,24 @@
       </c>
       <c r="J149" s="6" t="inlineStr">
         <is>
-          <t>Company master (IC licence number); printing.test.js</t>
-        </is>
-      </c>
-      <c r="K149" s="6" t="inlineStr"/>
-      <c r="L149" s="7" t="inlineStr"/>
+          <t>Not delivered (in development)</t>
+        </is>
+      </c>
+      <c r="K149" s="6" t="inlineStr">
+        <is>
+          <t>Personal identifiers shown in full to every role with read access.</t>
+        </is>
+      </c>
+      <c r="L149" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="7" t="inlineStr">
         <is>
-          <t>14.02</t>
+          <t>14.13</t>
         </is>
       </c>
       <c r="B150" s="6" t="inlineStr">
@@ -8658,7 +8698,7 @@
       </c>
       <c r="C150" s="6" t="inlineStr">
         <is>
-          <t>Licence renewal tracking of the firm and licensed individuals</t>
+          <t>Encryption of personal identifiers</t>
         </is>
       </c>
       <c r="D150" s="7" t="inlineStr">
@@ -8668,14 +8708,14 @@
       </c>
       <c r="E150" s="7" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>NPC</t>
         </is>
       </c>
       <c r="F150" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G150" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G150" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="H150" s="7">
         <f>F150*G150</f>
@@ -8687,12 +8727,12 @@
       </c>
       <c r="J150" s="6" t="inlineStr">
         <is>
-          <t>None found</t>
+          <t>Storage encryption (hosting); two-step secrets AES-256-GCM; BV-DEF-003 open</t>
         </is>
       </c>
       <c r="K150" s="6" t="inlineStr">
         <is>
-          <t>No licence expiry calendar for the firm, its officers or solicitors.</t>
+          <t>No field-level encryption of IDs and TIN.</t>
         </is>
       </c>
       <c r="L150" s="7" t="inlineStr"/>
@@ -8700,7 +8740,7 @@
     <row r="151">
       <c r="A151" s="7" t="inlineStr">
         <is>
-          <t>14.03</t>
+          <t>14.14</t>
         </is>
       </c>
       <c r="B151" s="6" t="inlineStr">
@@ -8710,7 +8750,7 @@
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>Fit and proper records of directors and officers</t>
+          <t>Data residency in the Philippines when required</t>
         </is>
       </c>
       <c r="D151" s="7" t="inlineStr">
@@ -8720,14 +8760,14 @@
       </c>
       <c r="E151" s="7" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>NPC</t>
         </is>
       </c>
       <c r="F151" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G151" s="13" t="n">
-        <v>0</v>
+      <c r="G151" s="12" t="n">
+        <v>2</v>
       </c>
       <c r="H151" s="7">
         <f>F151*G151</f>
@@ -8739,82 +8779,58 @@
       </c>
       <c r="J151" s="6" t="inlineStr">
         <is>
-          <t>None found</t>
-        </is>
-      </c>
-      <c r="K151" s="6" t="inlineStr">
-        <is>
-          <t>Kept outside the system.</t>
-        </is>
-      </c>
+          <t>Hosting options: local partner or on-premise (architecture document)</t>
+        </is>
+      </c>
+      <c r="K151" s="6" t="inlineStr"/>
       <c r="L151" s="7" t="inlineStr"/>
     </row>
     <row r="152">
-      <c r="A152" s="7" t="inlineStr">
-        <is>
-          <t>14.04</t>
-        </is>
-      </c>
-      <c r="B152" s="6" t="inlineStr">
-        <is>
-          <t>Insurance Commission and Data Privacy compliance</t>
-        </is>
-      </c>
-      <c r="C152" s="6" t="inlineStr">
-        <is>
-          <t>IC annual statement and financial reports in the IC format</t>
-        </is>
-      </c>
-      <c r="D152" s="7" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="E152" s="7" t="inlineStr">
-        <is>
-          <t>IC</t>
-        </is>
-      </c>
-      <c r="F152" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G152" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H152" s="7">
-        <f>F152*G152</f>
-        <v/>
-      </c>
-      <c r="I152" s="7">
-        <f>2*F152</f>
-        <v/>
-      </c>
-      <c r="J152" s="6" t="inlineStr">
-        <is>
-          <t>Financial Statements; Trial Balance (figures only)</t>
-        </is>
-      </c>
-      <c r="K152" s="6" t="inlineStr">
-        <is>
-          <t>No IC-format report (checklist item 60).</t>
-        </is>
-      </c>
-      <c r="L152" s="7" t="inlineStr"/>
+      <c r="A152" s="9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B152" s="9" t="inlineStr">
+        <is>
+          <t>Reporting, administration, security and go-live</t>
+        </is>
+      </c>
+      <c r="C152" s="9" t="inlineStr">
+        <is>
+          <t>L1 subtotal: fit 83.9%</t>
+        </is>
+      </c>
+      <c r="D152" s="9" t="inlineStr"/>
+      <c r="E152" s="9" t="inlineStr"/>
+      <c r="F152" s="10" t="n">
+        <v>31</v>
+      </c>
+      <c r="G152" s="9" t="inlineStr"/>
+      <c r="H152" s="10" t="n">
+        <v>52</v>
+      </c>
+      <c r="I152" s="10" t="n">
+        <v>62</v>
+      </c>
+      <c r="J152" s="9" t="inlineStr"/>
+      <c r="K152" s="9" t="inlineStr"/>
+      <c r="L152" s="9" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="7" t="inlineStr">
         <is>
-          <t>14.05</t>
+          <t>15.01</t>
         </is>
       </c>
       <c r="B153" s="6" t="inlineStr">
         <is>
-          <t>Insurance Commission and Data Privacy compliance</t>
+          <t>Reporting, administration, security and go-live</t>
         </is>
       </c>
       <c r="C153" s="6" t="inlineStr">
         <is>
-          <t>IC production and business reports (premium placed by insurer and line)</t>
+          <t>Report catalogue (39 reports) in Excel, CSV and PDF with scheduled e-mail</t>
         </is>
       </c>
       <c r="D153" s="7" t="inlineStr">
@@ -8824,14 +8840,14 @@
       </c>
       <c r="E153" s="7" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="F153" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G153" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="G153" s="12" t="n">
+        <v>2</v>
       </c>
       <c r="H153" s="7">
         <f>F153*G153</f>
@@ -8843,30 +8859,26 @@
       </c>
       <c r="J153" s="6" t="inlineStr">
         <is>
-          <t>Production Register; Premium by Product / Month / Insurer</t>
-        </is>
-      </c>
-      <c r="K153" s="6" t="inlineStr">
-        <is>
-          <t>Figures available; IC layout not produced.</t>
-        </is>
-      </c>
+          <t>Reports &gt; All Reports (/reports/catalogue); reports.test.js; Daily reports job</t>
+        </is>
+      </c>
+      <c r="K153" s="6" t="inlineStr"/>
       <c r="L153" s="7" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="7" t="inlineStr">
         <is>
-          <t>14.06</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>Insurance Commission and Data Privacy compliance</t>
+          <t>Reporting, administration, security and go-live</t>
         </is>
       </c>
       <c r="C154" s="6" t="inlineStr">
         <is>
-          <t>Records of business available for IC examination</t>
+          <t>Role dashboards (executive, sales, processing, claims, commission)</t>
         </is>
       </c>
       <c r="D154" s="7" t="inlineStr">
@@ -8876,11 +8888,11 @@
       </c>
       <c r="E154" s="7" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="F154" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G154" s="12" t="n">
         <v>2</v>
@@ -8895,7 +8907,7 @@
       </c>
       <c r="J154" s="6" t="inlineStr">
         <is>
-          <t>Numbered placement trail RFQ to policy to receipt; reports; audit log</t>
+          <t>Dashboard menu; dashboard.test.js</t>
         </is>
       </c>
       <c r="K154" s="6" t="inlineStr"/>
@@ -8904,17 +8916,17 @@
     <row r="155">
       <c r="A155" s="7" t="inlineStr">
         <is>
-          <t>14.07</t>
+          <t>15.03</t>
         </is>
       </c>
       <c r="B155" s="6" t="inlineStr">
         <is>
-          <t>Insurance Commission and Data Privacy compliance</t>
+          <t>Reporting, administration, security and go-live</t>
         </is>
       </c>
       <c r="C155" s="6" t="inlineStr">
         <is>
-          <t>Premium held in trust for insurers, apart from own funds</t>
+          <t>Ad hoc reporting and BI extract</t>
         </is>
       </c>
       <c r="D155" s="7" t="inlineStr">
@@ -8924,14 +8936,14 @@
       </c>
       <c r="E155" s="7" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="F155" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G155" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="G155" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="H155" s="7">
         <f>F155*G155</f>
@@ -8943,26 +8955,30 @@
       </c>
       <c r="J155" s="6" t="inlineStr">
         <is>
-          <t>Premiums Payable to Insurers per insurer; Premium Trust Account; payment-segregation.test.js</t>
-        </is>
-      </c>
-      <c r="K155" s="6" t="inlineStr"/>
+          <t>Report criteria, filters and exports</t>
+        </is>
+      </c>
+      <c r="K155" s="6" t="inlineStr">
+        <is>
+          <t>No report designer or data warehouse extract.</t>
+        </is>
+      </c>
       <c r="L155" s="7" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="7" t="inlineStr">
         <is>
-          <t>14.08</t>
+          <t>15.04</t>
         </is>
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>Insurance Commission and Data Privacy compliance</t>
+          <t>Reporting, administration, security and go-live</t>
         </is>
       </c>
       <c r="C156" s="6" t="inlineStr">
         <is>
-          <t>Complaints handling and financial consumer protection (RA 11765)</t>
+          <t>Role-based access, deny by default, checked on every API call</t>
         </is>
       </c>
       <c r="D156" s="7" t="inlineStr">
@@ -8972,14 +8988,14 @@
       </c>
       <c r="E156" s="7" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>NPC</t>
         </is>
       </c>
       <c r="F156" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G156" s="13" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="G156" s="12" t="n">
+        <v>2</v>
       </c>
       <c r="H156" s="7">
         <f>F156*G156</f>
@@ -8991,30 +9007,26 @@
       </c>
       <c r="J156" s="6" t="inlineStr">
         <is>
-          <t>None found (grep complaint returns nothing)</t>
-        </is>
-      </c>
-      <c r="K156" s="6" t="inlineStr">
-        <is>
-          <t>No complaints register or response time tracking.</t>
-        </is>
-      </c>
+          <t>User Management &gt; Role Permissions, User Access Matrix; role-access.test.js; access-control.test.js</t>
+        </is>
+      </c>
+      <c r="K156" s="6" t="inlineStr"/>
       <c r="L156" s="7" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="7" t="inlineStr">
         <is>
-          <t>14.09</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="B157" s="6" t="inlineStr">
         <is>
-          <t>Insurance Commission and Data Privacy compliance</t>
+          <t>Reporting, administration, security and go-live</t>
         </is>
       </c>
       <c r="C157" s="6" t="inlineStr">
         <is>
-          <t>Data subject requests, export and anonymisation</t>
+          <t>Maker-checker, authority matrix, delegations, SoD and access reviews</t>
         </is>
       </c>
       <c r="D157" s="7" t="inlineStr">
@@ -9024,7 +9036,7 @@
       </c>
       <c r="E157" s="7" t="inlineStr">
         <is>
-          <t>NPC</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="F157" s="7" t="n">
@@ -9043,7 +9055,7 @@
       </c>
       <c r="J157" s="6" t="inlineStr">
         <is>
-          <t>Master &gt; Data Privacy &gt; Data Subject Requests; privacy.test.js</t>
+          <t>User Management &gt; Authority Matrix, Delegations, Segregation of Duties, Access Reviews; user-access.test.js</t>
         </is>
       </c>
       <c r="K157" s="6" t="inlineStr"/>
@@ -9052,17 +9064,17 @@
     <row r="158">
       <c r="A158" s="7" t="inlineStr">
         <is>
-          <t>14.10</t>
+          <t>15.06</t>
         </is>
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>Insurance Commission and Data Privacy compliance</t>
+          <t>Reporting, administration, security and go-live</t>
         </is>
       </c>
       <c r="C158" s="6" t="inlineStr">
         <is>
-          <t>Retention and disposal of personal data</t>
+          <t>Password policy, lockout and two-step verification</t>
         </is>
       </c>
       <c r="D158" s="7" t="inlineStr">
@@ -9076,7 +9088,7 @@
         </is>
       </c>
       <c r="F158" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G158" s="12" t="n">
         <v>2</v>
@@ -9091,7 +9103,7 @@
       </c>
       <c r="J158" s="6" t="inlineStr">
         <is>
-          <t>privacy.retention_years; housekeeping.* settings; privacy.test.js</t>
+          <t>security.require_2fa_roles; security.test.js; hardening.test.js</t>
         </is>
       </c>
       <c r="K158" s="6" t="inlineStr"/>
@@ -9100,17 +9112,17 @@
     <row r="159">
       <c r="A159" s="7" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>15.07</t>
         </is>
       </c>
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>Insurance Commission and Data Privacy compliance</t>
+          <t>Reporting, administration, security and go-live</t>
         </is>
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
-          <t>Breach detection support and breach register</t>
+          <t>Audit trail with before and after values, searchable by users</t>
         </is>
       </c>
       <c r="D159" s="7" t="inlineStr">
@@ -9124,7 +9136,7 @@
         </is>
       </c>
       <c r="F159" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G159" s="11" t="n">
         <v>1</v>
@@ -9139,30 +9151,34 @@
       </c>
       <c r="J159" s="6" t="inlineStr">
         <is>
-          <t>Login history, audit log, failed sign-in alarms</t>
+          <t>Master &gt; Configuration &gt; Audit Trail; audit log written for create, update, approval, report run, sign-in</t>
         </is>
       </c>
       <c r="K159" s="6" t="inlineStr">
         <is>
-          <t>No breach register or 72-hour notification tracker.</t>
-        </is>
-      </c>
-      <c r="L159" s="7" t="inlineStr"/>
+          <t>Audit log delivered; the reworked Audit Trail screen is in development and counted as not delivered.</t>
+        </is>
+      </c>
+      <c r="L159" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="7" t="inlineStr">
         <is>
-          <t>14.12</t>
+          <t>15.08</t>
         </is>
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>Insurance Commission and Data Privacy compliance</t>
+          <t>Reporting, administration, security and go-live</t>
         </is>
       </c>
       <c r="C160" s="6" t="inlineStr">
         <is>
-          <t>Masking of personal data on screens and exports by role</t>
+          <t>Menu organised by role and task</t>
         </is>
       </c>
       <c r="D160" s="7" t="inlineStr">
@@ -9172,14 +9188,14 @@
       </c>
       <c r="E160" s="7" t="inlineStr">
         <is>
-          <t>NPC</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="F160" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G160" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G160" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="H160" s="7">
         <f>F160*G160</f>
@@ -9191,12 +9207,12 @@
       </c>
       <c r="J160" s="6" t="inlineStr">
         <is>
-          <t>Not delivered (in development)</t>
+          <t>brokerverse/src/components/SideBar/list.js (173 menu screens)</t>
         </is>
       </c>
       <c r="K160" s="6" t="inlineStr">
         <is>
-          <t>Personal identifiers shown in full to every role with read access.</t>
+          <t>Menu redesign in development.</t>
         </is>
       </c>
       <c r="L160" s="7" t="inlineStr">
@@ -9208,17 +9224,17 @@
     <row r="161">
       <c r="A161" s="7" t="inlineStr">
         <is>
-          <t>14.13</t>
+          <t>15.09</t>
         </is>
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
-          <t>Insurance Commission and Data Privacy compliance</t>
+          <t>Reporting, administration, security and go-live</t>
         </is>
       </c>
       <c r="C161" s="6" t="inlineStr">
         <is>
-          <t>Encryption of personal identifiers</t>
+          <t>My Work: one inbox of tasks and approvals per user</t>
         </is>
       </c>
       <c r="D161" s="7" t="inlineStr">
@@ -9228,11 +9244,11 @@
       </c>
       <c r="E161" s="7" t="inlineStr">
         <is>
-          <t>NPC</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="F161" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G161" s="11" t="n">
         <v>1</v>
@@ -9247,30 +9263,34 @@
       </c>
       <c r="J161" s="6" t="inlineStr">
         <is>
-          <t>Storage encryption (hosting); two-step secrets AES-256-GCM; BV-DEF-003 open</t>
+          <t>In-app notifications and approval notifications; approval-notifications.test.js</t>
         </is>
       </c>
       <c r="K161" s="6" t="inlineStr">
         <is>
-          <t>No field-level encryption of IDs and TIN.</t>
-        </is>
-      </c>
-      <c r="L161" s="7" t="inlineStr"/>
+          <t>My Work inbox in development.</t>
+        </is>
+      </c>
+      <c r="L161" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="7" t="inlineStr">
         <is>
-          <t>14.14</t>
+          <t>15.10</t>
         </is>
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>Insurance Commission and Data Privacy compliance</t>
+          <t>Reporting, administration, security and go-live</t>
         </is>
       </c>
       <c r="C162" s="6" t="inlineStr">
         <is>
-          <t>Data residency in the Philippines when required</t>
+          <t>Document numbering, configuration with approval, e-mail outbox and notifications</t>
         </is>
       </c>
       <c r="D162" s="7" t="inlineStr">
@@ -9280,11 +9300,11 @@
       </c>
       <c r="E162" s="7" t="inlineStr">
         <is>
-          <t>NPC</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="F162" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G162" s="12" t="n">
         <v>2</v>
@@ -9299,48 +9319,72 @@
       </c>
       <c r="J162" s="6" t="inlineStr">
         <is>
-          <t>Hosting options: local partner or on-premise (architecture document)</t>
+          <t>Master &gt; Document Numbering, Configuration, Configuration Approvals, E-mail Outbox; numbering.test.js; configuration-controls.test.js; email-outbox.test.js</t>
         </is>
       </c>
       <c r="K162" s="6" t="inlineStr"/>
       <c r="L162" s="7" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" s="9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B163" s="9" t="inlineStr">
+      <c r="A163" s="7" t="inlineStr">
+        <is>
+          <t>15.11</t>
+        </is>
+      </c>
+      <c r="B163" s="6" t="inlineStr">
         <is>
           <t>Reporting, administration, security and go-live</t>
         </is>
       </c>
-      <c r="C163" s="9" t="inlineStr">
-        <is>
-          <t>L1 subtotal: fit 85.7%</t>
-        </is>
-      </c>
-      <c r="D163" s="9" t="inlineStr"/>
-      <c r="E163" s="9" t="inlineStr"/>
-      <c r="F163" s="10" t="n">
-        <v>35</v>
-      </c>
-      <c r="G163" s="9" t="inlineStr"/>
-      <c r="H163" s="10" t="n">
-        <v>60</v>
-      </c>
-      <c r="I163" s="10" t="n">
-        <v>70</v>
-      </c>
-      <c r="J163" s="9" t="inlineStr"/>
-      <c r="K163" s="9" t="inlineStr"/>
-      <c r="L163" s="9" t="inlineStr"/>
+      <c r="C163" s="6" t="inlineStr">
+        <is>
+          <t>Branding, letterhead and e-signature on documents</t>
+        </is>
+      </c>
+      <c r="D163" s="7" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E163" s="7" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+      <c r="F163" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G163" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H163" s="7">
+        <f>F163*G163</f>
+        <v/>
+      </c>
+      <c r="I163" s="7">
+        <f>2*F163</f>
+        <v/>
+      </c>
+      <c r="J163" s="6" t="inlineStr">
+        <is>
+          <t>Letterhead from Company master; System Settings logo and theme</t>
+        </is>
+      </c>
+      <c r="K163" s="6" t="inlineStr">
+        <is>
+          <t>Branding and e-signature in development.</t>
+        </is>
+      </c>
+      <c r="L163" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="7" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>15.12</t>
         </is>
       </c>
       <c r="B164" s="6" t="inlineStr">
@@ -9350,7 +9394,7 @@
       </c>
       <c r="C164" s="6" t="inlineStr">
         <is>
-          <t>Report catalogue (39 reports) in Excel, CSV and PDF with scheduled e-mail</t>
+          <t>Philippine reference masters (PSGC geography, banks, IDs, salutations, IC insurer list)</t>
         </is>
       </c>
       <c r="D164" s="7" t="inlineStr">
@@ -9364,10 +9408,10 @@
         </is>
       </c>
       <c r="F164" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G164" s="12" t="n">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="G164" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="H164" s="7">
         <f>F164*G164</f>
@@ -9379,16 +9423,24 @@
       </c>
       <c r="J164" s="6" t="inlineStr">
         <is>
-          <t>Reports &gt; All Reports (/reports/catalogue); reports.test.js; Daily reports job</t>
-        </is>
-      </c>
-      <c r="K164" s="6" t="inlineStr"/>
-      <c r="L164" s="7" t="inlineStr"/>
+          <t>Seeds: Metro Manila and selected LGUs (seeds/10_masters.sql); KYC ID setting</t>
+        </is>
+      </c>
+      <c r="K164" s="6" t="inlineStr">
+        <is>
+          <t>Full Philippine masters are in development.</t>
+        </is>
+      </c>
+      <c r="L164" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="7" t="inlineStr">
         <is>
-          <t>15.02</t>
+          <t>15.13</t>
         </is>
       </c>
       <c r="B165" s="6" t="inlineStr">
@@ -9398,7 +9450,7 @@
       </c>
       <c r="C165" s="6" t="inlineStr">
         <is>
-          <t>Role dashboards (executive, sales, processing, claims, commission)</t>
+          <t>Go-live data load (masters, in-force book, open items, GL opening balances) with rehearsal and reconciliation</t>
         </is>
       </c>
       <c r="D165" s="7" t="inlineStr">
@@ -9412,7 +9464,7 @@
         </is>
       </c>
       <c r="F165" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G165" s="12" t="n">
         <v>2</v>
@@ -9427,7 +9479,7 @@
       </c>
       <c r="J165" s="6" t="inlineStr">
         <is>
-          <t>Dashboard menu; dashboard.test.js</t>
+          <t>Master &gt; Go-Live Data Load; go-live.test.js; go-live-workbench.test.js; go-live-roundtrip.test.js; docs/e2e/GOLIVE_REHEARSAL_RUN.md (51 checks passed)</t>
         </is>
       </c>
       <c r="K165" s="6" t="inlineStr"/>
@@ -9436,7 +9488,7 @@
     <row r="166">
       <c r="A166" s="7" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>15.16</t>
         </is>
       </c>
       <c r="B166" s="6" t="inlineStr">
@@ -9446,7 +9498,7 @@
       </c>
       <c r="C166" s="6" t="inlineStr">
         <is>
-          <t>Ad hoc reporting and BI extract</t>
+          <t>Hosting choice, backups and disaster recovery</t>
         </is>
       </c>
       <c r="D166" s="7" t="inlineStr">
@@ -9460,10 +9512,10 @@
         </is>
       </c>
       <c r="F166" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G166" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="G166" s="12" t="n">
+        <v>2</v>
       </c>
       <c r="H166" s="7">
         <f>F166*G166</f>
@@ -9475,714 +9527,46 @@
       </c>
       <c r="J166" s="6" t="inlineStr">
         <is>
-          <t>Report criteria, filters and exports</t>
+          <t>Architecture and BCDR documents; /api/health</t>
         </is>
       </c>
       <c r="K166" s="6" t="inlineStr">
         <is>
-          <t>No report designer or data warehouse extract.</t>
+          <t>Recovery objectives are recommended values; no DR test yet.</t>
         </is>
       </c>
       <c r="L166" s="7" t="inlineStr"/>
     </row>
     <row r="167">
-      <c r="A167" s="7" t="inlineStr">
-        <is>
-          <t>15.04</t>
-        </is>
-      </c>
-      <c r="B167" s="6" t="inlineStr">
-        <is>
-          <t>Reporting, administration, security and go-live</t>
-        </is>
-      </c>
-      <c r="C167" s="6" t="inlineStr">
-        <is>
-          <t>Role-based access, deny by default, checked on every API call</t>
-        </is>
-      </c>
-      <c r="D167" s="7" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="E167" s="7" t="inlineStr">
-        <is>
-          <t>NPC</t>
-        </is>
-      </c>
-      <c r="F167" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G167" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="H167" s="7">
-        <f>F167*G167</f>
-        <v/>
-      </c>
-      <c r="I167" s="7">
-        <f>2*F167</f>
-        <v/>
-      </c>
-      <c r="J167" s="6" t="inlineStr">
-        <is>
-          <t>User Management &gt; Role Permissions, User Access Matrix; role-access.test.js; access-control.test.js</t>
-        </is>
-      </c>
-      <c r="K167" s="6" t="inlineStr"/>
-      <c r="L167" s="7" t="inlineStr"/>
-    </row>
-    <row r="168">
-      <c r="A168" s="7" t="inlineStr">
-        <is>
-          <t>15.05</t>
-        </is>
-      </c>
-      <c r="B168" s="6" t="inlineStr">
-        <is>
-          <t>Reporting, administration, security and go-live</t>
-        </is>
-      </c>
-      <c r="C168" s="6" t="inlineStr">
-        <is>
-          <t>Maker-checker, authority matrix, delegations, SoD and access reviews</t>
-        </is>
-      </c>
-      <c r="D168" s="7" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="E168" s="7" t="inlineStr">
-        <is>
-          <t>Ops</t>
-        </is>
-      </c>
-      <c r="F168" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G168" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="H168" s="7">
-        <f>F168*G168</f>
-        <v/>
-      </c>
-      <c r="I168" s="7">
-        <f>2*F168</f>
-        <v/>
-      </c>
-      <c r="J168" s="6" t="inlineStr">
-        <is>
-          <t>User Management &gt; Authority Matrix, Delegations, Segregation of Duties, Access Reviews; user-access.test.js</t>
-        </is>
-      </c>
-      <c r="K168" s="6" t="inlineStr"/>
-      <c r="L168" s="7" t="inlineStr"/>
-    </row>
-    <row r="169">
-      <c r="A169" s="7" t="inlineStr">
-        <is>
-          <t>15.06</t>
-        </is>
-      </c>
-      <c r="B169" s="6" t="inlineStr">
-        <is>
-          <t>Reporting, administration, security and go-live</t>
-        </is>
-      </c>
-      <c r="C169" s="6" t="inlineStr">
-        <is>
-          <t>Password policy, lockout and two-step verification</t>
-        </is>
-      </c>
-      <c r="D169" s="7" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="E169" s="7" t="inlineStr">
-        <is>
-          <t>NPC</t>
-        </is>
-      </c>
-      <c r="F169" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G169" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="H169" s="7">
-        <f>F169*G169</f>
-        <v/>
-      </c>
-      <c r="I169" s="7">
-        <f>2*F169</f>
-        <v/>
-      </c>
-      <c r="J169" s="6" t="inlineStr">
-        <is>
-          <t>security.require_2fa_roles; security.test.js; hardening.test.js</t>
-        </is>
-      </c>
-      <c r="K169" s="6" t="inlineStr"/>
-      <c r="L169" s="7" t="inlineStr"/>
-    </row>
-    <row r="170">
-      <c r="A170" s="7" t="inlineStr">
-        <is>
-          <t>15.07</t>
-        </is>
-      </c>
-      <c r="B170" s="6" t="inlineStr">
-        <is>
-          <t>Reporting, administration, security and go-live</t>
-        </is>
-      </c>
-      <c r="C170" s="6" t="inlineStr">
-        <is>
-          <t>Audit trail with before and after values, searchable by users</t>
-        </is>
-      </c>
-      <c r="D170" s="7" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="E170" s="7" t="inlineStr">
-        <is>
-          <t>NPC</t>
-        </is>
-      </c>
-      <c r="F170" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G170" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H170" s="7">
-        <f>F170*G170</f>
-        <v/>
-      </c>
-      <c r="I170" s="7">
-        <f>2*F170</f>
-        <v/>
-      </c>
-      <c r="J170" s="6" t="inlineStr">
-        <is>
-          <t>Master &gt; Configuration &gt; Audit Trail; audit log written for create, update, approval, report run, sign-in</t>
-        </is>
-      </c>
-      <c r="K170" s="6" t="inlineStr">
-        <is>
-          <t>Audit log delivered; the reworked Audit Trail screen is in development and counted as not delivered.</t>
-        </is>
-      </c>
-      <c r="L170" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="7" t="inlineStr">
-        <is>
-          <t>15.08</t>
-        </is>
-      </c>
-      <c r="B171" s="6" t="inlineStr">
-        <is>
-          <t>Reporting, administration, security and go-live</t>
-        </is>
-      </c>
-      <c r="C171" s="6" t="inlineStr">
-        <is>
-          <t>Menu organised by role and task</t>
-        </is>
-      </c>
-      <c r="D171" s="7" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="E171" s="7" t="inlineStr">
-        <is>
-          <t>Ops</t>
-        </is>
-      </c>
-      <c r="F171" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G171" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H171" s="7">
-        <f>F171*G171</f>
-        <v/>
-      </c>
-      <c r="I171" s="7">
-        <f>2*F171</f>
-        <v/>
-      </c>
-      <c r="J171" s="6" t="inlineStr">
-        <is>
-          <t>brokerverse/src/components/SideBar/list.js (173 menu screens)</t>
-        </is>
-      </c>
-      <c r="K171" s="6" t="inlineStr">
-        <is>
-          <t>Menu redesign in development.</t>
-        </is>
-      </c>
-      <c r="L171" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="7" t="inlineStr">
-        <is>
-          <t>15.09</t>
-        </is>
-      </c>
-      <c r="B172" s="6" t="inlineStr">
-        <is>
-          <t>Reporting, administration, security and go-live</t>
-        </is>
-      </c>
-      <c r="C172" s="6" t="inlineStr">
-        <is>
-          <t>My Work: one inbox of tasks and approvals per user</t>
-        </is>
-      </c>
-      <c r="D172" s="7" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="E172" s="7" t="inlineStr">
-        <is>
-          <t>Ops</t>
-        </is>
-      </c>
-      <c r="F172" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G172" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H172" s="7">
-        <f>F172*G172</f>
-        <v/>
-      </c>
-      <c r="I172" s="7">
-        <f>2*F172</f>
-        <v/>
-      </c>
-      <c r="J172" s="6" t="inlineStr">
-        <is>
-          <t>In-app notifications and approval notifications; approval-notifications.test.js</t>
-        </is>
-      </c>
-      <c r="K172" s="6" t="inlineStr">
-        <is>
-          <t>My Work inbox in development.</t>
-        </is>
-      </c>
-      <c r="L172" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="7" t="inlineStr">
-        <is>
-          <t>15.10</t>
-        </is>
-      </c>
-      <c r="B173" s="6" t="inlineStr">
-        <is>
-          <t>Reporting, administration, security and go-live</t>
-        </is>
-      </c>
-      <c r="C173" s="6" t="inlineStr">
-        <is>
-          <t>Document numbering and configuration with approval and audit</t>
-        </is>
-      </c>
-      <c r="D173" s="7" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="E173" s="7" t="inlineStr">
-        <is>
-          <t>Ops</t>
-        </is>
-      </c>
-      <c r="F173" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G173" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="H173" s="7">
-        <f>F173*G173</f>
-        <v/>
-      </c>
-      <c r="I173" s="7">
-        <f>2*F173</f>
-        <v/>
-      </c>
-      <c r="J173" s="6" t="inlineStr">
-        <is>
-          <t>Master &gt; Document Numbering, Configuration, Configuration Approvals; numbering.test.js; configuration-controls.test.js</t>
-        </is>
-      </c>
-      <c r="K173" s="6" t="inlineStr"/>
-      <c r="L173" s="7" t="inlineStr"/>
-    </row>
-    <row r="174">
-      <c r="A174" s="7" t="inlineStr">
-        <is>
-          <t>15.11</t>
-        </is>
-      </c>
-      <c r="B174" s="6" t="inlineStr">
-        <is>
-          <t>Reporting, administration, security and go-live</t>
-        </is>
-      </c>
-      <c r="C174" s="6" t="inlineStr">
-        <is>
-          <t>Branding, letterhead and e-signature on documents</t>
-        </is>
-      </c>
-      <c r="D174" s="7" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="E174" s="7" t="inlineStr">
-        <is>
-          <t>Ops</t>
-        </is>
-      </c>
-      <c r="F174" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G174" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H174" s="7">
-        <f>F174*G174</f>
-        <v/>
-      </c>
-      <c r="I174" s="7">
-        <f>2*F174</f>
-        <v/>
-      </c>
-      <c r="J174" s="6" t="inlineStr">
-        <is>
-          <t>Letterhead from Company master; System Settings logo and theme</t>
-        </is>
-      </c>
-      <c r="K174" s="6" t="inlineStr">
-        <is>
-          <t>Branding and e-signature in development.</t>
-        </is>
-      </c>
-      <c r="L174" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="7" t="inlineStr">
-        <is>
-          <t>15.12</t>
-        </is>
-      </c>
-      <c r="B175" s="6" t="inlineStr">
-        <is>
-          <t>Reporting, administration, security and go-live</t>
-        </is>
-      </c>
-      <c r="C175" s="6" t="inlineStr">
-        <is>
-          <t>Philippine reference masters (PSGC geography, banks, IDs, salutations, IC insurer list)</t>
-        </is>
-      </c>
-      <c r="D175" s="7" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="E175" s="7" t="inlineStr">
-        <is>
-          <t>Ops</t>
-        </is>
-      </c>
-      <c r="F175" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G175" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H175" s="7">
-        <f>F175*G175</f>
-        <v/>
-      </c>
-      <c r="I175" s="7">
-        <f>2*F175</f>
-        <v/>
-      </c>
-      <c r="J175" s="6" t="inlineStr">
-        <is>
-          <t>Seeds: Metro Manila and selected LGUs (seeds/10_masters.sql); KYC ID setting</t>
-        </is>
-      </c>
-      <c r="K175" s="6" t="inlineStr">
-        <is>
-          <t>Full Philippine masters are in development.</t>
-        </is>
-      </c>
-      <c r="L175" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="7" t="inlineStr">
-        <is>
-          <t>15.13</t>
-        </is>
-      </c>
-      <c r="B176" s="6" t="inlineStr">
-        <is>
-          <t>Reporting, administration, security and go-live</t>
-        </is>
-      </c>
-      <c r="C176" s="6" t="inlineStr">
-        <is>
-          <t>Go-live data load: masters, in-force book, open items, GL opening balances</t>
-        </is>
-      </c>
-      <c r="D176" s="7" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="E176" s="7" t="inlineStr">
-        <is>
-          <t>Ops</t>
-        </is>
-      </c>
-      <c r="F176" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G176" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="H176" s="7">
-        <f>F176*G176</f>
-        <v/>
-      </c>
-      <c r="I176" s="7">
-        <f>2*F176</f>
-        <v/>
-      </c>
-      <c r="J176" s="6" t="inlineStr">
-        <is>
-          <t>Master &gt; Go-Live Data Load; go-live.test.js; go-live-workbench.test.js; go-live-roundtrip.test.js</t>
-        </is>
-      </c>
-      <c r="K176" s="6" t="inlineStr"/>
-      <c r="L176" s="7" t="inlineStr"/>
-    </row>
-    <row r="177">
-      <c r="A177" s="7" t="inlineStr">
-        <is>
-          <t>15.14</t>
-        </is>
-      </c>
-      <c r="B177" s="6" t="inlineStr">
-        <is>
-          <t>Reporting, administration, security and go-live</t>
-        </is>
-      </c>
-      <c r="C177" s="6" t="inlineStr">
-        <is>
-          <t>Migration rehearsal and reconciliation</t>
-        </is>
-      </c>
-      <c r="D177" s="7" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="E177" s="7" t="inlineStr">
-        <is>
-          <t>Ops</t>
-        </is>
-      </c>
-      <c r="F177" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G177" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="H177" s="7">
-        <f>F177*G177</f>
-        <v/>
-      </c>
-      <c r="I177" s="7">
-        <f>2*F177</f>
-        <v/>
-      </c>
-      <c r="J177" s="6" t="inlineStr">
-        <is>
-          <t>scripts/golive-rehearsal.js; docs/e2e/GOLIVE_REHEARSAL_RUN.md (51 checks passed)</t>
-        </is>
-      </c>
-      <c r="K177" s="6" t="inlineStr"/>
-      <c r="L177" s="7" t="inlineStr"/>
-    </row>
-    <row r="178">
-      <c r="A178" s="7" t="inlineStr">
-        <is>
-          <t>15.15</t>
-        </is>
-      </c>
-      <c r="B178" s="6" t="inlineStr">
-        <is>
-          <t>Reporting, administration, security and go-live</t>
-        </is>
-      </c>
-      <c r="C178" s="6" t="inlineStr">
-        <is>
-          <t>E-mail outbox and in-app notifications</t>
-        </is>
-      </c>
-      <c r="D178" s="7" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="E178" s="7" t="inlineStr">
-        <is>
-          <t>Ops</t>
-        </is>
-      </c>
-      <c r="F178" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G178" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="H178" s="7">
-        <f>F178*G178</f>
-        <v/>
-      </c>
-      <c r="I178" s="7">
-        <f>2*F178</f>
-        <v/>
-      </c>
-      <c r="J178" s="6" t="inlineStr">
-        <is>
-          <t>Master &gt; Configuration &gt; E-mail Outbox; email-outbox.test.js</t>
-        </is>
-      </c>
-      <c r="K178" s="6" t="inlineStr"/>
-      <c r="L178" s="7" t="inlineStr"/>
-    </row>
-    <row r="179">
-      <c r="A179" s="7" t="inlineStr">
-        <is>
-          <t>15.16</t>
-        </is>
-      </c>
-      <c r="B179" s="6" t="inlineStr">
-        <is>
-          <t>Reporting, administration, security and go-live</t>
-        </is>
-      </c>
-      <c r="C179" s="6" t="inlineStr">
-        <is>
-          <t>Hosting choice, backups and disaster recovery</t>
-        </is>
-      </c>
-      <c r="D179" s="7" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="E179" s="7" t="inlineStr">
-        <is>
-          <t>Ops</t>
-        </is>
-      </c>
-      <c r="F179" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G179" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="H179" s="7">
-        <f>F179*G179</f>
-        <v/>
-      </c>
-      <c r="I179" s="7">
-        <f>2*F179</f>
-        <v/>
-      </c>
-      <c r="J179" s="6" t="inlineStr">
-        <is>
-          <t>Architecture and BCDR documents; /api/health</t>
-        </is>
-      </c>
-      <c r="K179" s="6" t="inlineStr">
-        <is>
-          <t>Recovery objectives are recommended values; no DR test yet.</t>
-        </is>
-      </c>
-      <c r="L179" s="7" t="inlineStr"/>
-    </row>
-    <row r="180">
-      <c r="A180" s="4" t="inlineStr"/>
-      <c r="B180" s="4" t="inlineStr">
+      <c r="A167" s="4" t="inlineStr"/>
+      <c r="B167" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C180" s="4" t="inlineStr">
-        <is>
-          <t>Overall fit 81.5%</t>
-        </is>
-      </c>
-      <c r="D180" s="4" t="inlineStr"/>
-      <c r="E180" s="4" t="inlineStr"/>
-      <c r="F180" s="4" t="inlineStr"/>
-      <c r="G180" s="4" t="inlineStr"/>
-      <c r="H180" s="14">
-        <f>SUMIF(A2:A179,"*.*",H2:H179)</f>
-        <v/>
-      </c>
-      <c r="I180" s="14">
-        <f>SUMIF(A2:A179,"*.*",I2:I179)</f>
-        <v/>
-      </c>
-      <c r="J180" s="4" t="inlineStr"/>
-      <c r="K180" s="4" t="inlineStr"/>
-      <c r="L180" s="4" t="inlineStr"/>
+      <c r="C167" s="4" t="inlineStr">
+        <is>
+          <t>Overall fit 80.4%</t>
+        </is>
+      </c>
+      <c r="D167" s="4" t="inlineStr"/>
+      <c r="E167" s="4" t="inlineStr"/>
+      <c r="F167" s="4" t="inlineStr"/>
+      <c r="G167" s="4" t="inlineStr"/>
+      <c r="H167" s="14">
+        <f>SUMIF(A2:A166,"*.*",H2:H166)</f>
+        <v/>
+      </c>
+      <c r="I167" s="14">
+        <f>SUMIF(A2:A166,"*.*",I2:I166)</f>
+        <v/>
+      </c>
+      <c r="J167" s="4" t="inlineStr"/>
+      <c r="K167" s="4" t="inlineStr"/>
+      <c r="L167" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L179"/>
+  <autoFilter ref="A1:L166"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13235,10 +12619,10 @@
         <v>2.5</v>
       </c>
       <c r="N2" s="7" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="O2" s="7" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="P2" s="7" t="n">
         <v>0</v>
@@ -13330,10 +12714,10 @@
         <v>2.8</v>
       </c>
       <c r="N3" s="7" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="O3" s="7" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="P3" s="7" t="n">
         <v>2</v>
@@ -13425,30 +12809,30 @@
         <v>3.3</v>
       </c>
       <c r="N4" s="7" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O4" s="7" t="n">
-        <v>17.5</v>
+        <v>17.7</v>
       </c>
       <c r="P4" s="7" t="n">
         <v>3</v>
       </c>
       <c r="Q4" s="7" t="inlineStr">
         <is>
-          <t>27 to 37%</t>
+          <t>28 to 38%</t>
         </is>
       </c>
       <c r="R4" s="7" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>81 to 111</t>
+          <t>84 to 114</t>
         </is>
       </c>
       <c r="T4" s="7" t="inlineStr">
         <is>
-          <t>16 to 22</t>
+          <t>17 to 23</t>
         </is>
       </c>
       <c r="U4" s="6" t="inlineStr">
@@ -13517,13 +12901,13 @@
         </is>
       </c>
       <c r="M5" s="7" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="N5" s="7" t="n">
         <v>7</v>
       </c>
       <c r="O5" s="7" t="n">
-        <v>20.1</v>
+        <v>20.5</v>
       </c>
       <c r="P5" s="7" t="n">
         <v>7</v>
@@ -13615,10 +12999,10 @@
         <v>2.7</v>
       </c>
       <c r="N6" s="7" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="O6" s="7" t="n">
-        <v>20.2</v>
+        <v>20.5</v>
       </c>
       <c r="P6" s="7" t="n">
         <v>10</v>
@@ -13707,13 +13091,13 @@
         </is>
       </c>
       <c r="M7" s="7" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N7" s="7" t="n">
-        <v>10.1</v>
+        <v>9.9</v>
       </c>
       <c r="O7" s="7" t="n">
-        <v>20.6</v>
+        <v>20.9</v>
       </c>
       <c r="P7" s="7" t="n">
         <v>10</v>
@@ -13802,13 +13186,13 @@
         </is>
       </c>
       <c r="M8" s="7" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="O8" s="7" t="n">
-        <v>25.5</v>
+        <v>25.8</v>
       </c>
       <c r="P8" s="7" t="n">
         <v>9</v>
@@ -13900,10 +13284,10 @@
         <v>3.3</v>
       </c>
       <c r="N9" s="7" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="O9" s="7" t="n">
-        <v>28.3</v>
+        <v>28.7</v>
       </c>
       <c r="P9" s="7" t="n">
         <v>10</v>
@@ -13995,10 +13379,10 @@
         <v>3.4</v>
       </c>
       <c r="N10" s="7" t="n">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="O10" s="7" t="n">
-        <v>24.5</v>
+        <v>25</v>
       </c>
       <c r="P10" s="7" t="n">
         <v>12</v>
@@ -14201,7 +13585,7 @@
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
@@ -14311,7 +13695,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
@@ -14366,7 +13750,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
@@ -14476,7 +13860,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
@@ -14531,7 +13915,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
@@ -14586,7 +13970,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
@@ -14641,7 +14025,7 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
@@ -14696,7 +14080,7 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
@@ -14751,7 +14135,7 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
@@ -14806,7 +14190,7 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C14" s="13" t="inlineStr">
         <is>
@@ -14861,7 +14245,7 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
@@ -14916,7 +14300,7 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
@@ -15013,7 +14397,7 @@
         <v>24</v>
       </c>
       <c r="E18" s="14" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F18" s="14" t="n">
         <v>38</v>
@@ -15103,7 +14487,7 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>163 L2 processes in 15 L1 areas, written from Philippine broking practice: Insurance Code (RA 10607) and IC rules, NIRC and EOPT Act (RA 11976) with RR 7-2024, Data Privacy Act (RA 10173) and NPC rules, AMLA (RA 9160 as amended), Financial Consumer Protection Act (RA 11765), LTO and CTPL practice.</t>
+          <t>150 L2 processes in 15 L1 areas, written from Philippine broking practice: Insurance Code (RA 10607) and IC rules, NIRC and EOPT Act (RA 11976) with RR 7-2024, Data Privacy Act (RA 10173) and NPC rules, AMLA (RA 9160 as amended), Financial Consumer Protection Act (RA 11765), LTO and CTPL practice.</t>
         </is>
       </c>
     </row>

--- a/docs/package/08_Management/BrokerVerse_PH_Fit_and_ASEAN_Rollout_Assessment.xlsx
+++ b/docs/package/08_Management/BrokerVerse_PH_Fit_and_ASEAN_Rollout_Assessment.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PH Process Fit'!$A$1:$L$166</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Gaps Ranked'!$A$1:$L$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Gaps Ranked'!$A$1:$L$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -83,22 +83,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00DCEFE3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DCEFE3"/>
+        <fgColor rgb="00FBE0C2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F8D7DA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FBE0C2"/>
       </patternFill>
     </fill>
   </fills>
@@ -162,13 +162,13 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -805,7 +805,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Assessed on the code of branch brokerverse-platform as of 04 October 2026. Work in development is counted as not delivered. Scores: 2 supported end to end, 1 partly supported, 0 not supported.</t>
+          <t>Version 1.1: re-scored on the code of branch brokerverse-platform as of 04 October 2026 with every release package merged (version 1.0 of the same date was the pre-release assessment). Scores: 2 supported end to end, 1 partly supported, 0 not supported.</t>
         </is>
       </c>
     </row>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>0.804</v>
+        <v>0.993</v>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.7070000000000001</v>
+        <v>0.978</v>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>0.8540000000000001</v>
+        <v>1</v>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>0.8059999999999999</v>
+        <v>0.992</v>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>0.795</v>
+        <v>0.992</v>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
@@ -904,15 +904,17 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Fit once work in development lands</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>0.8440000000000001</v>
+          <t>Processes not scored 2</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>12 L2 processes covered by work in development, counted at 2</t>
+          <t>Scored 1: regulator confirmation of a report layout outstanding (sheet Gaps Ranked)</t>
         </is>
       </c>
     </row>
@@ -923,7 +925,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>0.6759999999999999</v>
+        <v>0.9590000000000001</v>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
@@ -938,7 +940,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>0.8100000000000001</v>
+        <v>1</v>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
@@ -953,7 +955,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>0.7829999999999999</v>
+        <v>1</v>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
@@ -968,7 +970,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>0.357</v>
+        <v>0.929</v>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
@@ -984,7 +986,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>96 / 36 / 18</t>
+          <t>148 / 2 / 0</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr"/>
@@ -1020,11 +1022,11 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>0.523</v>
+        <v>0.955</v>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>10 (4 / 2 / 4)</t>
+          <t>10 (9 / 1 / 0)</t>
         </is>
       </c>
     </row>
@@ -1035,11 +1037,11 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>0.654</v>
+        <v>1</v>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>7 (3 / 3 / 1)</t>
+          <t>7 (7 / 0 / 0)</t>
         </is>
       </c>
     </row>
@@ -1050,11 +1052,11 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>0.8959999999999999</v>
+        <v>1</v>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>11 (8 / 3 / 0)</t>
+          <t>11 (11 / 0 / 0)</t>
         </is>
       </c>
     </row>
@@ -1065,11 +1067,11 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>0.848</v>
+        <v>1</v>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>10 (7 / 2 / 1)</t>
+          <t>10 (10 / 0 / 0)</t>
         </is>
       </c>
     </row>
@@ -1080,11 +1082,11 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>0.833</v>
+        <v>1</v>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>11 (7 / 3 / 1)</t>
+          <t>11 (11 / 0 / 0)</t>
         </is>
       </c>
     </row>
@@ -1095,11 +1097,11 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>0.8159999999999999</v>
+        <v>1</v>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>8 (6 / 1 / 1)</t>
+          <t>8 (8 / 0 / 0)</t>
         </is>
       </c>
     </row>
@@ -1110,11 +1112,11 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>0.917</v>
+        <v>1</v>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>6 (5 / 0 / 1)</t>
+          <t>6 (6 / 0 / 0)</t>
         </is>
       </c>
     </row>
@@ -1125,11 +1127,11 @@
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>0.893</v>
+        <v>1</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>12 (10 / 1 / 1)</t>
+          <t>12 (12 / 0 / 0)</t>
         </is>
       </c>
     </row>
@@ -1140,11 +1142,11 @@
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>0.833</v>
+        <v>1</v>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>8 (6 / 0 / 2)</t>
+          <t>8 (8 / 0 / 0)</t>
         </is>
       </c>
     </row>
@@ -1155,11 +1157,11 @@
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>9 (7 / 1 / 1)</t>
+          <t>9 (9 / 0 / 0)</t>
         </is>
       </c>
     </row>
@@ -1170,11 +1172,11 @@
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>0.8420000000000001</v>
+        <v>1</v>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>8 (5 / 3 / 0)</t>
+          <t>8 (8 / 0 / 0)</t>
         </is>
       </c>
     </row>
@@ -1185,11 +1187,11 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>10 (9 / 1 / 0)</t>
+          <t>10 (10 / 0 / 0)</t>
         </is>
       </c>
     </row>
@@ -1200,11 +1202,11 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>0.742</v>
+        <v>1</v>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>13 (6 / 6 / 1)</t>
+          <t>13 (13 / 0 / 0)</t>
         </is>
       </c>
     </row>
@@ -1215,11 +1217,11 @@
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>0.593</v>
+        <v>0.9440000000000001</v>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>13 (5 / 4 / 4)</t>
+          <t>13 (12 / 1 / 0)</t>
         </is>
       </c>
     </row>
@@ -1230,11 +1232,11 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>0.8390000000000001</v>
+        <v>1</v>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>14 (8 / 6 / 0)</t>
+          <t>14 (14 / 0 / 0)</t>
         </is>
       </c>
     </row>
@@ -1280,15 +1282,15 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>20 to 28%</t>
+          <t>17 to 25%</t>
         </is>
       </c>
       <c r="C37" s="7" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>12 to 17</t>
+          <t>10 to 15</t>
         </is>
       </c>
       <c r="E37" s="7" t="n">
@@ -1303,15 +1305,15 @@
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>19 to 29%</t>
+          <t>16 to 26%</t>
         </is>
       </c>
       <c r="C38" s="7" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>11 to 17</t>
+          <t>10 to 16</t>
         </is>
       </c>
       <c r="E38" s="7" t="n">
@@ -1326,15 +1328,15 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>28 to 38%</t>
+          <t>24 to 34%</t>
         </is>
       </c>
       <c r="C39" s="7" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>17 to 23</t>
+          <t>14 to 20</t>
         </is>
       </c>
       <c r="E39" s="7" t="n">
@@ -1349,15 +1351,15 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>33 to 43%</t>
+          <t>30 to 40%</t>
         </is>
       </c>
       <c r="C40" s="7" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>20 to 26</t>
+          <t>18 to 24</t>
         </is>
       </c>
       <c r="E40" s="7" t="n">
@@ -1372,15 +1374,15 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>36 to 50%</t>
+          <t>32 to 46%</t>
         </is>
       </c>
       <c r="C41" s="7" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>22 to 30</t>
+          <t>19 to 28</t>
         </is>
       </c>
       <c r="E41" s="7" t="n">
@@ -1395,15 +1397,15 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>36 to 52%</t>
+          <t>32 to 48%</t>
         </is>
       </c>
       <c r="C42" s="7" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>22 to 31</t>
+          <t>19 to 29</t>
         </is>
       </c>
       <c r="E42" s="7" t="n">
@@ -1418,15 +1420,15 @@
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>40 to 52%</t>
+          <t>36 to 48%</t>
         </is>
       </c>
       <c r="C43" s="7" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>24 to 31</t>
+          <t>22 to 29</t>
         </is>
       </c>
       <c r="E43" s="7" t="n">
@@ -1441,15 +1443,15 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>44 to 56%</t>
+          <t>40 to 52%</t>
         </is>
       </c>
       <c r="C44" s="7" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>26 to 34</t>
+          <t>24 to 31</t>
         </is>
       </c>
       <c r="E44" s="7" t="n">
@@ -1464,15 +1466,15 @@
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>41 to 57%</t>
+          <t>38 to 54%</t>
         </is>
       </c>
       <c r="C45" s="7" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>25 to 34</t>
+          <t>23 to 32</t>
         </is>
       </c>
       <c r="E45" s="7" t="n">
@@ -1586,7 +1588,7 @@
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>L1 subtotal: fit 52.3%</t>
+          <t>L1 subtotal: fit 95.5%</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr"/>
@@ -1596,7 +1598,7 @@
       </c>
       <c r="G2" s="9" t="inlineStr"/>
       <c r="H2" s="10" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="I2" s="10" t="n">
         <v>44</v>
@@ -1635,7 +1637,7 @@
         <v>3</v>
       </c>
       <c r="G3" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3" s="7">
         <f>F3*G3</f>
@@ -1647,19 +1649,11 @@
       </c>
       <c r="J3" s="6" t="inlineStr">
         <is>
-          <t>Operations &gt; Clients (/agent/clientlisting); clients.test.js; addresses API (country, province, city, barangay, postal code)</t>
-        </is>
-      </c>
-      <c r="K3" s="6" t="inlineStr">
-        <is>
-          <t>Client is created at first policy issue. Location masters are labelled State and hold Metro Manila and selected areas, not the full PSGC list (in development).</t>
-        </is>
-      </c>
-      <c r="L3" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>Operations &gt; Clients &gt; Onboard client (/agent/clientlisting); modules/aml/kyc.js, modules/addresses; PSGC masters (migration 0250, seed 12_ph_geography.sql: 18 regions, 82 provinces, 1,642 cities and municipalities, barangays, ZIP codes); aml.test.js (client onboarding before the first policy), addresses.test.js, clients.test.js</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="inlineStr"/>
+      <c r="L3" s="7" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
@@ -1691,7 +1685,7 @@
         <v>2</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4" s="7">
         <f>F4*G4</f>
@@ -1703,14 +1697,10 @@
       </c>
       <c r="J4" s="6" t="inlineStr">
         <is>
-          <t>Prospects (corporate requires company name and TIN); leads.test.js</t>
-        </is>
-      </c>
-      <c r="K4" s="6" t="inlineStr">
-        <is>
-          <t>No structured authorised persons or board resolution record for juridical clients.</t>
-        </is>
-      </c>
+          <t>Onboard client &gt; Juridical (SEC, DTI or CDA registration, signatories with board resolution or secretary's certificate); table aml_client_signatories (migration 0260); aml.test.js (onboards a juridical client with registration, signatories, beneficial owners and the board resolution)</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr"/>
       <c r="L4" s="7" t="inlineStr"/>
     </row>
     <row r="5">
@@ -1742,7 +1732,7 @@
       <c r="F5" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G5" s="12" t="n">
+      <c r="G5" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H5" s="7">
@@ -1755,14 +1745,10 @@
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>Policy issue KYC (policy.kyc_required_fields, policy.kyc_id_types, modules/policies/kyc.js); policies.test.js</t>
-        </is>
-      </c>
-      <c r="K5" s="6" t="inlineStr">
-        <is>
-          <t>Required for motor by default; other lines by setting. The PH ID master list is in development (setting works today).</t>
-        </is>
-      </c>
+          <t>Onboard client &gt; Government ID presented (Government ID Type master, seed 69_ph_practice_masters.sql) and KYC documents upload; policy issue KYC (policy.kyc_required_fields, policy.kyc_id_types); aml.test.js, policies.test.js</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="inlineStr"/>
       <c r="L5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
@@ -1794,8 +1780,8 @@
       <c r="F6" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G6" s="13" t="n">
-        <v>0</v>
+      <c r="G6" s="11" t="n">
+        <v>2</v>
       </c>
       <c r="H6" s="7">
         <f>F6*G6</f>
@@ -1807,14 +1793,10 @@
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>None found in backend/src/modules</t>
-        </is>
-      </c>
-      <c r="K6" s="6" t="inlineStr">
-        <is>
-          <t>No customer risk rating, EDD workflow or periodic KYC refresh.</t>
-        </is>
-      </c>
+          <t>Compliance &gt; Client Due Diligence, EDD Reviews, KYC Refresh; modules/aml/risk.js (configurable factors and thresholds, aml.risk_low_max_score / risk_high_min_score, PEP always High), EDD review maker-checker, aml.block_issue_pending_edd, job aml-kyc-refresh-due; aml.test.js (risk-based CDD, EDD and KYC refresh)</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr"/>
       <c r="L6" s="7" t="inlineStr"/>
     </row>
     <row r="7">
@@ -1846,8 +1828,8 @@
       <c r="F7" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G7" s="13" t="n">
-        <v>0</v>
+      <c r="G7" s="11" t="n">
+        <v>2</v>
       </c>
       <c r="H7" s="7">
         <f>F7*G7</f>
@@ -1859,14 +1841,10 @@
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>None found</t>
-        </is>
-      </c>
-      <c r="K7" s="6" t="inlineStr">
-        <is>
-          <t>No beneficial owner capture.</t>
-        </is>
-      </c>
+          <t>Onboard client &gt; Add beneficial owner (aml.beneficial_owner_threshold 25%, senior managing official fallback); table aml_beneficial_owners (migration 0260); owners screened with the client; aml.test.js</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr"/>
       <c r="L7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
@@ -1898,8 +1876,8 @@
       <c r="F8" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G8" s="13" t="n">
-        <v>0</v>
+      <c r="G8" s="11" t="n">
+        <v>2</v>
       </c>
       <c r="H8" s="7">
         <f>F8*G8</f>
@@ -1911,12 +1889,12 @@
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>None found (grep sanction/PEP returns nothing)</t>
+          <t>Compliance &gt; Screening Lists (UN consolidated XML, AMLC and ATC designations, PEP, internal negative list, versioned uploads with rescreen), Screening Hits (clear, escalate, confirm); modules/aml/screening.js, matching.js, providers.js (uploaded lists, test provider, provider API with retry job aml-provider-retry); screening at onboarding, policy issue, list update, refund approval and claim payment (aml.screening_block_events); aml.test.js (sanctions, PEP and negative list screening)</t>
         </is>
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
-          <t>No screening at onboarding or at payment.</t>
+          <t>No list content is delivered: the broker loads the UN, AMLC and PEP lists it is entitled to use. A commercial screening provider, when used, is connected through the provider adapter and certified with that provider.</t>
         </is>
       </c>
       <c r="L8" s="7" t="inlineStr"/>
@@ -1950,8 +1928,8 @@
       <c r="F9" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G9" s="13" t="n">
-        <v>0</v>
+      <c r="G9" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="H9" s="7">
         <f>F9*G9</f>
@@ -1963,12 +1941,12 @@
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>Receipts Register, Collection Report give transaction data only (compliance matrix, AMLA chapter)</t>
+          <t>Compliance &gt; Transaction Alerts (six rules, job aml-transaction-monitoring), AML Cases (STR and CTR cases, due dates in working days), AMLC Reports (CTR and STR files, filing record); modules/aml/monitoring.js, cases.js, reports.js; aml.test.js (covered and suspicious transactions, cases and AMLC reports)</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>No threshold rules, alert queue or AMLC reporting file.</t>
+          <t>Monitoring, alerts and cases are delivered end to end. The report file is the product's own layout BV-AMLC-TXN 1.0 built after the AMLC reporting guidelines; the institution code, transaction codes, ID type codes and field order must be confirmed against the AMLC's current guidelines and a test file validated in the AMLC portal before the first filing. Scored 1 until that confirmation.</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr"/>
@@ -2002,7 +1980,7 @@
       <c r="F10" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="12" t="n">
+      <c r="G10" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H10" s="7">
@@ -2015,7 +1993,7 @@
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>Business records never deleted by housekeeping; privacy.retention_years 10; privacy.test.js</t>
+          <t>aml.record_retention_years (5) blocks anonymisation; privacy.retention_years 10; business records never deleted by housekeeping; aml.test.js (keeps AML records for 5 years), privacy.test.js</t>
         </is>
       </c>
       <c r="K10" s="6" t="inlineStr"/>
@@ -2050,7 +2028,7 @@
       <c r="F11" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="G11" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H11" s="7">
@@ -2063,7 +2041,7 @@
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>Clients &gt; client view tabs; clients.test.js; UAT scenario retail and corporate phases</t>
+          <t>Clients &gt; client view tabs Policy, Claim, Renewal, Endorsement, Data privacy, Activities, Identification and due diligence; clients.test.js; UAT scenario retail and corporate phases</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr"/>
@@ -2098,7 +2076,7 @@
       <c r="F12" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G12" s="12" t="n">
+      <c r="G12" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H12" s="7">
@@ -2111,7 +2089,7 @@
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>Data privacy tab on client and prospect; Master &gt; Data Privacy &gt; Consent Register; privacy.test.js</t>
+          <t>Data privacy tab on client and prospect; Master &gt; Data Privacy &gt; Consent Register; consent checked by campaigns and SMS; privacy.test.js, campaigns.test.js, integrations.test.js</t>
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr"/>
@@ -2130,7 +2108,7 @@
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>L1 subtotal: fit 65.4%</t>
+          <t>L1 subtotal: fit 100.0%</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr"/>
@@ -2140,7 +2118,7 @@
       </c>
       <c r="G13" s="9" t="inlineStr"/>
       <c r="H13" s="10" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="I13" s="10" t="n">
         <v>26</v>
@@ -2178,7 +2156,7 @@
       <c r="F14" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G14" s="12" t="n">
+      <c r="G14" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H14" s="7">
@@ -2226,7 +2204,7 @@
       <c r="F15" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G15" s="12" t="n">
+      <c r="G15" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H15" s="7">
@@ -2239,7 +2217,7 @@
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>Lead statuses New to Converted or Lost; Lead Conversion Funnel report; reports.test.js</t>
+          <t>Lead statuses New to Converted or Lost (a first activity moves New to Contacted); Lead Conversion Funnel report; reports.test.js, sales-activities.test.js</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr"/>
@@ -2274,8 +2252,8 @@
       <c r="F16" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G16" s="13" t="n">
-        <v>0</v>
+      <c r="G16" s="11" t="n">
+        <v>2</v>
       </c>
       <c r="H16" s="7">
         <f>F16*G16</f>
@@ -2287,19 +2265,11 @@
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>No activity log on leads (modules/leads); My Work inbox in development</t>
-        </is>
-      </c>
-      <c r="K16" s="6" t="inlineStr">
-        <is>
-          <t>Account executives cannot log activities or schedule follow-ups on a prospect.</t>
-        </is>
-      </c>
-      <c r="L16" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>Activities timeline on prospect, client and quotation (Log activity); Sales &amp; Marketing &gt; Sales Activities (/sales/activities) with the Activity Report; Master &gt; Organization &gt; Sales Activity Types and Outcomes; next step becomes a My Work task; modules/sales-activities (migration 0320); sales-activities.test.js</t>
+        </is>
+      </c>
+      <c r="K16" s="6" t="inlineStr"/>
+      <c r="L16" s="7" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
@@ -2331,7 +2301,7 @@
         <v>2</v>
       </c>
       <c r="G17" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17" s="7">
         <f>F17*G17</f>
@@ -2343,14 +2313,10 @@
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>Record scope for scoped roles (security.scoped_roles); scope.test.js</t>
-        </is>
-      </c>
-      <c r="K17" s="6" t="inlineStr">
-        <is>
-          <t>Owner scoping exists; no assignment rules, reassignment queue or team view.</t>
-        </is>
-      </c>
+          <t>Sales &amp; Marketing &gt; Lead Assignment (/sales/lead-assignment): Team View by reporting line, Queue with bulk reassignment, Assignment Rules (round robin, fewest open, fixed); modules/leads (migration 0300); lead-assignment.test.js; My Work &gt; My Team</t>
+        </is>
+      </c>
+      <c r="K17" s="6" t="inlineStr"/>
       <c r="L17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
@@ -2382,7 +2348,7 @@
       <c r="F18" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G18" s="12" t="n">
+      <c r="G18" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H18" s="7">
@@ -2431,7 +2397,7 @@
         <v>2</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H19" s="7">
         <f>F19*G19</f>
@@ -2443,14 +2409,10 @@
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>Commission &gt; Agents/Referrer Accounts (types Agent, Sub-agent, External); commission.test.js</t>
-        </is>
-      </c>
-      <c r="K19" s="6" t="inlineStr">
-        <is>
-          <t>No dealer or dealer-branch master, channel hierarchy or dealer production report.</t>
-        </is>
-      </c>
+          <t>Master &gt; Insurance Management &gt; Distribution Channels (dealers with branches, financing banks with mortgagee clause, affinity partners; migration 0301); Sales &amp; Marketing &gt; Dealer Programmes; Reports &gt; Dealer Production; distribution-channels.test.js, motor-programmes.test.js</t>
+        </is>
+      </c>
+      <c r="K19" s="6" t="inlineStr"/>
       <c r="L19" s="7" t="inlineStr"/>
     </row>
     <row r="20">
@@ -2483,7 +2445,7 @@
         <v>1</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" s="7">
         <f>F20*G20</f>
@@ -2495,14 +2457,10 @@
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>Marketing consent per purpose; Renewals &gt; Lapse Management win-back campaigns</t>
-        </is>
-      </c>
-      <c r="K20" s="6" t="inlineStr">
-        <is>
-          <t>No general campaign or mass mailing module.</t>
-        </is>
-      </c>
+          <t>Sales &amp; Marketing &gt; Campaigns (/sales/campaigns): segments, templates, send through the e-mail outbox, opt-out link to the consent register, results; job campaign-dispatch; modules/campaigns (migration 0307); campaigns.test.js</t>
+        </is>
+      </c>
+      <c r="K20" s="6" t="inlineStr"/>
       <c r="L20" s="7" t="inlineStr"/>
     </row>
     <row r="21">
@@ -2518,7 +2476,7 @@
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>L1 subtotal: fit 89.6%</t>
+          <t>L1 subtotal: fit 100.0%</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr"/>
@@ -2528,7 +2486,7 @@
       </c>
       <c r="G21" s="9" t="inlineStr"/>
       <c r="H21" s="10" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I21" s="10" t="n">
         <v>48</v>
@@ -2566,7 +2524,7 @@
       <c r="F22" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G22" s="12" t="n">
+      <c r="G22" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H22" s="7">
@@ -2614,7 +2572,7 @@
       <c r="F23" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G23" s="12" t="n">
+      <c r="G23" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H23" s="7">
@@ -2663,7 +2621,7 @@
         <v>2</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H24" s="7">
         <f>F24*G24</f>
@@ -2675,19 +2633,11 @@
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>Market comparison table on slip PDFs (modules/documents/templates.js)</t>
-        </is>
-      </c>
-      <c r="K24" s="6" t="inlineStr">
-        <is>
-          <t>Printable comparison report for the client is in development.</t>
-        </is>
-      </c>
-      <c r="L24" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>Sales &amp; Marketing &gt; Comparison Reports (/sales/comparison-reports): prepared from RFQ offers or quotations, recommendation and reasons, branded PDF without commission, e-mailed through the outbox, client's choice recorded; modules/comparison-reports (migration 0306, series CMP); comparison-reports.test.js</t>
+        </is>
+      </c>
+      <c r="K24" s="6" t="inlineStr"/>
+      <c r="L24" s="7" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
@@ -2718,7 +2668,7 @@
       <c r="F25" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G25" s="12" t="n">
+      <c r="G25" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H25" s="7">
@@ -2766,7 +2716,7 @@
       <c r="F26" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G26" s="12" t="n">
+      <c r="G26" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H26" s="7">
@@ -2814,7 +2764,7 @@
       <c r="F27" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G27" s="12" t="n">
+      <c r="G27" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H27" s="7">
@@ -2862,7 +2812,7 @@
       <c r="F28" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G28" s="12" t="n">
+      <c r="G28" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H28" s="7">
@@ -2910,7 +2860,7 @@
       <c r="F29" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G29" s="12" t="n">
+      <c r="G29" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H29" s="7">
@@ -2928,7 +2878,7 @@
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>Approval through the live e-mail link blocked in the test environment (no SMTP); recorded responses tested.</t>
+          <t>Approval through the live e-mail link is exercised with the recorded responses in the test environment (no SMTP).</t>
         </is>
       </c>
       <c r="L29" s="7" t="inlineStr"/>
@@ -2962,7 +2912,7 @@
       <c r="F30" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G30" s="12" t="n">
+      <c r="G30" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H30" s="7">
@@ -3011,7 +2961,7 @@
         <v>1</v>
       </c>
       <c r="G31" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" s="7">
         <f>F31*G31</f>
@@ -3023,19 +2973,15 @@
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>Approval link records acceptance; Signatories master</t>
+          <t>My Profile &gt; My e-signature (captured with consent, versioned); Master &gt; System Settings &gt; Theme and Branding &gt; document signature slots print the signatures on issued documents (drafts carry UNSIGNED DRAFT); client acceptance recorded through the signed approval link; modules/e-signatures (migration 0254); branding.test.js (e-signatures), customer-response.test.js</t>
         </is>
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>E-signature on documents is in development.</t>
-        </is>
-      </c>
-      <c r="L31" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>The client's acceptance is recorded by the signed link and the comparison report's recorded choice, not by a drawn signature of the client.</t>
+        </is>
+      </c>
+      <c r="L31" s="7" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
@@ -3067,7 +3013,7 @@
         <v>2</v>
       </c>
       <c r="G32" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H32" s="7">
         <f>F32*G32</f>
@@ -3079,19 +3025,11 @@
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>Product Configurator &gt; Product Templates (MOT-003-2025 CTPL and APPA tariff used); product-configurator.test.js</t>
-        </is>
-      </c>
-      <c r="K32" s="6" t="inlineStr">
-        <is>
-          <t>Only the motor tariff feeds quotations; coverage, acceptance and document rules are not yet connected (in development).</t>
-        </is>
-      </c>
-      <c r="L32" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>Quotation wizard takes the covers of the Coverage Builder and the risk fields of the acceptance rules and rating factors of the governing template (motor.pricing_template_code); referrals to the rule's authority, loadings, market mapping on RFQ, document templates with merge fields; modules/product-configurator, modules/quotations (migrations 0252, 0322); quote-covers-risk-fields.test.js, product-rules-in-flow.test.js</t>
+        </is>
+      </c>
+      <c r="K32" s="6" t="inlineStr"/>
+      <c r="L32" s="7" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
@@ -3106,7 +3044,7 @@
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>L1 subtotal: fit 84.8%</t>
+          <t>L1 subtotal: fit 100.0%</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr"/>
@@ -3116,7 +3054,7 @@
       </c>
       <c r="G33" s="9" t="inlineStr"/>
       <c r="H33" s="10" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="I33" s="10" t="n">
         <v>46</v>
@@ -3154,7 +3092,7 @@
       <c r="F34" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G34" s="12" t="n">
+      <c r="G34" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H34" s="7">
@@ -3202,7 +3140,7 @@
       <c r="F35" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G35" s="12" t="n">
+      <c r="G35" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H35" s="7">
@@ -3250,7 +3188,7 @@
       <c r="F36" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G36" s="12" t="n">
+      <c r="G36" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H36" s="7">
@@ -3298,7 +3236,7 @@
       <c r="F37" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G37" s="12" t="n">
+      <c r="G37" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H37" s="7">
@@ -3346,7 +3284,7 @@
       <c r="F38" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G38" s="12" t="n">
+      <c r="G38" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H38" s="7">
@@ -3394,7 +3332,7 @@
       <c r="F39" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G39" s="12" t="n">
+      <c r="G39" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H39" s="7">
@@ -3442,8 +3380,8 @@
       <c r="F40" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G40" s="13" t="n">
-        <v>0</v>
+      <c r="G40" s="11" t="n">
+        <v>2</v>
       </c>
       <c r="H40" s="7">
         <f>F40*G40</f>
@@ -3455,14 +3393,10 @@
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
-          <t>None found (grep cover note / binder returns nothing)</t>
-        </is>
-      </c>
-      <c r="K40" s="6" t="inlineStr">
-        <is>
-          <t>No cover note document or temporary cover record.</t>
-        </is>
-      </c>
+          <t>Operations &gt; Cover Notes (/operations/cover-notes): issued from an accepted quotation or a sent or bound placement slip, CVN series, letterhead print, e-mail, superseded by the policy, daily expiry job; modules/cover-notes (migration 0290); ops-accounting.test.js (cover notes)</t>
+        </is>
+      </c>
+      <c r="K40" s="6" t="inlineStr"/>
       <c r="L40" s="7" t="inlineStr"/>
     </row>
     <row r="41">
@@ -3495,7 +3429,7 @@
         <v>2</v>
       </c>
       <c r="G41" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H41" s="7">
         <f>F41*G41</f>
@@ -3507,19 +3441,15 @@
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>Master &gt; Generals &gt; Insurance Management &gt; Insurance Company</t>
+          <t>Insurance Company master fields IC Certificate of Authority No. and Valid Until (IC non-life insurer list seeded, 69_ph_practice_masters.sql); Compliance &gt; Insurance Commission &gt; Insurer Authority; check at RFQ, firm order and policy issue (compliance.insurer_authority_check warn or block, migration 0271); ic-compliance.test.js (insurers authorised by the IC)</t>
         </is>
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>No certificate of authority number or expiry check; IC non-life insurer list is in development.</t>
-        </is>
-      </c>
-      <c r="L41" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>Delivered as warn: the broker enters the certificate numbers of the insurers it works with, then switches the setting to block.</t>
+        </is>
+      </c>
+      <c r="L41" s="7" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
@@ -3551,7 +3481,7 @@
         <v>1</v>
       </c>
       <c r="G42" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H42" s="7">
         <f>F42*G42</f>
@@ -3563,14 +3493,10 @@
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
-          <t>Reinsurance &gt; Treaty Dashboard, Cession Tracking; reinsurance.test.js</t>
-        </is>
-      </c>
-      <c r="K42" s="6" t="inlineStr">
-        <is>
-          <t>The module records treaties and cessions from the cedant side; there is no facultative reinsurance slip workflow.</t>
-        </is>
-      </c>
+          <t>Reinsurance &gt; Facultative Placements (/reinsurance/facultative): slip for the cedant, sent to reinsurers, lines accepted to 100%, binding books premium due, net due to reinsurers and brokerage, settlements, bordereau; modules/reinsurance (migration 0305); facultative-reinsurance.test.js</t>
+        </is>
+      </c>
+      <c r="K42" s="6" t="inlineStr"/>
       <c r="L42" s="7" t="inlineStr"/>
     </row>
     <row r="43">
@@ -3602,7 +3528,7 @@
       <c r="F43" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G43" s="12" t="n">
+      <c r="G43" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H43" s="7">
@@ -3634,7 +3560,7 @@
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>L1 subtotal: fit 83.3%</t>
+          <t>L1 subtotal: fit 100.0%</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr"/>
@@ -3644,7 +3570,7 @@
       </c>
       <c r="G44" s="9" t="inlineStr"/>
       <c r="H44" s="10" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="I44" s="10" t="n">
         <v>54</v>
@@ -3682,7 +3608,7 @@
       <c r="F45" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G45" s="12" t="n">
+      <c r="G45" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H45" s="7">
@@ -3730,7 +3656,7 @@
       <c r="F46" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G46" s="12" t="n">
+      <c r="G46" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H46" s="7">
@@ -3778,7 +3704,7 @@
       <c r="F47" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G47" s="12" t="n">
+      <c r="G47" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H47" s="7">
@@ -3791,7 +3717,7 @@
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>Policy issued e-mail with schedule PDF; printing.test.js; email-documents.test.js</t>
+          <t>Policy issued e-mail with schedule PDF on the branded letterhead; product document templates with merge fields (Product Configurator &gt; Document Manager); printing.test.js; email-documents.test.js; product-rules-in-flow.test.js; branding.test.js</t>
         </is>
       </c>
       <c r="K47" s="6" t="inlineStr"/>
@@ -3826,7 +3752,7 @@
       <c r="F48" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G48" s="12" t="n">
+      <c r="G48" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H48" s="7">
@@ -3874,7 +3800,7 @@
       <c r="F49" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G49" s="12" t="n">
+      <c r="G49" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H49" s="7">
@@ -3922,7 +3848,7 @@
       <c r="F50" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G50" s="12" t="n">
+      <c r="G50" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H50" s="7">
@@ -3971,7 +3897,7 @@
         <v>3</v>
       </c>
       <c r="G51" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H51" s="7">
         <f>F51*G51</f>
@@ -3983,12 +3909,12 @@
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
-          <t>Policy fields Cert Number and Authen Code (recorded by hand)</t>
+          <t>Operations &gt; CTPL Authentication (/operations/ctpl-authentication): COC series per insurer, COC number allocated at issue, authentication request through connector CTPL_AUTH (test mode delivered), code printed on the schedule, keyed-in code as fallback, LTO_FEED connector, unauthenticated report; outbox with retry (Master &gt; Integrations); modules/integrations/ctpl.js (migration 0312); integrations.test.js (CTPL authentication)</t>
         </is>
       </c>
       <c r="K51" s="6" t="inlineStr">
         <is>
-          <t>No integration with the authentication provider or LTO; done in the insurer or government portal.</t>
+          <t>Certification that remains with the partner: the accredited provider's acceptance of the live requests and, where the provider does not transmit to the LTO, the LTO interface. Until then the keyed-in code from the provider portal is the fallback.</t>
         </is>
       </c>
       <c r="L51" s="7" t="inlineStr"/>
@@ -4023,7 +3949,7 @@
         <v>2</v>
       </c>
       <c r="G52" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H52" s="7">
         <f>F52*G52</f>
@@ -4035,14 +3961,10 @@
       </c>
       <c r="J52" s="6" t="inlineStr">
         <is>
-          <t>Mortgagee field on motor policy; 3-year CTPL for brand-new vehicles</t>
-        </is>
-      </c>
-      <c r="K52" s="6" t="inlineStr">
-        <is>
-          <t>No dealer or financing-bank programme set-up, bulk dealer upload or bank endorsement letters.</t>
-        </is>
-      </c>
+          <t>Sales &amp; Marketing &gt; Dealer Programmes (/sales/dealer-programmes): programme terms, who pays, Dealer Sales upload creating prospect, quotation and policy per sale, bank endorsement letter printed and e-mailed; modules/motor-programmes (migration 0302); motor-programmes.test.js</t>
+        </is>
+      </c>
+      <c r="K52" s="6" t="inlineStr"/>
       <c r="L52" s="7" t="inlineStr"/>
     </row>
     <row r="53">
@@ -4075,7 +3997,7 @@
         <v>2</v>
       </c>
       <c r="G53" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H53" s="7">
         <f>F53*G53</f>
@@ -4087,14 +4009,10 @@
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>Policy bulk upload for new business and in-force book; upload-templates.test.js</t>
-        </is>
-      </c>
-      <c r="K53" s="6" t="inlineStr">
-        <is>
-          <t>No fleet schedule with per-vehicle premium inside one policy.</t>
-        </is>
-      </c>
+          <t>Operations &gt; Fleet Schedules (/operations/fleet-schedules): per-vehicle pricing, Fleet Vehicles upload, one policy for the total, vehicles added or deleted by endorsement pro-rata, schedule print; modules/fleet (migration 0303); fleet-schedules.test.js; policy bulk upload for the in-force book (upload-templates.test.js)</t>
+        </is>
+      </c>
+      <c r="K53" s="6" t="inlineStr"/>
       <c r="L53" s="7" t="inlineStr"/>
     </row>
     <row r="54">
@@ -4126,7 +4044,7 @@
       <c r="F54" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G54" s="12" t="n">
+      <c r="G54" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H54" s="7">
@@ -4174,8 +4092,8 @@
       <c r="F55" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G55" s="13" t="n">
-        <v>0</v>
+      <c r="G55" s="11" t="n">
+        <v>2</v>
       </c>
       <c r="H55" s="7">
         <f>F55*G55</f>
@@ -4187,14 +4105,10 @@
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
-          <t>None found</t>
-        </is>
-      </c>
-      <c r="K55" s="6" t="inlineStr">
-        <is>
-          <t>No open cover or declaration processing.</t>
-        </is>
-      </c>
+          <t>Operations &gt; Marine Open Covers (/operations/open-covers): contract with rates and limits per conveyance, open policy, certificates with mark-up and minimum premium, monthly declaration billed on the open policy; modules/marine (migration 0304); marine-open-cover.test.js</t>
+        </is>
+      </c>
+      <c r="K55" s="6" t="inlineStr"/>
       <c r="L55" s="7" t="inlineStr"/>
     </row>
     <row r="56">
@@ -4210,7 +4124,7 @@
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>L1 subtotal: fit 81.6%</t>
+          <t>L1 subtotal: fit 100.0%</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr"/>
@@ -4220,7 +4134,7 @@
       </c>
       <c r="G56" s="9" t="inlineStr"/>
       <c r="H56" s="10" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="I56" s="10" t="n">
         <v>38</v>
@@ -4258,7 +4172,7 @@
       <c r="F57" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G57" s="12" t="n">
+      <c r="G57" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H57" s="7">
@@ -4306,7 +4220,7 @@
       <c r="F58" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G58" s="12" t="n">
+      <c r="G58" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H58" s="7">
@@ -4354,7 +4268,7 @@
       <c r="F59" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G59" s="12" t="n">
+      <c r="G59" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H59" s="7">
@@ -4403,7 +4317,7 @@
         <v>3</v>
       </c>
       <c r="G60" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H60" s="7">
         <f>F60*G60</f>
@@ -4415,14 +4329,10 @@
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
-          <t>Cancellation endorsement (cancellationType); endorsements.test.js; package sections pro rata (packages.endorsement_prorata)</t>
-        </is>
-      </c>
-      <c r="K60" s="6" t="inlineStr">
-        <is>
-          <t>For regular policies the return premium of a cancellation is entered by the user, not computed from days left.</t>
-        </is>
-      </c>
+          <t>Operations &gt; Policy Cancellation (/operations/policy-cancellation): return premium computed on the server from the days left (pro-rata, short-period or flat by cancellation reason), taxes returned per endorsements.cancellation_returned_taxes, commission clawback, partial cancellation; modules/cancellations (migration 0291); ops-accounting.test.js (cancellation return premium)</t>
+        </is>
+      </c>
+      <c r="K60" s="6" t="inlineStr"/>
       <c r="L60" s="7" t="inlineStr"/>
     </row>
     <row r="61">
@@ -4454,8 +4364,8 @@
       <c r="F61" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G61" s="13" t="n">
-        <v>0</v>
+      <c r="G61" s="11" t="n">
+        <v>2</v>
       </c>
       <c r="H61" s="7">
         <f>F61*G61</f>
@@ -4467,14 +4377,10 @@
       </c>
       <c r="J61" s="6" t="inlineStr">
         <is>
-          <t>None found (grep short period returns nothing)</t>
-        </is>
-      </c>
-      <c r="K61" s="6" t="inlineStr">
-        <is>
-          <t>No short-period table or computation.</t>
-        </is>
-      </c>
+          <t>Master &gt; Insurance Management &gt; Short-Period Rates (/master/insurance/short-period-rates) and Cancellation Reasons; endorsements.short_period_for_insured; ops-accounting.test.js (short-period scale)</t>
+        </is>
+      </c>
+      <c r="K61" s="6" t="inlineStr"/>
       <c r="L61" s="7" t="inlineStr"/>
     </row>
     <row r="62">
@@ -4506,7 +4412,7 @@
       <c r="F62" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G62" s="12" t="n">
+      <c r="G62" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H62" s="7">
@@ -4554,7 +4460,7 @@
       <c r="F63" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G63" s="12" t="n">
+      <c r="G63" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H63" s="7">
@@ -4602,7 +4508,7 @@
       <c r="F64" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G64" s="12" t="n">
+      <c r="G64" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H64" s="7">
@@ -4634,7 +4540,7 @@
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>L1 subtotal: fit 91.7%</t>
+          <t>L1 subtotal: fit 100.0%</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr"/>
@@ -4644,7 +4550,7 @@
       </c>
       <c r="G65" s="9" t="inlineStr"/>
       <c r="H65" s="10" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I65" s="10" t="n">
         <v>24</v>
@@ -4682,7 +4588,7 @@
       <c r="F66" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G66" s="12" t="n">
+      <c r="G66" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H66" s="7">
@@ -4730,7 +4636,7 @@
       <c r="F67" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G67" s="12" t="n">
+      <c r="G67" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H67" s="7">
@@ -4778,7 +4684,7 @@
       <c r="F68" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G68" s="12" t="n">
+      <c r="G68" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H68" s="7">
@@ -4826,7 +4732,7 @@
       <c r="F69" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G69" s="12" t="n">
+      <c r="G69" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H69" s="7">
@@ -4874,7 +4780,7 @@
       <c r="F70" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G70" s="12" t="n">
+      <c r="G70" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H70" s="7">
@@ -4922,8 +4828,8 @@
       <c r="F71" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G71" s="13" t="n">
-        <v>0</v>
+      <c r="G71" s="11" t="n">
+        <v>2</v>
       </c>
       <c r="H71" s="7">
         <f>F71*G71</f>
@@ -4935,12 +4841,12 @@
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
-          <t>E-mail and in-app only (product functionality checklist item 59)</t>
+          <t>Master &gt; System Configuration &gt; Message Templates (RENEWAL_NOTICE, PAYMENT_REMINDER, CLAIM_UPDATE, Viber variant) with consent check; connectors SMS_SEMAPHORE (test mode delivered), SMS_GLOBE_LABS, SMS_GENERIC, VIBER_BUSINESS; jobs sms-renewal-notices and sms-payment-reminders; outbox with retry; modules/integrations/messaging.js (migration 0311); integrations.test.js (messaging)</t>
         </is>
       </c>
       <c r="K71" s="6" t="inlineStr">
         <is>
-          <t>No SMS or Viber gateway.</t>
+          <t>Certification that remains with the partner: the SMS gateway contract, sender name or short code and the live credentials; the jobs are delivered switched off until the connector is live.</t>
         </is>
       </c>
       <c r="L71" s="7" t="inlineStr"/>
@@ -4958,7 +4864,7 @@
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>L1 subtotal: fit 89.3%</t>
+          <t>L1 subtotal: fit 100.0%</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr"/>
@@ -4968,7 +4874,7 @@
       </c>
       <c r="G72" s="9" t="inlineStr"/>
       <c r="H72" s="10" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="I72" s="10" t="n">
         <v>56</v>
@@ -5006,7 +4912,7 @@
       <c r="F73" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G73" s="12" t="n">
+      <c r="G73" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H73" s="7">
@@ -5054,7 +4960,7 @@
       <c r="F74" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G74" s="12" t="n">
+      <c r="G74" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H74" s="7">
@@ -5102,7 +5008,7 @@
       <c r="F75" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G75" s="12" t="n">
+      <c r="G75" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H75" s="7">
@@ -5150,7 +5056,7 @@
       <c r="F76" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G76" s="12" t="n">
+      <c r="G76" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H76" s="7">
@@ -5163,7 +5069,7 @@
       </c>
       <c r="J76" s="6" t="inlineStr">
         <is>
-          <t>Master &gt; Document Numbering (61 series); numbering.test.js; printing.test.js</t>
+          <t>Master &gt; Document Numbering; numbering.test.js; printing.test.js; receipts.document_title</t>
         </is>
       </c>
       <c r="K76" s="6" t="inlineStr"/>
@@ -5198,7 +5104,7 @@
       <c r="F77" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G77" s="12" t="n">
+      <c r="G77" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H77" s="7">
@@ -5211,7 +5117,7 @@
       </c>
       <c r="J77" s="6" t="inlineStr">
         <is>
-          <t>Bank transaction types; receipts.test.js; bank-reconciliation.test.js</t>
+          <t>Bank transaction types; receipts.test.js; bank-reconciliation.test.js; post-dated cheque bounce (ops-accounting.test.js)</t>
         </is>
       </c>
       <c r="K77" s="6" t="inlineStr"/>
@@ -5246,7 +5152,7 @@
       <c r="F78" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G78" s="12" t="n">
+      <c r="G78" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H78" s="7">
@@ -5264,7 +5170,7 @@
       </c>
       <c r="K78" s="6" t="inlineStr">
         <is>
-          <t>Tested with the sandbox provider only; live keys are a go-live task.</t>
+          <t>Tested with the sandbox provider; live keys are a go-live task.</t>
         </is>
       </c>
       <c r="L78" s="7" t="inlineStr"/>
@@ -5298,7 +5204,7 @@
       <c r="F79" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G79" s="12" t="n">
+      <c r="G79" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H79" s="7">
@@ -5346,7 +5252,7 @@
       <c r="F80" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G80" s="12" t="n">
+      <c r="G80" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H80" s="7">
@@ -5395,7 +5301,7 @@
         <v>2</v>
       </c>
       <c r="G81" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H81" s="7">
         <f>F81*G81</f>
@@ -5407,14 +5313,10 @@
       </c>
       <c r="J81" s="6" t="inlineStr">
         <is>
-          <t>Accounts &gt; Credit Control &gt; Instalment Plans; credit-control.test.js</t>
-        </is>
-      </c>
-      <c r="K81" s="6" t="inlineStr">
-        <is>
-          <t>Plans split the follow-up of a bill without changing the ledger; no invoice per instalment.</t>
-        </is>
-      </c>
+          <t>Accounts &gt; Credit Control &gt; Instalment Plans &gt; Issue instalment invoices (credit.instalment_invoices_on_save): one bill per instalment with its own invoice number, due date, journal and collection item; migration 0293; ops-accounting.test.js (separate instalment invoices); credit-control.test.js</t>
+        </is>
+      </c>
+      <c r="K81" s="6" t="inlineStr"/>
       <c r="L81" s="7" t="inlineStr"/>
     </row>
     <row r="82">
@@ -5446,7 +5348,7 @@
       <c r="F82" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G82" s="12" t="n">
+      <c r="G82" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H82" s="7">
@@ -5494,7 +5396,7 @@
       <c r="F83" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G83" s="12" t="n">
+      <c r="G83" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H83" s="7">
@@ -5507,7 +5409,7 @@
       </c>
       <c r="J83" s="6" t="inlineStr">
         <is>
-          <t>Collection items; collections.test.js</t>
+          <t>Collection items; promise to pay becomes a My Work task; collections.test.js; my-work.test.js</t>
         </is>
       </c>
       <c r="K83" s="6" t="inlineStr"/>
@@ -5542,8 +5444,8 @@
       <c r="F84" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G84" s="13" t="n">
-        <v>0</v>
+      <c r="G84" s="11" t="n">
+        <v>2</v>
       </c>
       <c r="H84" s="7">
         <f>F84*G84</f>
@@ -5555,14 +5457,10 @@
       </c>
       <c r="J84" s="6" t="inlineStr">
         <is>
-          <t>Not found as a register (cheque date handling in disbursements only)</t>
-        </is>
-      </c>
-      <c r="K84" s="6" t="inlineStr">
-        <is>
-          <t>Post-dated cheques received from clients are not tracked until deposit.</t>
-        </is>
-      </c>
+          <t>Accounts &gt; Post-Dated Cheques (/accounts/post-dated-cheques): register against a bill, deposit due tab and daily job, deposit posts the receipt, cleared, bounced (receipt cancelled, client e-mailed), replace, return; modules/pdc (migration 0292); ops-accounting.test.js (post-dated cheque register)</t>
+        </is>
+      </c>
+      <c r="K84" s="6" t="inlineStr"/>
       <c r="L84" s="7" t="inlineStr"/>
     </row>
     <row r="85">
@@ -5578,7 +5476,7 @@
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>L1 subtotal: fit 83.3%</t>
+          <t>L1 subtotal: fit 100.0%</t>
         </is>
       </c>
       <c r="D85" s="9" t="inlineStr"/>
@@ -5588,7 +5486,7 @@
       </c>
       <c r="G85" s="9" t="inlineStr"/>
       <c r="H85" s="10" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I85" s="10" t="n">
         <v>36</v>
@@ -5626,7 +5524,7 @@
       <c r="F86" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G86" s="12" t="n">
+      <c r="G86" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H86" s="7">
@@ -5674,7 +5572,7 @@
       <c r="F87" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G87" s="12" t="n">
+      <c r="G87" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H87" s="7">
@@ -5722,7 +5620,7 @@
       <c r="F88" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G88" s="12" t="n">
+      <c r="G88" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H88" s="7">
@@ -5770,8 +5668,8 @@
       <c r="F89" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G89" s="13" t="n">
-        <v>0</v>
+      <c r="G89" s="11" t="n">
+        <v>2</v>
       </c>
       <c r="H89" s="7">
         <f>F89*G89</f>
@@ -5783,12 +5681,12 @@
       </c>
       <c r="J89" s="6" t="inlineStr">
         <is>
-          <t>Transfers recorded only (checklist item 58)</t>
+          <t>Accounts &gt; Bank Payment Files (/accounts/bank-payment-files): batch of approved vouchers, maker-checker within the Authority Matrix, file written from Master &gt; Finance &gt; Bank File Layouts (delimited or fixed width; starter layouts BDO, BPI, Metrobank, Landbank, UnionBank, generic CSV), status file import or Record result, payment journals; payee bank accounts; connector BANK_FILES with outbox and inbox; modules/integrations/bankfiles (migration 0314); integrations.test.js (bank payment files)</t>
         </is>
       </c>
       <c r="K89" s="6" t="inlineStr">
         <is>
-          <t>No bank upload file; payments keyed in the bank portal.</t>
+          <t>Certification that remains with the partner: each bank validates the layout against its current file specification and accepts a test file during onboarding; the starter layouts are marked Test mode until then. Record result is the manual fallback.</t>
         </is>
       </c>
       <c r="L89" s="7" t="inlineStr"/>
@@ -5822,7 +5720,7 @@
       <c r="F90" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G90" s="12" t="n">
+      <c r="G90" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H90" s="7">
@@ -5870,7 +5768,7 @@
       <c r="F91" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G91" s="12" t="n">
+      <c r="G91" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H91" s="7">
@@ -5918,7 +5816,7 @@
       <c r="F92" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G92" s="12" t="n">
+      <c r="G92" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H92" s="7">
@@ -5966,8 +5864,8 @@
       <c r="F93" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G93" s="13" t="n">
-        <v>0</v>
+      <c r="G93" s="11" t="n">
+        <v>2</v>
       </c>
       <c r="H93" s="7">
         <f>F93*G93</f>
@@ -5979,12 +5877,12 @@
       </c>
       <c r="J93" s="6" t="inlineStr">
         <is>
-          <t>Files and e-mail only (checklist item 57)</t>
+          <t>Master &gt; System Configuration &gt; Insurer Integration (/master/configuration/insurer-integration): mapping per insurer (broker code, product codes, issuance request and answer maps, claim statuses), requests for policy issuance, policy and premium data (tolerance flag) and claim status, signed inbox for pushed statuses, claim status CSV as fallback; connector INSURER_API (test mode delivered); modules/integrations/insurer.js (migration 0313); integrations.test.js (insurer system integration)</t>
         </is>
       </c>
       <c r="K93" s="6" t="inlineStr">
         <is>
-          <t>No insurer API connector.</t>
+          <t>Certification that remains with the partner: each insurer's API contract, endpoint, credentials and field mapping are agreed and tested with that insurer; files and e-mail remain the fallback.</t>
         </is>
       </c>
       <c r="L93" s="7" t="inlineStr"/>
@@ -6002,7 +5900,7 @@
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>L1 subtotal: fit 87.5%</t>
+          <t>L1 subtotal: fit 100.0%</t>
         </is>
       </c>
       <c r="D94" s="9" t="inlineStr"/>
@@ -6012,7 +5910,7 @@
       </c>
       <c r="G94" s="9" t="inlineStr"/>
       <c r="H94" s="10" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="I94" s="10" t="n">
         <v>40</v>
@@ -6050,7 +5948,7 @@
       <c r="F95" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G95" s="12" t="n">
+      <c r="G95" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H95" s="7">
@@ -6098,7 +5996,7 @@
       <c r="F96" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G96" s="12" t="n">
+      <c r="G96" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H96" s="7">
@@ -6146,7 +6044,7 @@
       <c r="F97" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G97" s="12" t="n">
+      <c r="G97" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H97" s="7">
@@ -6194,7 +6092,7 @@
       <c r="F98" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G98" s="12" t="n">
+      <c r="G98" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H98" s="7">
@@ -6242,7 +6140,7 @@
       <c r="F99" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G99" s="12" t="n">
+      <c r="G99" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H99" s="7">
@@ -6255,7 +6153,7 @@
       </c>
       <c r="J99" s="6" t="inlineStr">
         <is>
-          <t>Generate payout; Disbursement &gt; Bulk Disburse; disbursements.test.js</t>
+          <t>Generate payout; Disbursement &gt; Bulk Disburse; bank payment file for referrer payouts; disbursements.test.js; integrations.test.js</t>
         </is>
       </c>
       <c r="K99" s="6" t="inlineStr"/>
@@ -6290,7 +6188,7 @@
       <c r="F100" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G100" s="12" t="n">
+      <c r="G100" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H100" s="7">
@@ -6338,7 +6236,7 @@
       <c r="F101" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G101" s="12" t="n">
+      <c r="G101" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H101" s="7">
@@ -6386,8 +6284,8 @@
       <c r="F102" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G102" s="13" t="n">
-        <v>0</v>
+      <c r="G102" s="11" t="n">
+        <v>2</v>
       </c>
       <c r="H102" s="7">
         <f>F102*G102</f>
@@ -6399,14 +6297,10 @@
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
-          <t>No licence number or expiry on referrer accounts (grep licence: company master only)</t>
-        </is>
-      </c>
-      <c r="K102" s="6" t="inlineStr">
-        <is>
-          <t>Commission can be paid to a referrer without a valid IC licence where one is required.</t>
-        </is>
-      </c>
+          <t>Compliance &gt; Insurance Commission &gt; Licence Register (holder type Agent / referrer); compliance.referrer_licence_check block (delivered), warn or off on Approve, Generate payout and payout voucher approval for compliance.licence_required_referrer_types; migration 0270; ic-compliance.test.js (commission payout needs a licence in force)</t>
+        </is>
+      </c>
+      <c r="K102" s="6" t="inlineStr"/>
       <c r="L102" s="7" t="inlineStr"/>
     </row>
     <row r="103">
@@ -6439,7 +6333,7 @@
         <v>1</v>
       </c>
       <c r="G103" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H103" s="7">
         <f>F103*G103</f>
@@ -6451,14 +6345,10 @@
       </c>
       <c r="J103" s="6" t="inlineStr">
         <is>
-          <t>Journal Voucher (manual)</t>
-        </is>
-      </c>
-      <c r="K103" s="6" t="inlineStr">
-        <is>
-          <t>No computation; booked by journal voucher.</t>
-        </is>
-      </c>
+          <t>Commission &gt; Insurer Overrides &gt; Agreements and Computations (/commission/insurer-overrides): tiers by production, loss ratio or growth, computation OVC series, approval posts the receivable, sales invoice, settlement with 2307; modules/insurer-overrides (migration 0284); insurer-overrides.test.js</t>
+        </is>
+      </c>
+      <c r="K103" s="6" t="inlineStr"/>
       <c r="L103" s="7" t="inlineStr"/>
     </row>
     <row r="104">
@@ -6474,7 +6364,7 @@
       </c>
       <c r="C104" s="9" t="inlineStr">
         <is>
-          <t>L1 subtotal: fit 84.2%</t>
+          <t>L1 subtotal: fit 100.0%</t>
         </is>
       </c>
       <c r="D104" s="9" t="inlineStr"/>
@@ -6484,7 +6374,7 @@
       </c>
       <c r="G104" s="9" t="inlineStr"/>
       <c r="H104" s="10" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="I104" s="10" t="n">
         <v>38</v>
@@ -6522,7 +6412,7 @@
       <c r="F105" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G105" s="12" t="n">
+      <c r="G105" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H105" s="7">
@@ -6570,7 +6460,7 @@
       <c r="F106" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G106" s="12" t="n">
+      <c r="G106" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H106" s="7">
@@ -6619,7 +6509,7 @@
         <v>2</v>
       </c>
       <c r="G107" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H107" s="7">
         <f>F107*G107</f>
@@ -6631,14 +6521,10 @@
       </c>
       <c r="J107" s="6" t="inlineStr">
         <is>
-          <t>Claim documents upload; causes of loss per line (GET /claims/config)</t>
-        </is>
-      </c>
-      <c r="K107" s="6" t="inlineStr">
-        <is>
-          <t>No required-document checklist or reminder to the claimant.</t>
-        </is>
-      </c>
+          <t>Operations &gt; Claim Documents (/operations/claim-documents) from Master &gt; Insurance Management &gt; Claim Document Checklist by line and claim type; received, waived, remind the claimant (job Missing claim documents), submission to the insurer refused while a required document is missing; modules/claim-documents (migration 0294); ops-accounting.test.js (claim document checklist)</t>
+        </is>
+      </c>
+      <c r="K107" s="6" t="inlineStr"/>
       <c r="L107" s="7" t="inlineStr"/>
     </row>
     <row r="108">
@@ -6670,7 +6556,7 @@
       <c r="F108" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G108" s="12" t="n">
+      <c r="G108" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H108" s="7">
@@ -6683,7 +6569,7 @@
       </c>
       <c r="J108" s="6" t="inlineStr">
         <is>
-          <t>Claim statuses; claims.sla_days 20; Claims Dashboard; Claims Position, Claims Ageing; claims.test.js; reports.test.js</t>
+          <t>Claim statuses; claims.sla_days 20; Claims Dashboard; Claims Position, Claims Ageing; claim status by insurer API or file; claims.test.js; reports.test.js; integrations.test.js</t>
         </is>
       </c>
       <c r="K108" s="6" t="inlineStr"/>
@@ -6718,7 +6604,7 @@
       <c r="F109" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G109" s="12" t="n">
+      <c r="G109" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H109" s="7">
@@ -6767,7 +6653,7 @@
         <v>2</v>
       </c>
       <c r="G110" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H110" s="7">
         <f>F110*G110</f>
@@ -6779,14 +6665,10 @@
       </c>
       <c r="J110" s="6" t="inlineStr">
         <is>
-          <t>Settlement cash panel (POST /claims/:id/settlement-cash/...); claims.test.js</t>
-        </is>
-      </c>
-      <c r="K110" s="6" t="inlineStr">
-        <is>
-          <t>Panel is on the claim screens; Accounting menu not extended, so the System Administrator records it (known limitation).</t>
-        </is>
-      </c>
+          <t>Accounts &gt; Claims Settlements (/accounts/claims-settlements): funds received (claim.funds_received), pay claimant with claim payment voucher CPV series (claim.paid_to_claimant), release form; claimant screened at payment; modules/claim-payments (migration 0294); ops-accounting.test.js (claims settlements from the Accounting menu); aml.test.js</t>
+        </is>
+      </c>
+      <c r="K110" s="6" t="inlineStr"/>
       <c r="L110" s="7" t="inlineStr"/>
     </row>
     <row r="111">
@@ -6818,7 +6700,7 @@
       <c r="F111" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G111" s="12" t="n">
+      <c r="G111" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H111" s="7">
@@ -6867,7 +6749,7 @@
         <v>2</v>
       </c>
       <c r="G112" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H112" s="7">
         <f>F112*G112</f>
@@ -6879,14 +6761,10 @@
       </c>
       <c r="J112" s="6" t="inlineStr">
         <is>
-          <t>Repair shop on settlement (migration 0216)</t>
-        </is>
-      </c>
-      <c r="K112" s="6" t="inlineStr">
-        <is>
-          <t>No estimate approval or letter of authority workflow.</t>
-        </is>
-      </c>
+          <t>Operations &gt; Motor Claim Repairs (/operations/motor-claim-repairs): estimates of accredited shops (Master &gt; Repair Shops), adjuster decision, letter of authority LOA series with participation and parts depreciation, supplementary letters, vehicle release; modules/motor-claims (migration 0295); ops-accounting.test.js (motor claim repairs)</t>
+        </is>
+      </c>
+      <c r="K112" s="6" t="inlineStr"/>
       <c r="L112" s="7" t="inlineStr"/>
     </row>
     <row r="113">
@@ -6902,7 +6780,7 @@
       </c>
       <c r="C113" s="9" t="inlineStr">
         <is>
-          <t>L1 subtotal: fit 96.0%</t>
+          <t>L1 subtotal: fit 100.0%</t>
         </is>
       </c>
       <c r="D113" s="9" t="inlineStr"/>
@@ -6912,7 +6790,7 @@
       </c>
       <c r="G113" s="9" t="inlineStr"/>
       <c r="H113" s="10" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I113" s="10" t="n">
         <v>50</v>
@@ -6950,7 +6828,7 @@
       <c r="F114" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G114" s="12" t="n">
+      <c r="G114" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H114" s="7">
@@ -6998,7 +6876,7 @@
       <c r="F115" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G115" s="12" t="n">
+      <c r="G115" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H115" s="7">
@@ -7046,7 +6924,7 @@
       <c r="F116" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G116" s="12" t="n">
+      <c r="G116" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H116" s="7">
@@ -7094,7 +6972,7 @@
       <c r="F117" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G117" s="12" t="n">
+      <c r="G117" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H117" s="7">
@@ -7142,7 +7020,7 @@
       <c r="F118" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G118" s="12" t="n">
+      <c r="G118" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H118" s="7">
@@ -7190,7 +7068,7 @@
       <c r="F119" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G119" s="12" t="n">
+      <c r="G119" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H119" s="7">
@@ -7203,7 +7081,7 @@
       </c>
       <c r="J119" s="6" t="inlineStr">
         <is>
-          <t>Accounts &gt; Period End &gt; Month-End Close; period-end.test.js; period-end-calendar.test.js</t>
+          <t>Accounts &gt; Period End &gt; Month-End Close (steps including depreciation); period-end.test.js; period-end-calendar.test.js; ops-accounting.test.js</t>
         </is>
       </c>
       <c r="K119" s="6" t="inlineStr"/>
@@ -7238,7 +7116,7 @@
       <c r="F120" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G120" s="12" t="n">
+      <c r="G120" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H120" s="7">
@@ -7286,7 +7164,7 @@
       <c r="F121" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G121" s="12" t="n">
+      <c r="G121" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H121" s="7">
@@ -7334,7 +7212,7 @@
       <c r="F122" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G122" s="12" t="n">
+      <c r="G122" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H122" s="7">
@@ -7366,7 +7244,7 @@
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>Supplier invoices, input VAT, fixed assets and depreciation</t>
+          <t>Supplier invoices, input VAT, fixed assets, depreciation and disposal</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
@@ -7383,7 +7261,7 @@
         <v>2</v>
       </c>
       <c r="G123" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H123" s="7">
         <f>F123*G123</f>
@@ -7395,14 +7273,10 @@
       </c>
       <c r="J123" s="6" t="inlineStr">
         <is>
-          <t>Supplier payment vouchers with withholding; input VAT tax code</t>
-        </is>
-      </c>
-      <c r="K123" s="6" t="inlineStr">
-        <is>
-          <t>No supplier invoice register (accounts payable sub-ledger) or fixed asset register.</t>
-        </is>
-      </c>
+          <t>Accounts &gt; Payables &gt; Supplier Invoices, Supplier Payments, AP Ageing, Suppliers, Supplier 2307 (/accounts/payables); Accounts &gt; Fixed Assets &gt; Asset Register, Depreciation Run, Disposals (/accounts/fixed-assets); posting rules ap.invoice, ap.payment, fa.depreciation, fa.disposal; modules/payables, modules/fixed-assets (migrations 0296, 0297, 0321); ops-accounting.test.js (accounts payable, fixed asset register and depreciation), ap-2307-asset-disposal.test.js</t>
+        </is>
+      </c>
+      <c r="K123" s="6" t="inlineStr"/>
       <c r="L123" s="7" t="inlineStr"/>
     </row>
     <row r="124">
@@ -7418,7 +7292,7 @@
       </c>
       <c r="C124" s="9" t="inlineStr">
         <is>
-          <t>L1 subtotal: fit 74.2%</t>
+          <t>L1 subtotal: fit 100.0%</t>
         </is>
       </c>
       <c r="D124" s="9" t="inlineStr"/>
@@ -7428,7 +7302,7 @@
       </c>
       <c r="G124" s="9" t="inlineStr"/>
       <c r="H124" s="10" t="n">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="I124" s="10" t="n">
         <v>62</v>
@@ -7466,7 +7340,7 @@
       <c r="F125" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G125" s="12" t="n">
+      <c r="G125" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H125" s="7">
@@ -7518,7 +7392,7 @@
       <c r="F126" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G126" s="12" t="n">
+      <c r="G126" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H126" s="7">
@@ -7567,7 +7441,7 @@
         <v>1</v>
       </c>
       <c r="G127" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H127" s="7">
         <f>F127*G127</f>
@@ -7579,14 +7453,10 @@
       </c>
       <c r="J127" s="6" t="inlineStr">
         <is>
-          <t>direct_bill.broker_vat_registered switch</t>
-        </is>
-      </c>
-      <c r="K127" s="6" t="inlineStr">
-        <is>
-          <t>No percentage tax working paper.</t>
-        </is>
-      </c>
+          <t>Accounts &gt; Tax &gt; Percentage Tax 2551Q (/accounts/tax/percentage-tax): gross sales per month from the revenue accounts, bir.percentage_tax_rate and bir.percentage_tax_atc, print, Excel, filing record; modules/bir/returns.js (migration 0280); bir-forms.test.js (2551Q)</t>
+        </is>
+      </c>
+      <c r="K127" s="6" t="inlineStr"/>
       <c r="L127" s="7" t="inlineStr"/>
     </row>
     <row r="128">
@@ -7618,7 +7488,7 @@
       <c r="F128" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G128" s="12" t="n">
+      <c r="G128" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H128" s="7">
@@ -7631,7 +7501,7 @@
       </c>
       <c r="J128" s="6" t="inlineStr">
         <is>
-          <t>Accounts &gt; Tax &gt; BIR Form 2307 (Issued by us); commission-taxes.test.js</t>
+          <t>Accounts &gt; Tax &gt; BIR Form 2307 (Issued by us); Accounts &gt; Payables &gt; Supplier 2307; commission-taxes.test.js; ap-2307-asset-disposal.test.js</t>
         </is>
       </c>
       <c r="K128" s="6" t="inlineStr"/>
@@ -7666,7 +7536,7 @@
       <c r="F129" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G129" s="12" t="n">
+      <c r="G129" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H129" s="7">
@@ -7715,7 +7585,7 @@
         <v>3</v>
       </c>
       <c r="G130" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H130" s="7">
         <f>F130*G130</f>
@@ -7727,12 +7597,12 @@
       </c>
       <c r="J130" s="6" t="inlineStr">
         <is>
-          <t>Accounts &gt; Tax &gt; QAP</t>
+          <t>Accounts &gt; Tax &gt; Withholding Returns (/accounts/tax/withholding-returns): filing calendar, 0619-E and 1601-EQ laid out with the BIR item numbers per ATC, 0619-E remittances deducted, reconciliation with the QAP and the ledger, PDF and Excel, filing and amended return records; modules/bir/returns.js (migration 0280); bir-forms.test.js (0619-E and 1601-EQ)</t>
         </is>
       </c>
       <c r="K130" s="6" t="inlineStr">
         <is>
-          <t>QAP is delivered; the return figures per ATC are not laid out as the 0619-E / 1601-EQ forms.</t>
+          <t>The figures are transferred to eBIRForms or eFPS by the broker; the system does not file.</t>
         </is>
       </c>
       <c r="L130" s="7" t="inlineStr"/>
@@ -7767,7 +7637,7 @@
         <v>2</v>
       </c>
       <c r="G131" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H131" s="7">
         <f>F131*G131</f>
@@ -7779,14 +7649,10 @@
       </c>
       <c r="J131" s="6" t="inlineStr">
         <is>
-          <t>QAP run for a full year range (generic date criteria)</t>
-        </is>
-      </c>
-      <c r="K131" s="6" t="inlineStr">
-        <is>
-          <t>No 1604-E alphalist layout.</t>
-        </is>
-      </c>
+          <t>Accounts &gt; Tax &gt; Annual Alphalist 1604-E (/accounts/tax/alphalist-1604e): remittances per month from the filing records, schedules 3 and 4, Excel, print, DAT file, filing record; bir-forms.test.js (1604-E)</t>
+        </is>
+      </c>
+      <c r="K131" s="6" t="inlineStr"/>
       <c r="L131" s="7" t="inlineStr"/>
     </row>
     <row r="132">
@@ -7818,7 +7684,7 @@
       <c r="F132" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G132" s="12" t="n">
+      <c r="G132" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H132" s="7">
@@ -7831,7 +7697,7 @@
       </c>
       <c r="J132" s="6" t="inlineStr">
         <is>
-          <t>Accounts &gt; Tax &gt; SLSP Sales, SLSP Purchases (BIR column order)</t>
+          <t>Accounts &gt; Tax &gt; SLSP Sales, SLSP Purchases (BIR column order); DAT files</t>
         </is>
       </c>
       <c r="K132" s="6" t="inlineStr"/>
@@ -7867,7 +7733,7 @@
         <v>3</v>
       </c>
       <c r="G133" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H133" s="7">
         <f>F133*G133</f>
@@ -7879,12 +7745,12 @@
       </c>
       <c r="J133" s="6" t="inlineStr">
         <is>
-          <t>INV, OR and DN series on letterhead with TIN; compliance matrix (Invoices and receipts)</t>
+          <t>Accounts &gt; Tax &gt; Sales Invoices (/accounts/tax/sales-invoices): SI series without gaps within the registered serial range, seller and buyer fields, VATable, exempt and zero-rated sales, payment acknowledgement as supplementary document, cancellation; receipts.document_title and supplementary statement; invoice.* settings (ATP or CAS permit, serial range, printer, buyer threshold); modules/bir/invoices.js (migration 0281); bir-forms.test.js (sales invoices under the EOPT Act)</t>
         </is>
       </c>
       <c r="K133" s="6" t="inlineStr">
         <is>
-          <t>Which document is the registered invoice and its printed fields are not fixed in the product; layout changes are outside OOTB.</t>
+          <t>The tax adviser confirms which documents are registered as the broker's invoices, the wording of the supplementary documents and the VAT treatment of each commission stream; these are settings, not code.</t>
         </is>
       </c>
       <c r="L133" s="7" t="inlineStr"/>
@@ -7919,7 +7785,7 @@
         <v>3</v>
       </c>
       <c r="G134" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H134" s="7">
         <f>F134*G134</f>
@@ -7931,12 +7797,12 @@
       </c>
       <c r="J134" s="6" t="inlineStr">
         <is>
-          <t>Journals, ledgers, audit trail, period locks, number series; documentation pack</t>
+          <t>Accounts &gt; Tax &gt; CAS Books and Documents (/accounts/tax/cas): readiness checklist, six loose-leaf books with page numbers running through the year, print register, reprint and void, system description, backup procedure, audit trail extract; modules/bir/cas.js (migration 0282); bir-forms.test.js (CAS registration pack)</t>
         </is>
       </c>
       <c r="K134" s="6" t="inlineStr">
         <is>
-          <t>No loose-leaf books print set or CAS output pack; registration is with the broker.</t>
+          <t>The registration or acknowledgement with the BIR is filed by the broker with the pack.</t>
         </is>
       </c>
       <c r="L134" s="7" t="inlineStr"/>
@@ -7970,8 +7836,8 @@
       <c r="F135" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G135" s="13" t="n">
-        <v>0</v>
+      <c r="G135" s="11" t="n">
+        <v>2</v>
       </c>
       <c r="H135" s="7">
         <f>F135*G135</f>
@@ -7983,12 +7849,12 @@
       </c>
       <c r="J135" s="6" t="inlineStr">
         <is>
-          <t>None found</t>
+          <t>Accounts &gt; Tax &gt; E-Invoicing (EIS) (/accounts/tax/eis): connector with eis.mode test (built-in provider) or live, signed payloads with SHA-256 hash, eis-outbox job with retry and backoff, retry, queue earlier invoices, export payloads for manual upload and Uploaded manually record; modules/bir/eis.js (migration 0283); bir-forms.test.js (EIS connector)</t>
         </is>
       </c>
       <c r="K135" s="6" t="inlineStr">
         <is>
-          <t>No EIS connector (not yet mandatory for most brokers; to verify).</t>
+          <t>Certification that remains with the partner: the broker's EIS enrolment, the BIR's final field list and signing certificate, the production endpoint and credentials. Delivered switched off; the manual upload is the fallback.</t>
         </is>
       </c>
       <c r="L135" s="7" t="inlineStr"/>
@@ -8023,7 +7889,7 @@
         <v>2</v>
       </c>
       <c r="G136" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H136" s="7">
         <f>F136*G136</f>
@@ -8035,12 +7901,12 @@
       </c>
       <c r="J136" s="6" t="inlineStr">
         <is>
-          <t>SAWT, QAP, SLSP as CSV or Excel in BIR column order</t>
+          <t>Accounts &gt; Tax &gt; BIR DAT Files (/accounts/tax/dat-files): QAP, SAWT, 1604-E alphalist (Alphalist Data Entry and Validation Module 7.x record layouts) and SLSP (RELIEF layout), header, detail and control records, warnings; modules/bir/dat.js; bir-forms.test.js (writes the files exactly as the documented layout)</t>
         </is>
       </c>
       <c r="K136" s="6" t="inlineStr">
         <is>
-          <t>Files are re-keyed or imported into the BIR tools; no DAT file.</t>
+          <t>Validate each file with the current BIR validation module before the first submission.</t>
         </is>
       </c>
       <c r="L136" s="7" t="inlineStr"/>
@@ -8074,7 +7940,7 @@
       <c r="F137" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G137" s="12" t="n">
+      <c r="G137" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H137" s="7">
@@ -8106,7 +7972,7 @@
       </c>
       <c r="C138" s="9" t="inlineStr">
         <is>
-          <t>L1 subtotal: fit 59.3%</t>
+          <t>L1 subtotal: fit 94.4%</t>
         </is>
       </c>
       <c r="D138" s="9" t="inlineStr"/>
@@ -8116,7 +7982,7 @@
       </c>
       <c r="G138" s="9" t="inlineStr"/>
       <c r="H138" s="10" t="n">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="I138" s="10" t="n">
         <v>54</v>
@@ -8154,8 +8020,8 @@
       <c r="F139" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G139" s="13" t="n">
-        <v>0</v>
+      <c r="G139" s="11" t="n">
+        <v>2</v>
       </c>
       <c r="H139" s="7">
         <f>F139*G139</f>
@@ -8167,14 +8033,10 @@
       </c>
       <c r="J139" s="6" t="inlineStr">
         <is>
-          <t>None found</t>
-        </is>
-      </c>
-      <c r="K139" s="6" t="inlineStr">
-        <is>
-          <t>No licence expiry calendar for the firm, its officers or solicitors.</t>
-        </is>
-      </c>
+          <t>Compliance &gt; Insurance Commission &gt; Licence Register (/compliance/licences): firm, officers, licensed individuals and referrers, states Valid, Expiring, Expired, renewal filed and recorded, expiry calendar, job compliance-reminders at 90, 60, 30, 15 and 7 days; modules/ic-compliance/licences.js (migration 0270); ic-compliance.test.js (licence register)</t>
+        </is>
+      </c>
+      <c r="K139" s="6" t="inlineStr"/>
       <c r="L139" s="7" t="inlineStr"/>
     </row>
     <row r="140">
@@ -8206,8 +8068,8 @@
       <c r="F140" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G140" s="13" t="n">
-        <v>0</v>
+      <c r="G140" s="11" t="n">
+        <v>2</v>
       </c>
       <c r="H140" s="7">
         <f>F140*G140</f>
@@ -8219,12 +8081,12 @@
       </c>
       <c r="J140" s="6" t="inlineStr">
         <is>
-          <t>None found</t>
+          <t>Compliance &gt; Insurance Commission &gt; Fit and Proper (/compliance/fit-and-proper): declarations from compliance.fit_proper_declarations, attachments, review outcome, next review in compliance.fit_proper_review_months; modules/ic-compliance/fitProper.js; ic-compliance.test.js (fit and proper records)</t>
         </is>
       </c>
       <c r="K140" s="6" t="inlineStr">
         <is>
-          <t>Kept outside the system.</t>
+          <t>The wording of the declarations is a setting the compliance officer confirms against the IC rules in force.</t>
         </is>
       </c>
       <c r="L140" s="7" t="inlineStr"/>
@@ -8258,7 +8120,7 @@
       <c r="F141" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G141" s="11" t="n">
+      <c r="G141" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H141" s="7">
@@ -8271,12 +8133,12 @@
       </c>
       <c r="J141" s="6" t="inlineStr">
         <is>
-          <t>Financial Statements; Trial Balance (figures only)</t>
+          <t>Compliance &gt; Insurance Commission &gt; IC Annual Statement (/compliance/ic-annual-statement): schedules 1 to 4 from the ledger and production on configurable IC lines (Account mapping, migration 0274), checks, accountant confirmation sheet, unmapped accounts, workbook; modules/ic-compliance/icReports.js; ic-compliance.test.js (annual statement)</t>
         </is>
       </c>
       <c r="K141" s="6" t="inlineStr">
         <is>
-          <t>No IC-format report (checklist item 60).</t>
+          <t>Delivered as a working paper: the schedules follow the structure of the IC annual statement of an insurance broker (form set named in compliance.ic_statement_form), and the accountant confirms the figures and transcribes them onto the IC form set in force. The official form layout is not reproduced by the system, so the item is scored 1.</t>
         </is>
       </c>
       <c r="L141" s="7" t="inlineStr"/>
@@ -8311,7 +8173,7 @@
         <v>2</v>
       </c>
       <c r="G142" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H142" s="7">
         <f>F142*G142</f>
@@ -8323,12 +8185,12 @@
       </c>
       <c r="J142" s="6" t="inlineStr">
         <is>
-          <t>Production Register; Premium by Product / Month / Insurer</t>
+          <t>Compliance &gt; Insurance Commission &gt; IC Production Report (/compliance/ic-production-report): premiums by insurer and IC line (compliance.ic_lines_of_business, ic_line_map) by month, quarter or year, co-insurance split by share, Excel with detail; ic-compliance.test.js (production report)</t>
         </is>
       </c>
       <c r="K142" s="6" t="inlineStr">
         <is>
-          <t>Figures available; IC layout not produced.</t>
+          <t>The IC line set is a setting; confirm it against the IC form in force before the first submission.</t>
         </is>
       </c>
       <c r="L142" s="7" t="inlineStr"/>
@@ -8362,7 +8224,7 @@
       <c r="F143" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G143" s="12" t="n">
+      <c r="G143" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H143" s="7">
@@ -8375,7 +8237,7 @@
       </c>
       <c r="J143" s="6" t="inlineStr">
         <is>
-          <t>Numbered placement trail RFQ to policy to receipt; reports; audit log; Company master IC licence number on letterhead (printing.test.js)</t>
+          <t>Numbered placement trail RFQ to policy to receipt; reports; audit log; Company master IC licence number on letterhead and footer line (printing.test.js, branding.test.js)</t>
         </is>
       </c>
       <c r="K143" s="6" t="inlineStr"/>
@@ -8410,7 +8272,7 @@
       <c r="F144" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G144" s="12" t="n">
+      <c r="G144" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H144" s="7">
@@ -8423,7 +8285,7 @@
       </c>
       <c r="J144" s="6" t="inlineStr">
         <is>
-          <t>Premiums Payable to Insurers per insurer; Premium Trust Account; payment-segregation.test.js</t>
+          <t>Premiums Payable to Insurers per insurer; Premium Trust Account; IC Annual Statement schedule 4; payment-segregation.test.js; ic-compliance.test.js</t>
         </is>
       </c>
       <c r="K144" s="6" t="inlineStr"/>
@@ -8458,8 +8320,8 @@
       <c r="F145" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G145" s="13" t="n">
-        <v>0</v>
+      <c r="G145" s="11" t="n">
+        <v>2</v>
       </c>
       <c r="H145" s="7">
         <f>F145*G145</f>
@@ -8471,12 +8333,12 @@
       </c>
       <c r="J145" s="6" t="inlineStr">
         <is>
-          <t>None found (grep complaint returns nothing)</t>
+          <t>Compliance &gt; Insurance Commission &gt; Complaints (/compliance/complaints): register with CPT series, acknowledgement and resolution deadlines (complaints.ack_days, resolution_days_simple and _complex), letters on the letterhead, escalation, referral to the IC, job complaints-deadlines, regulator report; modules/ic-compliance/complaints.js (migration 0272); ic-compliance.test.js (complaints register)</t>
         </is>
       </c>
       <c r="K145" s="6" t="inlineStr">
         <is>
-          <t>No complaints register or response time tracking.</t>
+          <t>The deadline values are settings to confirm against the IC rules in force.</t>
         </is>
       </c>
       <c r="L145" s="7" t="inlineStr"/>
@@ -8510,7 +8372,7 @@
       <c r="F146" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G146" s="12" t="n">
+      <c r="G146" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H146" s="7">
@@ -8558,7 +8420,7 @@
       <c r="F147" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G147" s="12" t="n">
+      <c r="G147" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H147" s="7">
@@ -8607,7 +8469,7 @@
         <v>2</v>
       </c>
       <c r="G148" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H148" s="7">
         <f>F148*G148</f>
@@ -8619,14 +8481,10 @@
       </c>
       <c r="J148" s="6" t="inlineStr">
         <is>
-          <t>Login history, audit log, failed sign-in alarms</t>
-        </is>
-      </c>
-      <c r="K148" s="6" t="inlineStr">
-        <is>
-          <t>No breach register or 72-hour notification tracker.</t>
-        </is>
-      </c>
+          <t>Compliance &gt; Data Privacy (NPC) &gt; Breach Register (/compliance/breaches): incident log with PDB series, 72-hour clock from discovery (privacy.breach_notify_hours), NPC criteria assessment, NPC and data subject notification records, hourly job privacy-breach-deadlines, annual report; login history and failed sign-in alarms; modules/data-breaches (migration 0273); data-breaches.test.js</t>
+        </is>
+      </c>
+      <c r="K148" s="6" t="inlineStr"/>
       <c r="L148" s="7" t="inlineStr"/>
     </row>
     <row r="149">
@@ -8658,8 +8516,8 @@
       <c r="F149" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G149" s="13" t="n">
-        <v>0</v>
+      <c r="G149" s="11" t="n">
+        <v>2</v>
       </c>
       <c r="H149" s="7">
         <f>F149*G149</f>
@@ -8671,19 +8529,11 @@
       </c>
       <c r="J149" s="6" t="inlineStr">
         <is>
-          <t>Not delivered (in development)</t>
-        </is>
-      </c>
-      <c r="K149" s="6" t="inlineStr">
-        <is>
-          <t>Personal identifiers shown in full to every role with read access.</t>
-        </is>
-      </c>
-      <c r="L149" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>Permission view:pii (Master &gt; Users and Access &gt; Roles): TIN, ID, mobile, e-mail, bank account and birth date masked on lists, views and Excel, CSV and PDF exports; on-request reveal recorded in the audit trail; privacy.masking_enabled, masking_exempt_paths, pii_reveal_mode; lib/piiPolicy.js and lib/pii.js applied in app.js (migration 0276); personal-data-protection.test.js (masking by role); mask-data.test.js (production copies)</t>
+        </is>
+      </c>
+      <c r="K149" s="6" t="inlineStr"/>
+      <c r="L149" s="7" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="7" t="inlineStr">
@@ -8715,7 +8565,7 @@
         <v>1</v>
       </c>
       <c r="G150" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H150" s="7">
         <f>F150*G150</f>
@@ -8727,14 +8577,10 @@
       </c>
       <c r="J150" s="6" t="inlineStr">
         <is>
-          <t>Storage encryption (hosting); two-step secrets AES-256-GCM; BV-DEF-003 open</t>
-        </is>
-      </c>
-      <c r="K150" s="6" t="inlineStr">
-        <is>
-          <t>No field-level encryption of IDs and TIN.</t>
-        </is>
-      </c>
+          <t>TIN, government ID and bank account numbers of clients, prospects and referrers, policy KYC IDs and 2307 payee TIN encrypted at rest with PII_ENCRYPTION_KEY and a blind index for exact search; key rotation (deploy/REFERENCE.md); migration 0277; personal-data-protection.test.js (field-level encryption)</t>
+        </is>
+      </c>
+      <c r="K150" s="6" t="inlineStr"/>
       <c r="L150" s="7" t="inlineStr"/>
     </row>
     <row r="151">
@@ -8766,7 +8612,7 @@
       <c r="F151" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G151" s="12" t="n">
+      <c r="G151" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H151" s="7">
@@ -8798,7 +8644,7 @@
       </c>
       <c r="C152" s="9" t="inlineStr">
         <is>
-          <t>L1 subtotal: fit 83.9%</t>
+          <t>L1 subtotal: fit 100.0%</t>
         </is>
       </c>
       <c r="D152" s="9" t="inlineStr"/>
@@ -8808,7 +8654,7 @@
       </c>
       <c r="G152" s="9" t="inlineStr"/>
       <c r="H152" s="10" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="I152" s="10" t="n">
         <v>62</v>
@@ -8830,7 +8676,7 @@
       </c>
       <c r="C153" s="6" t="inlineStr">
         <is>
-          <t>Report catalogue (39 reports) in Excel, CSV and PDF with scheduled e-mail</t>
+          <t>Report catalogue in Excel, CSV and PDF with scheduled e-mail</t>
         </is>
       </c>
       <c r="D153" s="7" t="inlineStr">
@@ -8846,7 +8692,7 @@
       <c r="F153" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G153" s="12" t="n">
+      <c r="G153" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H153" s="7">
@@ -8894,7 +8740,7 @@
       <c r="F154" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G154" s="12" t="n">
+      <c r="G154" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H154" s="7">
@@ -8943,7 +8789,7 @@
         <v>1</v>
       </c>
       <c r="G155" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H155" s="7">
         <f>F155*G155</f>
@@ -8955,14 +8801,10 @@
       </c>
       <c r="J155" s="6" t="inlineStr">
         <is>
-          <t>Report criteria, filters and exports</t>
-        </is>
-      </c>
-      <c r="K155" s="6" t="inlineStr">
-        <is>
-          <t>No report designer or data warehouse extract.</t>
-        </is>
-      </c>
+          <t>Reports &gt; Report Builder (/reports/builder): datasets by permission, columns, filters, grouping with totals, Excel, saved reports private or shared by role; BI extract tab and job bi-extract (one CSV per dataset to bi.extract_folder); modules/report-builder (migration 0308); report-builder.test.js</t>
+        </is>
+      </c>
+      <c r="K155" s="6" t="inlineStr"/>
       <c r="L155" s="7" t="inlineStr"/>
     </row>
     <row r="156">
@@ -8994,7 +8836,7 @@
       <c r="F156" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G156" s="12" t="n">
+      <c r="G156" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H156" s="7">
@@ -9042,7 +8884,7 @@
       <c r="F157" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G157" s="12" t="n">
+      <c r="G157" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H157" s="7">
@@ -9090,7 +8932,7 @@
       <c r="F158" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G158" s="12" t="n">
+      <c r="G158" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H158" s="7">
@@ -9139,7 +8981,7 @@
         <v>3</v>
       </c>
       <c r="G159" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H159" s="7">
         <f>F159*G159</f>
@@ -9151,19 +8993,11 @@
       </c>
       <c r="J159" s="6" t="inlineStr">
         <is>
-          <t>Master &gt; Configuration &gt; Audit Trail; audit log written for create, update, approval, report run, sign-in</t>
-        </is>
-      </c>
-      <c r="K159" s="6" t="inlineStr">
-        <is>
-          <t>Audit log delivered; the reworked Audit Trail screen is in development and counted as not delivered.</t>
-        </is>
-      </c>
-      <c r="L159" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>Master &gt; System Configuration &gt; Audit Trail (/master/configuration/audit-trail): search by record type, record ID, user and dates, before and after values, source (migration 0247); audit extract for the CAS pack; modules/audit; audit-events.test.js (audit trail API)</t>
+        </is>
+      </c>
+      <c r="K159" s="6" t="inlineStr"/>
+      <c r="L159" s="7" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="7" t="inlineStr">
@@ -9195,7 +9029,7 @@
         <v>1</v>
       </c>
       <c r="G160" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H160" s="7">
         <f>F160*G160</f>
@@ -9207,19 +9041,11 @@
       </c>
       <c r="J160" s="6" t="inlineStr">
         <is>
-          <t>brokerverse/src/components/SideBar/list.js (173 menu screens)</t>
-        </is>
-      </c>
-      <c r="K160" s="6" t="inlineStr">
-        <is>
-          <t>Menu redesign in development.</t>
-        </is>
-      </c>
-      <c r="L160" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>Enterprise side menu in sections (brokerverse/src/components/SideBar/list.js, menuPermissions.js), Master in sections, Help panel (F1) with the manual section per screen; role-access.test.js, screen-data.test.js</t>
+        </is>
+      </c>
+      <c r="K160" s="6" t="inlineStr"/>
+      <c r="L160" s="7" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="7" t="inlineStr">
@@ -9251,7 +9077,7 @@
         <v>2</v>
       </c>
       <c r="G161" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H161" s="7">
         <f>F161*G161</f>
@@ -9263,19 +9089,11 @@
       </c>
       <c r="J161" s="6" t="inlineStr">
         <is>
-          <t>In-app notifications and approval notifications; approval-notifications.test.js</t>
-        </is>
-      </c>
-      <c r="K161" s="6" t="inlineStr">
-        <is>
-          <t>My Work inbox in development.</t>
-        </is>
-      </c>
-      <c r="L161" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>Operations &gt; My Work (/operations/my-work): My Items by category and role, My Team by reporting line with reassignment, My Tasks with reminders, Calendar; automatic follow-ups from promises to pay, renewal next steps, claim follow-ups and sales activities; modules/my-work (migration 0253); my-work.test.js, sales-activities.test.js</t>
+        </is>
+      </c>
+      <c r="K161" s="6" t="inlineStr"/>
+      <c r="L161" s="7" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="7" t="inlineStr">
@@ -9306,7 +9124,7 @@
       <c r="F162" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G162" s="12" t="n">
+      <c r="G162" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H162" s="7">
@@ -9355,7 +9173,7 @@
         <v>1</v>
       </c>
       <c r="G163" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H163" s="7">
         <f>F163*G163</f>
@@ -9367,19 +9185,11 @@
       </c>
       <c r="J163" s="6" t="inlineStr">
         <is>
-          <t>Letterhead from Company master; System Settings logo and theme</t>
-        </is>
-      </c>
-      <c r="K163" s="6" t="inlineStr">
-        <is>
-          <t>Branding and e-signature in development.</t>
-        </is>
-      </c>
-      <c r="L163" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>Master &gt; System Settings &gt; Theme and Branding (/master/configuration/theme-branding): theme presets with contrast check, logo, sign-in picture, document, report and e-mail branding, brand packs exported and imported (optional Toyota Insurance Services pack, used only with that client's permission); every PDF through printContext; e-signature slots per document; modules/branding, modules/e-signatures (migration 0254); branding.test.js</t>
+        </is>
+      </c>
+      <c r="K163" s="6" t="inlineStr"/>
+      <c r="L163" s="7" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="7" t="inlineStr">
@@ -9394,7 +9204,7 @@
       </c>
       <c r="C164" s="6" t="inlineStr">
         <is>
-          <t>Philippine reference masters (PSGC geography, banks, IDs, salutations, IC insurer list)</t>
+          <t>Philippine reference masters (PSGC geography, banks, IDs, salutations, holidays, IC insurer list)</t>
         </is>
       </c>
       <c r="D164" s="7" t="inlineStr">
@@ -9411,7 +9221,7 @@
         <v>2</v>
       </c>
       <c r="G164" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H164" s="7">
         <f>F164*G164</f>
@@ -9423,19 +9233,15 @@
       </c>
       <c r="J164" s="6" t="inlineStr">
         <is>
-          <t>Seeds: Metro Manila and selected LGUs (seeds/10_masters.sql); KYC ID setting</t>
+          <t>Master &gt; Location &gt; Province (labelled Province), City / Municipality, barangays and ZIP codes from PSGC 2Q 2026 (migration 0250, seed 12_ph_geography.sql); salutations, civil status, government ID types, registration authorities, payment modes, holidays, Philippine banks and the IC non-life insurer list with certificate fields (seed 69_ph_practice_masters.sql); addresses.test.js, masters.test.js</t>
         </is>
       </c>
       <c r="K164" s="6" t="inlineStr">
         <is>
-          <t>Full Philippine masters are in development.</t>
-        </is>
-      </c>
-      <c r="L164" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>Barangays are loaded per region from the shipped PSGC file by the administrator (tool with dry run), a go-live step.</t>
+        </is>
+      </c>
+      <c r="L164" s="7" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="7" t="inlineStr">
@@ -9466,7 +9272,7 @@
       <c r="F165" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G165" s="12" t="n">
+      <c r="G165" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H165" s="7">
@@ -9479,7 +9285,7 @@
       </c>
       <c r="J165" s="6" t="inlineStr">
         <is>
-          <t>Master &gt; Go-Live Data Load; go-live.test.js; go-live-workbench.test.js; go-live-roundtrip.test.js; docs/e2e/GOLIVE_REHEARSAL_RUN.md (51 checks passed)</t>
+          <t>Master &gt; Go-Live Data Load (configuration and migration workbooks, validate, errors workbook, load, reconciliation); go-live.test.js; go-live-workbench.test.js; go-live-roundtrip.test.js; docs/e2e/GOLIVE_REHEARSAL_RUN.md (51 checks passed)</t>
         </is>
       </c>
       <c r="K165" s="6" t="inlineStr"/>
@@ -9514,7 +9320,7 @@
       <c r="F166" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G166" s="12" t="n">
+      <c r="G166" s="11" t="n">
         <v>2</v>
       </c>
       <c r="H166" s="7">
@@ -9527,7 +9333,7 @@
       </c>
       <c r="J166" s="6" t="inlineStr">
         <is>
-          <t>Architecture and BCDR documents; /api/health</t>
+          <t>Architecture and BCDR documents; release pipeline (Dev, SIT, UAT, Pre-Prod, Production); /api/health</t>
         </is>
       </c>
       <c r="K166" s="6" t="inlineStr">
@@ -9546,18 +9352,18 @@
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>Overall fit 80.4%</t>
+          <t>Overall fit 99.3%</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr"/>
       <c r="E167" s="4" t="inlineStr"/>
       <c r="F167" s="4" t="inlineStr"/>
       <c r="G167" s="4" t="inlineStr"/>
-      <c r="H167" s="14">
+      <c r="H167" s="13">
         <f>SUMIF(A2:A166,"*.*",H2:H166)</f>
         <v/>
       </c>
-      <c r="I167" s="14">
+      <c r="I167" s="13">
         <f>SUMIF(A2:A166,"*.*",I2:I166)</f>
         <v/>
       </c>
@@ -9577,7 +9383,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L57"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -9662,46 +9468,46 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>14.04</t>
         </is>
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>Client onboarding, KYC and AML</t>
+          <t>Insurance Commission and Data Privacy compliance</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>Beneficial ownership of juridical clients</t>
+          <t>IC annual statement and financial reports in the IC format</t>
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr">
         <is>
-          <t>AMLC</t>
+          <t>IC</t>
         </is>
       </c>
       <c r="F2" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G2" s="13" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="G2" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
-          <t>No beneficial owner capture.</t>
+          <t>Delivered as a working paper: the schedules follow the structure of the IC annual statement of an insurance broker (form set named in compliance.ic_statement_form), and the accountant confirms the figures and transcribes them onto the IC form set in force. The official form layout is not reproduced by the system, so the item is scored 1.</t>
         </is>
       </c>
       <c r="J2" s="7" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Regulator confirmation</t>
         </is>
       </c>
       <c r="K2" s="7" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="L2" s="7" t="inlineStr"/>
@@ -9712,41 +9518,41 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>Commission, referrers and incentives</t>
+          <t>Client onboarding, KYC and AML</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>Licence check of agents and sub-agents before paying commission</t>
+          <t>Covered and suspicious transaction monitoring and AMLC reporting</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>AMLC</t>
         </is>
       </c>
       <c r="F3" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G3" s="13" t="n">
-        <v>0</v>
+      <c r="G3" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
-          <t>Commission can be paid to a referrer without a valid IC licence where one is required.</t>
+          <t>Monitoring, alerts and cases are delivered end to end. The report file is the product's own layout BV-AMLC-TXN 1.0 built after the AMLC reporting guidelines; the institution code, transaction codes, ID type codes and field order must be confirmed against the AMLC's current guidelines and a test file validated in the AMLC portal before the first filing. Scored 1 until that confirmation.</t>
         </is>
       </c>
       <c r="J3" s="7" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Regulator confirmation</t>
         </is>
       </c>
       <c r="K3" s="7" t="inlineStr">
@@ -9756,2663 +9562,15 @@
       </c>
       <c r="L3" s="7" t="inlineStr"/>
     </row>
-    <row r="4">
-      <c r="A4" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>14.02</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Insurance Commission and Data Privacy compliance</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Licence renewal tracking of the firm and licensed individuals</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>IC</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G4" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>No licence expiry calendar for the firm, its officers or solicitors.</t>
-        </is>
-      </c>
-      <c r="J4" s="7" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="K4" s="7" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="L4" s="7" t="inlineStr"/>
-    </row>
     <row r="5">
-      <c r="A5" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>14.08</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Insurance Commission and Data Privacy compliance</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Complaints handling and financial consumer protection (RA 11765)</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>IC</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G5" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>No complaints register or response time tracking.</t>
-        </is>
-      </c>
-      <c r="J5" s="7" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="K5" s="7" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="L5" s="7" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>1.04</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Client onboarding, KYC and AML</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>Risk-based customer due diligence rating and enhanced due diligence</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>AMLC</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G6" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>No customer risk rating, EDD workflow or periodic KYC refresh.</t>
-        </is>
-      </c>
-      <c r="J6" s="7" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="K6" s="7" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L6" s="7" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>1.06</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Client onboarding, KYC and AML</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>Sanctions, PEP and negative list screening</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>AMLC</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G7" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>No screening at onboarding or at payment.</t>
-        </is>
-      </c>
-      <c r="J7" s="7" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="K7" s="7" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L7" s="7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>1.07</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Client onboarding, KYC and AML</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Covered and suspicious transaction monitoring and AMLC reporting</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>AMLC</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>No threshold rules, alert queue or AMLC reporting file.</t>
-        </is>
-      </c>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L8" s="7" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>14.12</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Insurance Commission and Data Privacy compliance</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>Masking of personal data on screens and exports by role</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>NPC</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G9" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>Personal identifiers shown in full to every role with read access.</t>
-        </is>
-      </c>
-      <c r="J9" s="7" t="inlineStr">
-        <is>
-          <t>In development</t>
-        </is>
-      </c>
-      <c r="K9" s="7" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L9" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>13.07</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>Taxes and BIR compliance</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>Monthly and quarterly EWT returns (0619-E, 1601-EQ) with QAP</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>BIR</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G10" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>QAP is delivered; the return figures per ATC are not laid out as the 0619-E / 1601-EQ forms.</t>
-        </is>
-      </c>
-      <c r="J10" s="7" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="K10" s="7" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="L10" s="7" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>15.07</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Reporting, administration, security and go-live</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>Audit trail with before and after values, searchable by users</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>NPC</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G11" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>Audit log delivered; the reworked Audit Trail screen is in development and counted as not delivered.</t>
-        </is>
-      </c>
-      <c r="J11" s="7" t="inlineStr">
-        <is>
-          <t>In development</t>
-        </is>
-      </c>
-      <c r="K11" s="7" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="L11" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>13.10</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>Taxes and BIR compliance</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>Invoices under the EOPT Act and RR 7-2024 (invoice as primary document, required fields)</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>BIR</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G12" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>Which document is the registered invoice and its printed fields are not fixed in the product; layout changes are outside OOTB.</t>
-        </is>
-      </c>
-      <c r="J12" s="7" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="K12" s="7" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L12" s="7" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>13.11</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Taxes and BIR compliance</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>Computerized accounting system registration support (books, outputs, controls)</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>BIR</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G13" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>No loose-leaf books print set or CAS output pack; registration is with the broker.</t>
-        </is>
-      </c>
-      <c r="J13" s="7" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L13" s="7" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>14.04</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Insurance Commission and Data Privacy compliance</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>IC annual statement and financial reports in the IC format</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>IC</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G14" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>No IC-format report (checklist item 60).</t>
-        </is>
-      </c>
-      <c r="J14" s="7" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="K14" s="7" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L14" s="7" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>5.07</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>Policy issuance, documents and motor (CTPL, LTO)</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>CTPL certificate of cover authentication with the IC-accredited system and LTO</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>IC</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G15" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" s="7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>No integration with the authentication provider or LTO; done in the insurer or government portal.</t>
-        </is>
-      </c>
-      <c r="J15" s="7" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="K15" s="7" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="L15" s="7" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>4.07</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>RFQ, placement, co-insurance and reinsurance</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>Cover note or binder while the policy is pending</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>Ops</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G16" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>No cover note document or temporary cover record.</t>
-        </is>
-      </c>
-      <c r="J16" s="7" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="K16" s="7" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="L16" s="7" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>6.05</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>Endorsements and cancellations</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>Short-period rate scale when the insured cancels</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>Ops</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G17" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>No short-period table or computation.</t>
-        </is>
-      </c>
-      <c r="J17" s="7" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="K17" s="7" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="L17" s="7" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>8.12</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>Billing, collection, credit control and receipts</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>Post-dated cheque register and deposit on due date</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>Ops</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>Post-dated cheques received from clients are not tracked until deposit.</t>
-        </is>
-      </c>
-      <c r="J18" s="7" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="K18" s="7" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="L18" s="7" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>2.04</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>Prospecting and sales pipeline</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>Sales activities: calls, meetings, follow-up tasks and reminders</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>Ops</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G19" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>Account executives cannot log activities or schedule follow-ups on a prospect.</t>
-        </is>
-      </c>
-      <c r="J19" s="7" t="inlineStr">
-        <is>
-          <t>In development</t>
-        </is>
-      </c>
-      <c r="K19" s="7" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L19" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>9.05</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>Remittance, direct bill and insurer reconciliation</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>Bank payment file (InstaPay, PESONet, bulk credit) for insurers and referrers</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>Ops</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>No bank upload file; payments keyed in the bank portal.</t>
-        </is>
-      </c>
-      <c r="J20" s="7" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="K20" s="7" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L20" s="7" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>1.02</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>Client onboarding, KYC and AML</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>Corporate client with TIN, registered name and authorised signatories</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>AMLC</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G21" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>No structured authorised persons or board resolution record for juridical clients.</t>
-        </is>
-      </c>
-      <c r="J21" s="7" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="K21" s="7" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="L21" s="7" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>13.08</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>Taxes and BIR compliance</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>Annual information return and alphalist (1604-E)</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>BIR</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G22" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>No 1604-E alphalist layout.</t>
-        </is>
-      </c>
-      <c r="J22" s="7" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="K22" s="7" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="L22" s="7" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>13.13</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>Taxes and BIR compliance</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>BIR validation files (DAT) for alphalists and SLSP</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>BIR</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G23" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>Files are re-keyed or imported into the BIR tools; no DAT file.</t>
-        </is>
-      </c>
-      <c r="J23" s="7" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="K23" s="7" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="L23" s="7" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>14.03</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>Insurance Commission and Data Privacy compliance</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>Fit and proper records of directors and officers</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>IC</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>Kept outside the system.</t>
-        </is>
-      </c>
-      <c r="J24" s="7" t="inlineStr">
-        <is>
-          <t>Procedure</t>
-        </is>
-      </c>
-      <c r="K24" s="7" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="L24" s="7" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>14.05</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>Insurance Commission and Data Privacy compliance</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>IC production and business reports (premium placed by insurer and line)</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>IC</t>
-        </is>
-      </c>
-      <c r="F25" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G25" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="I25" s="6" t="inlineStr">
-        <is>
-          <t>Figures available; IC layout not produced.</t>
-        </is>
-      </c>
-      <c r="J25" s="7" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="K25" s="7" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="L25" s="7" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>14.11</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>Insurance Commission and Data Privacy compliance</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>Breach detection support and breach register</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>NPC</t>
-        </is>
-      </c>
-      <c r="F26" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G26" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>No breach register or 72-hour notification tracker.</t>
-        </is>
-      </c>
-      <c r="J26" s="7" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="K26" s="7" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="L26" s="7" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>4.08</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>RFQ, placement, co-insurance and reinsurance</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>Placement only with insurers authorised by the IC</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>IC</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G27" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="I27" s="6" t="inlineStr">
-        <is>
-          <t>No certificate of authority number or expiry check; IC non-life insurer list is in development.</t>
-        </is>
-      </c>
-      <c r="J27" s="7" t="inlineStr">
-        <is>
-          <t>In development</t>
-        </is>
-      </c>
-      <c r="K27" s="7" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="L27" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>6.04</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>Endorsements and cancellations</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>Cancellation full, partial or pro-rata with return premium computed</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>Ops</t>
-        </is>
-      </c>
-      <c r="F28" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G28" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="I28" s="6" t="inlineStr">
-        <is>
-          <t>For regular policies the return premium of a cancellation is entered by the user, not computed from days left.</t>
-        </is>
-      </c>
-      <c r="J28" s="7" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="K28" s="7" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="L28" s="7" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>1.01</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>Client onboarding, KYC and AML</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>Individual client record with Philippine address, mobile and TIN</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>Ops</t>
-        </is>
-      </c>
-      <c r="F29" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G29" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="I29" s="6" t="inlineStr">
-        <is>
-          <t>Client is created at first policy issue. Location masters are labelled State and hold Metro Manila and selected areas, not the full PSGC list (in development).</t>
-        </is>
-      </c>
-      <c r="J29" s="7" t="inlineStr">
-        <is>
-          <t>In development</t>
-        </is>
-      </c>
-      <c r="K29" s="7" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L29" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>13.12</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>Taxes and BIR compliance</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>Electronic invoicing and sales data transmission to BIR (EIS)</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>BIR</t>
-        </is>
-      </c>
-      <c r="F30" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="I30" s="6" t="inlineStr">
-        <is>
-          <t>No EIS connector (not yet mandatory for most brokers; to verify).</t>
-        </is>
-      </c>
-      <c r="J30" s="7" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="K30" s="7" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="L30" s="7" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>11.03</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>Claims assistance</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>Claim document checklist per line and missing document follow-up</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>Ops</t>
-        </is>
-      </c>
-      <c r="F31" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G31" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I31" s="6" t="inlineStr">
-        <is>
-          <t>No required-document checklist or reminder to the claimant.</t>
-        </is>
-      </c>
-      <c r="J31" s="7" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="K31" s="7" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="L31" s="7" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>11.06</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>Claims assistance</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>Claims paid through the broker: funds received and paid to claimant</t>
-        </is>
-      </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>Ops</t>
-        </is>
-      </c>
-      <c r="F32" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G32" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H32" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I32" s="6" t="inlineStr">
-        <is>
-          <t>Panel is on the claim screens; Accounting menu not extended, so the System Administrator records it (known limitation).</t>
-        </is>
-      </c>
-      <c r="J32" s="7" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="K32" s="7" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="L32" s="7" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>Prospecting and sales pipeline</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>Lead assignment to account executives and team visibility</t>
-        </is>
-      </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>Ops</t>
-        </is>
-      </c>
-      <c r="F33" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G33" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H33" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I33" s="6" t="inlineStr">
-        <is>
-          <t>Owner scoping exists; no assignment rules, reassignment queue or team view.</t>
-        </is>
-      </c>
-      <c r="J33" s="7" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="K33" s="7" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="L33" s="7" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>3.03</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>Quotation and insurer comparison</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>Client-facing comparison and recommendation report</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>Ops</t>
-        </is>
-      </c>
-      <c r="F34" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G34" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H34" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I34" s="6" t="inlineStr">
-        <is>
-          <t>Printable comparison report for the client is in development.</t>
-        </is>
-      </c>
-      <c r="J34" s="7" t="inlineStr">
-        <is>
-          <t>In development</t>
-        </is>
-      </c>
-      <c r="K34" s="7" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="L34" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>7.07</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>Renewals and retention</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>Renewal notices by SMS or messaging app</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>Ops</t>
-        </is>
-      </c>
-      <c r="F35" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I35" s="6" t="inlineStr">
-        <is>
-          <t>No SMS or Viber gateway.</t>
-        </is>
-      </c>
-      <c r="J35" s="7" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="K35" s="7" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="L35" s="7" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>8.09</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>Billing, collection, credit control and receipts</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>Instalment billing with separate instalment invoices</t>
-        </is>
-      </c>
-      <c r="E36" s="7" t="inlineStr">
-        <is>
-          <t>Ops</t>
-        </is>
-      </c>
-      <c r="F36" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G36" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H36" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I36" s="6" t="inlineStr">
-        <is>
-          <t>Plans split the follow-up of a bill without changing the ledger; no invoice per instalment.</t>
-        </is>
-      </c>
-      <c r="J36" s="7" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="K36" s="7" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="L36" s="7" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>11.08</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>Claims assistance</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>Motor claims: repair shop, estimate and letter of authority</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>Ops</t>
-        </is>
-      </c>
-      <c r="F37" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G37" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H37" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I37" s="6" t="inlineStr">
-        <is>
-          <t>No estimate approval or letter of authority workflow.</t>
-        </is>
-      </c>
-      <c r="J37" s="7" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="K37" s="7" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L37" s="7" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>12.10</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>Accounting, general ledger, period end and audit</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>Supplier invoices, input VAT, fixed assets and depreciation</t>
-        </is>
-      </c>
-      <c r="E38" s="7" t="inlineStr">
-        <is>
-          <t>Ops</t>
-        </is>
-      </c>
-      <c r="F38" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G38" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I38" s="6" t="inlineStr">
-        <is>
-          <t>No supplier invoice register (accounts payable sub-ledger) or fixed asset register.</t>
-        </is>
-      </c>
-      <c r="J38" s="7" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="K38" s="7" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L38" s="7" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>15.09</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>Reporting, administration, security and go-live</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>My Work: one inbox of tasks and approvals per user</t>
-        </is>
-      </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>Ops</t>
-        </is>
-      </c>
-      <c r="F39" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G39" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H39" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I39" s="6" t="inlineStr">
-        <is>
-          <t>My Work inbox in development.</t>
-        </is>
-      </c>
-      <c r="J39" s="7" t="inlineStr">
-        <is>
-          <t>In development</t>
-        </is>
-      </c>
-      <c r="K39" s="7" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L39" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="7" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>15.12</t>
-        </is>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>Reporting, administration, security and go-live</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>Philippine reference masters (PSGC geography, banks, IDs, salutations, IC insurer list)</t>
-        </is>
-      </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>Ops</t>
-        </is>
-      </c>
-      <c r="F40" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G40" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H40" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I40" s="6" t="inlineStr">
-        <is>
-          <t>Full Philippine masters are in development.</t>
-        </is>
-      </c>
-      <c r="J40" s="7" t="inlineStr">
-        <is>
-          <t>In development</t>
-        </is>
-      </c>
-      <c r="K40" s="7" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L40" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>2.07</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>Prospecting and sales pipeline</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>Dealer, bank and affinity channel referrals (captive agency, motor dealer branches)</t>
-        </is>
-      </c>
-      <c r="E41" s="7" t="inlineStr">
-        <is>
-          <t>Ops</t>
-        </is>
-      </c>
-      <c r="F41" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G41" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H41" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I41" s="6" t="inlineStr">
-        <is>
-          <t>No dealer or dealer-branch master, channel hierarchy or dealer production report.</t>
-        </is>
-      </c>
-      <c r="J41" s="7" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="K41" s="7" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L41" s="7" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="7" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>3.11</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>Quotation and insurer comparison</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>Product rules from the Product Configurator drive the quotation</t>
-        </is>
-      </c>
-      <c r="E42" s="7" t="inlineStr">
-        <is>
-          <t>Ops</t>
-        </is>
-      </c>
-      <c r="F42" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G42" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H42" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I42" s="6" t="inlineStr">
-        <is>
-          <t>Only the motor tariff feeds quotations; coverage, acceptance and document rules are not yet connected (in development).</t>
-        </is>
-      </c>
-      <c r="J42" s="7" t="inlineStr">
-        <is>
-          <t>In development</t>
-        </is>
-      </c>
-      <c r="K42" s="7" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L42" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="7" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>5.08</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>Policy issuance, documents and motor (CTPL, LTO)</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>Brand-new vehicle programme: dealer sale, financing bank mortgagee clause, free first-year cover</t>
-        </is>
-      </c>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>Ops</t>
-        </is>
-      </c>
-      <c r="F43" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G43" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H43" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I43" s="6" t="inlineStr">
-        <is>
-          <t>No dealer or financing-bank programme set-up, bulk dealer upload or bank endorsement letters.</t>
-        </is>
-      </c>
-      <c r="J43" s="7" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="K43" s="7" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L43" s="7" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="7" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>5.09</t>
-        </is>
-      </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>Policy issuance, documents and motor (CTPL, LTO)</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>Bulk issuance: fleet schedules and group policies</t>
-        </is>
-      </c>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
-          <t>Ops</t>
-        </is>
-      </c>
-      <c r="F44" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G44" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I44" s="6" t="inlineStr">
-        <is>
-          <t>No fleet schedule with per-vehicle premium inside one policy.</t>
-        </is>
-      </c>
-      <c r="J44" s="7" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="K44" s="7" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L44" s="7" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="7" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" s="7" t="inlineStr">
-        <is>
-          <t>5.12</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>Policy issuance, documents and motor (CTPL, LTO)</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>Marine open cover with certificates and declarations</t>
-        </is>
-      </c>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>Ops</t>
-        </is>
-      </c>
-      <c r="F45" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G45" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I45" s="6" t="inlineStr">
-        <is>
-          <t>No open cover or declaration processing.</t>
-        </is>
-      </c>
-      <c r="J45" s="7" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="K45" s="7" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L45" s="7" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" s="7" t="inlineStr">
-        <is>
-          <t>9.09</t>
-        </is>
-      </c>
-      <c r="C46" s="6" t="inlineStr">
-        <is>
-          <t>Remittance, direct bill and insurer reconciliation</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>Insurer system integration (policy, premium, claims data by API)</t>
-        </is>
-      </c>
-      <c r="E46" s="7" t="inlineStr">
-        <is>
-          <t>Ops</t>
-        </is>
-      </c>
-      <c r="F46" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I46" s="6" t="inlineStr">
-        <is>
-          <t>No insurer API connector.</t>
-        </is>
-      </c>
-      <c r="J46" s="7" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="K46" s="7" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="L46" s="7" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="7" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>13.04</t>
-        </is>
-      </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>Taxes and BIR compliance</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>Percentage tax for a non-VAT broker or agent (2551Q)</t>
-        </is>
-      </c>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>BIR</t>
-        </is>
-      </c>
-      <c r="F47" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G47" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H47" s="7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I47" s="6" t="inlineStr">
-        <is>
-          <t>No percentage tax working paper.</t>
-        </is>
-      </c>
-      <c r="J47" s="7" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="K47" s="7" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="L47" s="7" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="7" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>14.13</t>
-        </is>
-      </c>
-      <c r="C48" s="6" t="inlineStr">
-        <is>
-          <t>Insurance Commission and Data Privacy compliance</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>Encryption of personal identifiers</t>
-        </is>
-      </c>
-      <c r="E48" s="7" t="inlineStr">
-        <is>
-          <t>NPC</t>
-        </is>
-      </c>
-      <c r="F48" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G48" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H48" s="7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I48" s="6" t="inlineStr">
-        <is>
-          <t>No field-level encryption of IDs and TIN.</t>
-        </is>
-      </c>
-      <c r="J48" s="7" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="K48" s="7" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L48" s="7" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="7" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>10.10</t>
-        </is>
-      </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>Commission, referrers and incentives</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>Overriding, profit and contingent commission from insurers</t>
-        </is>
-      </c>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t>Ops</t>
-        </is>
-      </c>
-      <c r="F49" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G49" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H49" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I49" s="6" t="inlineStr">
-        <is>
-          <t>No computation; booked by journal voucher.</t>
-        </is>
-      </c>
-      <c r="J49" s="7" t="inlineStr">
-        <is>
-          <t>Procedure</t>
-        </is>
-      </c>
-      <c r="K49" s="7" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="L49" s="7" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="7" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>15.08</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>Reporting, administration, security and go-live</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>Menu organised by role and task</t>
-        </is>
-      </c>
-      <c r="E50" s="7" t="inlineStr">
-        <is>
-          <t>Ops</t>
-        </is>
-      </c>
-      <c r="F50" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G50" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H50" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I50" s="6" t="inlineStr">
-        <is>
-          <t>Menu redesign in development.</t>
-        </is>
-      </c>
-      <c r="J50" s="7" t="inlineStr">
-        <is>
-          <t>In development</t>
-        </is>
-      </c>
-      <c r="K50" s="7" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="L50" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>15.11</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>Reporting, administration, security and go-live</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>Branding, letterhead and e-signature on documents</t>
-        </is>
-      </c>
-      <c r="E51" s="7" t="inlineStr">
-        <is>
-          <t>Ops</t>
-        </is>
-      </c>
-      <c r="F51" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G51" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H51" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I51" s="6" t="inlineStr">
-        <is>
-          <t>Branding and e-signature in development.</t>
-        </is>
-      </c>
-      <c r="J51" s="7" t="inlineStr">
-        <is>
-          <t>In development</t>
-        </is>
-      </c>
-      <c r="K51" s="7" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="L51" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="7" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" s="7" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>Quotation and insurer comparison</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>Electronic signature of proposal and acceptance</t>
-        </is>
-      </c>
-      <c r="E52" s="7" t="inlineStr">
-        <is>
-          <t>Ops</t>
-        </is>
-      </c>
-      <c r="F52" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G52" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H52" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I52" s="6" t="inlineStr">
-        <is>
-          <t>E-signature on documents is in development.</t>
-        </is>
-      </c>
-      <c r="J52" s="7" t="inlineStr">
-        <is>
-          <t>In development</t>
-        </is>
-      </c>
-      <c r="K52" s="7" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="L52" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="7" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>15.03</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>Reporting, administration, security and go-live</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>Ad hoc reporting and BI extract</t>
-        </is>
-      </c>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>Ops</t>
-        </is>
-      </c>
-      <c r="F53" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G53" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H53" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I53" s="6" t="inlineStr">
-        <is>
-          <t>No report designer or data warehouse extract.</t>
-        </is>
-      </c>
-      <c r="J53" s="7" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="K53" s="7" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L53" s="7" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="7" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>2.08</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>Prospecting and sales pipeline</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>Marketing campaigns to consenting clients</t>
-        </is>
-      </c>
-      <c r="E54" s="7" t="inlineStr">
-        <is>
-          <t>Ops</t>
-        </is>
-      </c>
-      <c r="F54" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H54" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I54" s="6" t="inlineStr">
-        <is>
-          <t>No general campaign or mass mailing module.</t>
-        </is>
-      </c>
-      <c r="J54" s="7" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="K54" s="7" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L54" s="7" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="7" t="n">
-        <v>54</v>
-      </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>RFQ, placement, co-insurance and reinsurance</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>Facultative reinsurance placement (where the broker acts as reinsurance broker)</t>
-        </is>
-      </c>
-      <c r="E55" s="7" t="inlineStr">
-        <is>
-          <t>Ops</t>
-        </is>
-      </c>
-      <c r="F55" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G55" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H55" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I55" s="6" t="inlineStr">
-        <is>
-          <t>The module records treaties and cessions from the cedant side; there is no facultative reinsurance slip workflow.</t>
-        </is>
-      </c>
-      <c r="J55" s="7" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="K55" s="7" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="L55" s="7" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="15" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Impact = weight x (2 - score), x 1.5 for a regulatory item. Effort: S up to 2 weeks, M 2 to 6 weeks, L over 6 weeks of one team, design to test. Ties ranked by smaller effort.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L55"/>
+  <autoFilter ref="A1:L3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12616,33 +9774,33 @@
         </is>
       </c>
       <c r="M2" s="7" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="N2" s="7" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="O2" s="7" t="n">
-        <v>15.2</v>
+        <v>12.8</v>
       </c>
       <c r="P2" s="7" t="n">
         <v>0</v>
       </c>
       <c r="Q2" s="7" t="inlineStr">
         <is>
-          <t>20 to 28%</t>
+          <t>17 to 25%</t>
         </is>
       </c>
       <c r="R2" s="7" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>60 to 84</t>
+          <t>51 to 75</t>
         </is>
       </c>
       <c r="T2" s="7" t="inlineStr">
         <is>
-          <t>12 to 17</t>
+          <t>10 to 15</t>
         </is>
       </c>
       <c r="U2" s="6" t="inlineStr">
@@ -12711,33 +9869,33 @@
         </is>
       </c>
       <c r="M3" s="7" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="N3" s="7" t="n">
-        <v>12.2</v>
+        <v>11.6</v>
       </c>
       <c r="O3" s="7" t="n">
-        <v>6.8</v>
+        <v>5.2</v>
       </c>
       <c r="P3" s="7" t="n">
         <v>2</v>
       </c>
       <c r="Q3" s="7" t="inlineStr">
         <is>
-          <t>19 to 29%</t>
+          <t>16 to 26%</t>
         </is>
       </c>
       <c r="R3" s="7" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
-          <t>57 to 87</t>
+          <t>48 to 78</t>
         </is>
       </c>
       <c r="T3" s="7" t="inlineStr">
         <is>
-          <t>11 to 17</t>
+          <t>10 to 16</t>
         </is>
       </c>
       <c r="U3" s="6" t="inlineStr">
@@ -12806,33 +9964,33 @@
         </is>
       </c>
       <c r="M4" s="7" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="N4" s="7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="O4" s="7" t="n">
-        <v>17.7</v>
+        <v>14.8</v>
       </c>
       <c r="P4" s="7" t="n">
         <v>3</v>
       </c>
       <c r="Q4" s="7" t="inlineStr">
         <is>
-          <t>28 to 38%</t>
+          <t>24 to 34%</t>
         </is>
       </c>
       <c r="R4" s="7" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>84 to 114</t>
+          <t>72 to 102</t>
         </is>
       </c>
       <c r="T4" s="7" t="inlineStr">
         <is>
-          <t>17 to 23</t>
+          <t>14 to 20</t>
         </is>
       </c>
       <c r="U4" s="6" t="inlineStr">
@@ -12901,33 +10059,33 @@
         </is>
       </c>
       <c r="M5" s="7" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="N5" s="7" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="O5" s="7" t="n">
-        <v>20.5</v>
+        <v>17.6</v>
       </c>
       <c r="P5" s="7" t="n">
         <v>7</v>
       </c>
       <c r="Q5" s="7" t="inlineStr">
         <is>
-          <t>33 to 43%</t>
+          <t>30 to 40%</t>
         </is>
       </c>
       <c r="R5" s="7" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>99 to 129</t>
+          <t>90 to 120</t>
         </is>
       </c>
       <c r="T5" s="7" t="inlineStr">
         <is>
-          <t>20 to 26</t>
+          <t>18 to 24</t>
         </is>
       </c>
       <c r="U5" s="6" t="inlineStr">
@@ -12999,30 +10157,30 @@
         <v>2.7</v>
       </c>
       <c r="N6" s="7" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="O6" s="7" t="n">
-        <v>20.5</v>
+        <v>18</v>
       </c>
       <c r="P6" s="7" t="n">
         <v>10</v>
       </c>
       <c r="Q6" s="7" t="inlineStr">
         <is>
-          <t>36 to 50%</t>
+          <t>32 to 46%</t>
         </is>
       </c>
       <c r="R6" s="7" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>108 to 150</t>
+          <t>96 to 138</t>
         </is>
       </c>
       <c r="T6" s="7" t="inlineStr">
         <is>
-          <t>22 to 30</t>
+          <t>19 to 28</t>
         </is>
       </c>
       <c r="U6" s="6" t="inlineStr">
@@ -13094,30 +10252,30 @@
         <v>3.1</v>
       </c>
       <c r="N7" s="7" t="n">
-        <v>9.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O7" s="7" t="n">
-        <v>20.9</v>
+        <v>18.5</v>
       </c>
       <c r="P7" s="7" t="n">
         <v>10</v>
       </c>
       <c r="Q7" s="7" t="inlineStr">
         <is>
-          <t>36 to 52%</t>
+          <t>32 to 48%</t>
         </is>
       </c>
       <c r="R7" s="7" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="S7" s="7" t="inlineStr">
         <is>
-          <t>108 to 156</t>
+          <t>96 to 144</t>
         </is>
       </c>
       <c r="T7" s="7" t="inlineStr">
         <is>
-          <t>22 to 31</t>
+          <t>19 to 29</t>
         </is>
       </c>
       <c r="U7" s="6" t="inlineStr">
@@ -13189,30 +10347,30 @@
         <v>3.1</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="O8" s="7" t="n">
-        <v>25.8</v>
+        <v>22.9</v>
       </c>
       <c r="P8" s="7" t="n">
         <v>9</v>
       </c>
       <c r="Q8" s="7" t="inlineStr">
         <is>
-          <t>40 to 52%</t>
+          <t>36 to 48%</t>
         </is>
       </c>
       <c r="R8" s="7" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>120 to 156</t>
+          <t>108 to 144</t>
         </is>
       </c>
       <c r="T8" s="7" t="inlineStr">
         <is>
-          <t>24 to 31</t>
+          <t>22 to 29</t>
         </is>
       </c>
       <c r="U8" s="6" t="inlineStr">
@@ -13284,30 +10442,30 @@
         <v>3.3</v>
       </c>
       <c r="N9" s="7" t="n">
-        <v>7.9</v>
+        <v>6.7</v>
       </c>
       <c r="O9" s="7" t="n">
-        <v>28.7</v>
+        <v>25.8</v>
       </c>
       <c r="P9" s="7" t="n">
         <v>10</v>
       </c>
       <c r="Q9" s="7" t="inlineStr">
         <is>
-          <t>44 to 56%</t>
+          <t>40 to 52%</t>
         </is>
       </c>
       <c r="R9" s="7" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>132 to 168</t>
+          <t>120 to 156</t>
         </is>
       </c>
       <c r="T9" s="7" t="inlineStr">
         <is>
-          <t>26 to 34</t>
+          <t>24 to 31</t>
         </is>
       </c>
       <c r="U9" s="6" t="inlineStr">
@@ -13379,30 +10537,30 @@
         <v>3.4</v>
       </c>
       <c r="N10" s="7" t="n">
-        <v>8.699999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="O10" s="7" t="n">
-        <v>25</v>
+        <v>22.6</v>
       </c>
       <c r="P10" s="7" t="n">
         <v>12</v>
       </c>
       <c r="Q10" s="7" t="inlineStr">
         <is>
-          <t>41 to 57%</t>
+          <t>38 to 54%</t>
         </is>
       </c>
       <c r="R10" s="7" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>123 to 171</t>
+          <t>114 to 162</t>
         </is>
       </c>
       <c r="T10" s="7" t="inlineStr">
         <is>
-          <t>25 to 34</t>
+          <t>23 to 32</t>
         </is>
       </c>
       <c r="U10" s="6" t="inlineStr">
@@ -13412,28 +10570,28 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>Timor-Leste joined ASEAN in October 2025. Not scored: a very small insurance market supervised by the Banco Central de Timor-Leste, USD currency, Tetum and Portuguese. Treat as Lao PDR or higher if a prospect appears (to verify with a local partner).</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>Country facts come from general knowledge of each regime and are marked "to verify" where uncertain. Confirm with local counsel or a partner before any commitment.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>Layer % = points of change on the whole product, from the ASEAN Heat Map sheet (L1 change x L1 weight). Language is added on top. Range = midpoint +/- uncertainty band.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>Effort = 3 person-weeks per point of change (indicative), calendar weeks with a team of 5. Excludes the first client implementation.</t>
         </is>
@@ -13532,47 +10690,47 @@
       <c r="B2" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="C2" s="11" t="inlineStr">
+      <c r="C2" s="12" t="inlineStr">
         <is>
           <t>20% L</t>
         </is>
       </c>
-      <c r="D2" s="11" t="inlineStr">
+      <c r="D2" s="12" t="inlineStr">
         <is>
           <t>25% L</t>
         </is>
       </c>
-      <c r="E2" s="11" t="inlineStr">
+      <c r="E2" s="12" t="inlineStr">
         <is>
           <t>30% L</t>
         </is>
       </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>30% L</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="G2" s="12" t="inlineStr">
         <is>
           <t>30% L</t>
         </is>
       </c>
-      <c r="H2" s="11" t="inlineStr">
+      <c r="H2" s="12" t="inlineStr">
         <is>
           <t>30% L</t>
         </is>
       </c>
-      <c r="I2" s="11" t="inlineStr">
+      <c r="I2" s="12" t="inlineStr">
         <is>
           <t>35% L</t>
         </is>
       </c>
-      <c r="J2" s="11" t="inlineStr">
+      <c r="J2" s="12" t="inlineStr">
         <is>
           <t>35% L</t>
         </is>
       </c>
-      <c r="K2" s="16" t="inlineStr">
+      <c r="K2" s="15" t="inlineStr">
         <is>
           <t>40% X</t>
         </is>
@@ -13587,47 +10745,47 @@
       <c r="B3" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="11" t="inlineStr">
         <is>
           <t>5% C</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
+      <c r="D3" s="11" t="inlineStr">
         <is>
           <t>5% C</t>
         </is>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="E3" s="11" t="inlineStr">
         <is>
           <t>5% C</t>
         </is>
       </c>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="F3" s="11" t="inlineStr">
         <is>
           <t>10% L</t>
         </is>
       </c>
-      <c r="G3" s="12" t="inlineStr">
+      <c r="G3" s="11" t="inlineStr">
         <is>
           <t>10% L</t>
         </is>
       </c>
-      <c r="H3" s="12" t="inlineStr">
+      <c r="H3" s="11" t="inlineStr">
         <is>
           <t>10% L</t>
         </is>
       </c>
-      <c r="I3" s="12" t="inlineStr">
+      <c r="I3" s="11" t="inlineStr">
         <is>
           <t>10% L</t>
         </is>
       </c>
-      <c r="J3" s="12" t="inlineStr">
+      <c r="J3" s="11" t="inlineStr">
         <is>
           <t>10% L</t>
         </is>
       </c>
-      <c r="K3" s="12" t="inlineStr">
+      <c r="K3" s="11" t="inlineStr">
         <is>
           <t>10% L</t>
         </is>
@@ -13642,47 +10800,47 @@
       <c r="B4" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>30% L</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>35% L</t>
         </is>
       </c>
-      <c r="E4" s="16" t="inlineStr">
+      <c r="E4" s="15" t="inlineStr">
         <is>
           <t>40% L</t>
         </is>
       </c>
-      <c r="F4" s="16" t="inlineStr">
+      <c r="F4" s="15" t="inlineStr">
         <is>
           <t>45% X</t>
         </is>
       </c>
-      <c r="G4" s="16" t="inlineStr">
+      <c r="G4" s="15" t="inlineStr">
         <is>
           <t>45% X</t>
         </is>
       </c>
-      <c r="H4" s="16" t="inlineStr">
+      <c r="H4" s="15" t="inlineStr">
         <is>
           <t>45% X</t>
         </is>
       </c>
-      <c r="I4" s="16" t="inlineStr">
+      <c r="I4" s="15" t="inlineStr">
         <is>
           <t>50% X</t>
         </is>
       </c>
-      <c r="J4" s="16" t="inlineStr">
+      <c r="J4" s="15" t="inlineStr">
         <is>
           <t>50% X</t>
         </is>
       </c>
-      <c r="K4" s="16" t="inlineStr">
+      <c r="K4" s="15" t="inlineStr">
         <is>
           <t>50% X</t>
         </is>
@@ -13697,47 +10855,47 @@
       <c r="B5" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>5% C</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>10% C</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>10% C</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>10% C</t>
         </is>
       </c>
-      <c r="G5" s="12" t="inlineStr">
+      <c r="G5" s="11" t="inlineStr">
         <is>
           <t>10% C</t>
         </is>
       </c>
-      <c r="H5" s="12" t="inlineStr">
+      <c r="H5" s="11" t="inlineStr">
         <is>
           <t>15% C</t>
         </is>
       </c>
-      <c r="I5" s="12" t="inlineStr">
+      <c r="I5" s="11" t="inlineStr">
         <is>
           <t>15% C</t>
         </is>
       </c>
-      <c r="J5" s="12" t="inlineStr">
+      <c r="J5" s="11" t="inlineStr">
         <is>
           <t>15% C</t>
         </is>
       </c>
-      <c r="K5" s="11" t="inlineStr">
+      <c r="K5" s="12" t="inlineStr">
         <is>
           <t>20% C</t>
         </is>
@@ -13752,49 +10910,49 @@
       <c r="B6" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>30% X</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>30% X</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>35% X</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>35% X</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>40% X</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="H6" s="15" t="inlineStr">
         <is>
           <t>40% X</t>
         </is>
       </c>
-      <c r="G6" s="16" t="inlineStr">
+      <c r="I6" s="15" t="inlineStr">
+        <is>
+          <t>40% X</t>
+        </is>
+      </c>
+      <c r="J6" s="15" t="inlineStr">
         <is>
           <t>45% X</t>
         </is>
       </c>
-      <c r="H6" s="16" t="inlineStr">
+      <c r="K6" s="15" t="inlineStr">
         <is>
           <t>45% X</t>
-        </is>
-      </c>
-      <c r="I6" s="16" t="inlineStr">
-        <is>
-          <t>45% X</t>
-        </is>
-      </c>
-      <c r="J6" s="16" t="inlineStr">
-        <is>
-          <t>50% X</t>
-        </is>
-      </c>
-      <c r="K6" s="16" t="inlineStr">
-        <is>
-          <t>50% X</t>
         </is>
       </c>
     </row>
@@ -13807,47 +10965,47 @@
       <c r="B7" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>10% C</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>10% C</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="11" t="inlineStr">
         <is>
           <t>10% C</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>15% C</t>
         </is>
       </c>
-      <c r="G7" s="12" t="inlineStr">
+      <c r="G7" s="11" t="inlineStr">
         <is>
           <t>15% C</t>
         </is>
       </c>
-      <c r="H7" s="12" t="inlineStr">
+      <c r="H7" s="11" t="inlineStr">
         <is>
           <t>15% C</t>
         </is>
       </c>
-      <c r="I7" s="12" t="inlineStr">
+      <c r="I7" s="11" t="inlineStr">
         <is>
           <t>15% C</t>
         </is>
       </c>
-      <c r="J7" s="11" t="inlineStr">
+      <c r="J7" s="12" t="inlineStr">
         <is>
           <t>20% C</t>
         </is>
       </c>
-      <c r="K7" s="12" t="inlineStr">
+      <c r="K7" s="11" t="inlineStr">
         <is>
           <t>15% C</t>
         </is>
@@ -13862,47 +11020,47 @@
       <c r="B8" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>5% C</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>5% C</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>10% C</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="F8" s="11" t="inlineStr">
         <is>
           <t>10% C</t>
         </is>
       </c>
-      <c r="G8" s="12" t="inlineStr">
+      <c r="G8" s="11" t="inlineStr">
         <is>
           <t>10% C</t>
         </is>
       </c>
-      <c r="H8" s="12" t="inlineStr">
+      <c r="H8" s="11" t="inlineStr">
         <is>
           <t>10% C</t>
         </is>
       </c>
-      <c r="I8" s="12" t="inlineStr">
+      <c r="I8" s="11" t="inlineStr">
         <is>
           <t>10% C</t>
         </is>
       </c>
-      <c r="J8" s="12" t="inlineStr">
+      <c r="J8" s="11" t="inlineStr">
         <is>
           <t>10% C</t>
         </is>
       </c>
-      <c r="K8" s="12" t="inlineStr">
+      <c r="K8" s="11" t="inlineStr">
         <is>
           <t>10% C</t>
         </is>
@@ -13917,49 +11075,49 @@
       <c r="B9" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>25% X</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>15% L</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>45% X</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>20% X</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>10% L</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>35% X</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>30% X</t>
+        </is>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>35% X</t>
+        </is>
+      </c>
+      <c r="H9" s="12" t="inlineStr">
+        <is>
+          <t>35% X</t>
+        </is>
+      </c>
+      <c r="I9" s="15" t="inlineStr">
         <is>
           <t>40% X</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>45% X</t>
-        </is>
-      </c>
-      <c r="H9" s="16" t="inlineStr">
-        <is>
-          <t>45% X</t>
-        </is>
-      </c>
-      <c r="I9" s="16" t="inlineStr">
+      <c r="J9" s="15" t="inlineStr">
         <is>
           <t>50% X</t>
         </is>
       </c>
-      <c r="J9" s="13" t="inlineStr">
-        <is>
-          <t>60% X</t>
-        </is>
-      </c>
-      <c r="K9" s="16" t="inlineStr">
-        <is>
-          <t>45% X</t>
+      <c r="K9" s="12" t="inlineStr">
+        <is>
+          <t>35% X</t>
         </is>
       </c>
     </row>
@@ -13972,49 +11130,49 @@
       <c r="B10" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>10% L</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>10% L</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>15% L</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>15% L</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>15% L</t>
+        </is>
+      </c>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>15% L</t>
+        </is>
+      </c>
+      <c r="I10" s="12" t="inlineStr">
         <is>
           <t>20% L</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="J10" s="12" t="inlineStr">
         <is>
           <t>20% L</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="K10" s="12" t="inlineStr">
         <is>
           <t>20% L</t>
-        </is>
-      </c>
-      <c r="H10" s="11" t="inlineStr">
-        <is>
-          <t>20% L</t>
-        </is>
-      </c>
-      <c r="I10" s="11" t="inlineStr">
-        <is>
-          <t>25% L</t>
-        </is>
-      </c>
-      <c r="J10" s="11" t="inlineStr">
-        <is>
-          <t>25% L</t>
-        </is>
-      </c>
-      <c r="K10" s="11" t="inlineStr">
-        <is>
-          <t>25% L</t>
         </is>
       </c>
     </row>
@@ -14027,47 +11185,47 @@
       <c r="B11" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>15% L</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>15% L</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>25% L</t>
         </is>
       </c>
-      <c r="F11" s="11" t="inlineStr">
+      <c r="F11" s="12" t="inlineStr">
         <is>
           <t>30% L</t>
         </is>
       </c>
-      <c r="G11" s="11" t="inlineStr">
+      <c r="G11" s="12" t="inlineStr">
         <is>
           <t>30% L</t>
         </is>
       </c>
-      <c r="H11" s="11" t="inlineStr">
+      <c r="H11" s="12" t="inlineStr">
         <is>
           <t>30% L</t>
         </is>
       </c>
-      <c r="I11" s="11" t="inlineStr">
+      <c r="I11" s="12" t="inlineStr">
         <is>
           <t>35% X</t>
         </is>
       </c>
-      <c r="J11" s="11" t="inlineStr">
+      <c r="J11" s="12" t="inlineStr">
         <is>
           <t>35% L</t>
         </is>
       </c>
-      <c r="K11" s="11" t="inlineStr">
+      <c r="K11" s="12" t="inlineStr">
         <is>
           <t>30% L</t>
         </is>
@@ -14082,47 +11240,47 @@
       <c r="B12" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>5% C</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>5% C</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>10% C</t>
         </is>
       </c>
-      <c r="F12" s="12" t="inlineStr">
+      <c r="F12" s="11" t="inlineStr">
         <is>
           <t>10% C</t>
         </is>
       </c>
-      <c r="G12" s="12" t="inlineStr">
+      <c r="G12" s="11" t="inlineStr">
         <is>
           <t>15% C</t>
         </is>
       </c>
-      <c r="H12" s="12" t="inlineStr">
+      <c r="H12" s="11" t="inlineStr">
         <is>
           <t>15% C</t>
         </is>
       </c>
-      <c r="I12" s="12" t="inlineStr">
+      <c r="I12" s="11" t="inlineStr">
         <is>
           <t>15% C</t>
         </is>
       </c>
-      <c r="J12" s="12" t="inlineStr">
+      <c r="J12" s="11" t="inlineStr">
         <is>
           <t>15% C</t>
         </is>
       </c>
-      <c r="K12" s="12" t="inlineStr">
+      <c r="K12" s="11" t="inlineStr">
         <is>
           <t>15% C</t>
         </is>
@@ -14137,47 +11295,47 @@
       <c r="B13" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>15% L</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>15% L</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E13" s="12" t="inlineStr">
         <is>
           <t>20% L</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr">
+      <c r="F13" s="12" t="inlineStr">
         <is>
           <t>25% L</t>
         </is>
       </c>
-      <c r="G13" s="11" t="inlineStr">
+      <c r="G13" s="12" t="inlineStr">
         <is>
           <t>35% L</t>
         </is>
       </c>
-      <c r="H13" s="16" t="inlineStr">
+      <c r="H13" s="15" t="inlineStr">
         <is>
           <t>40% L</t>
         </is>
       </c>
-      <c r="I13" s="11" t="inlineStr">
+      <c r="I13" s="12" t="inlineStr">
         <is>
           <t>30% L</t>
         </is>
       </c>
-      <c r="J13" s="16" t="inlineStr">
+      <c r="J13" s="15" t="inlineStr">
         <is>
           <t>50% X</t>
         </is>
       </c>
-      <c r="K13" s="16" t="inlineStr">
+      <c r="K13" s="15" t="inlineStr">
         <is>
           <t>40% L</t>
         </is>
@@ -14192,47 +11350,47 @@
       <c r="B14" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>65% X</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>45% L</t>
+        </is>
+      </c>
+      <c r="E14" s="16" t="inlineStr">
+        <is>
+          <t>65% X</t>
+        </is>
+      </c>
+      <c r="F14" s="16" t="inlineStr">
+        <is>
+          <t>65% X</t>
+        </is>
+      </c>
+      <c r="G14" s="16" t="inlineStr">
+        <is>
+          <t>65% X</t>
+        </is>
+      </c>
+      <c r="H14" s="16" t="inlineStr">
         <is>
           <t>70% X</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>45% L</t>
-        </is>
-      </c>
-      <c r="E14" s="13" t="inlineStr">
-        <is>
-          <t>70% X</t>
-        </is>
-      </c>
-      <c r="F14" s="13" t="inlineStr">
-        <is>
-          <t>70% X</t>
-        </is>
-      </c>
-      <c r="G14" s="13" t="inlineStr">
-        <is>
-          <t>70% X</t>
-        </is>
-      </c>
-      <c r="H14" s="13" t="inlineStr">
-        <is>
-          <t>70% X</t>
-        </is>
-      </c>
-      <c r="I14" s="13" t="inlineStr">
-        <is>
-          <t>80% X</t>
-        </is>
-      </c>
-      <c r="J14" s="13" t="inlineStr">
-        <is>
-          <t>80% X</t>
-        </is>
-      </c>
-      <c r="K14" s="13" t="inlineStr">
+      <c r="I14" s="16" t="inlineStr">
+        <is>
+          <t>75% X</t>
+        </is>
+      </c>
+      <c r="J14" s="16" t="inlineStr">
+        <is>
+          <t>75% X</t>
+        </is>
+      </c>
+      <c r="K14" s="16" t="inlineStr">
         <is>
           <t>70% X</t>
         </is>
@@ -14247,49 +11405,49 @@
       <c r="B15" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>35% X</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>35% X</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="inlineStr">
+        <is>
+          <t>40% X</t>
+        </is>
+      </c>
+      <c r="F15" s="15" t="inlineStr">
+        <is>
+          <t>40% X</t>
+        </is>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>35% X</t>
+        </is>
+      </c>
+      <c r="H15" s="12" t="inlineStr">
+        <is>
+          <t>35% X</t>
+        </is>
+      </c>
+      <c r="I15" s="15" t="inlineStr">
         <is>
           <t>50% X</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="J15" s="15" t="inlineStr">
         <is>
           <t>50% X</t>
         </is>
       </c>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>55% X</t>
-        </is>
-      </c>
-      <c r="F15" s="16" t="inlineStr">
-        <is>
-          <t>55% X</t>
-        </is>
-      </c>
-      <c r="G15" s="16" t="inlineStr">
+      <c r="K15" s="15" t="inlineStr">
         <is>
           <t>45% X</t>
-        </is>
-      </c>
-      <c r="H15" s="16" t="inlineStr">
-        <is>
-          <t>50% X</t>
-        </is>
-      </c>
-      <c r="I15" s="13" t="inlineStr">
-        <is>
-          <t>65% X</t>
-        </is>
-      </c>
-      <c r="J15" s="13" t="inlineStr">
-        <is>
-          <t>65% X</t>
-        </is>
-      </c>
-      <c r="K15" s="13" t="inlineStr">
-        <is>
-          <t>60% X</t>
         </is>
       </c>
     </row>
@@ -14302,49 +11460,49 @@
       <c r="B16" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>5% C</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>5% C</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>5% C</t>
+        </is>
+      </c>
+      <c r="F16" s="11" t="inlineStr">
         <is>
           <t>10% C</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
-        <is>
-          <t>10% C</t>
-        </is>
-      </c>
-      <c r="E16" s="12" t="inlineStr">
-        <is>
-          <t>10% C</t>
-        </is>
-      </c>
-      <c r="F16" s="12" t="inlineStr">
-        <is>
-          <t>15% C</t>
-        </is>
-      </c>
       <c r="G16" s="11" t="inlineStr">
         <is>
-          <t>20% L</t>
+          <t>10% L</t>
         </is>
       </c>
       <c r="H16" s="11" t="inlineStr">
         <is>
-          <t>20% L</t>
+          <t>10% L</t>
         </is>
       </c>
       <c r="I16" s="11" t="inlineStr">
         <is>
-          <t>20% L</t>
+          <t>10% L</t>
         </is>
       </c>
       <c r="J16" s="11" t="inlineStr">
         <is>
-          <t>20% L</t>
+          <t>10% L</t>
         </is>
       </c>
       <c r="K16" s="11" t="inlineStr">
         <is>
-          <t>25% L</t>
+          <t>15% L</t>
         </is>
       </c>
     </row>
@@ -14389,37 +11547,37 @@
           <t>Overall change % (midpoint)</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr"/>
-      <c r="C18" s="14" t="n">
-        <v>24</v>
-      </c>
-      <c r="D18" s="14" t="n">
-        <v>24</v>
-      </c>
-      <c r="E18" s="14" t="n">
-        <v>33</v>
-      </c>
-      <c r="F18" s="14" t="n">
-        <v>38</v>
-      </c>
-      <c r="G18" s="14" t="n">
-        <v>43</v>
-      </c>
-      <c r="H18" s="14" t="n">
-        <v>44</v>
-      </c>
-      <c r="I18" s="14" t="n">
+      <c r="B18" s="13" t="inlineStr"/>
+      <c r="C18" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="D18" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="E18" s="13" t="n">
+        <v>29</v>
+      </c>
+      <c r="F18" s="13" t="n">
+        <v>35</v>
+      </c>
+      <c r="G18" s="13" t="n">
+        <v>39</v>
+      </c>
+      <c r="H18" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="I18" s="13" t="n">
+        <v>42</v>
+      </c>
+      <c r="J18" s="13" t="n">
         <v>46</v>
       </c>
-      <c r="J18" s="14" t="n">
-        <v>50</v>
-      </c>
-      <c r="K18" s="14" t="n">
-        <v>49</v>
+      <c r="K18" s="13" t="n">
+        <v>46</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>Cell = share of the L1 area that changes, and the main layer: C configuration, L localisation of masters, tax rules and forms, X code (regulatory reports, e-invoicing and other integrations).</t>
         </is>
@@ -14436,7 +11594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -14475,137 +11633,173 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>Code on branch brokerverse-platform as of 04 October 2026. Work in development (menu, audit trail screen, Philippine masters: Province instead of State, PSGC geography, PH banks, IDs and salutations, IC non-life insurer list; My Work; Product Configurator connections; branding and e-signature; masking; comparison report) is counted as not delivered.</t>
+          <t>Version 1.1: code on branch brokerverse-platform as of 04 October 2026 with every release package merged (Philippine masters, enterprise menu and Help panel, My Work, Product Configurator in the flow, audit trail screen, go-live workbench, AML/CFT, IC and NPC compliance, BIR forms and EIS, operations and accounting additions, distribution, integrations framework, branding and e-signatures, sales activities, quote covers and risk fields, supplier 2307, fixed asset disposal). Nothing is counted as in development. Version 1.0 of the same date scored the pre-release code (overall 80.4%).</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Catalogue</t>
+          <t>Integrations</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>150 L2 processes in 15 L1 areas, written from Philippine broking practice: Insurance Code (RA 10607) and IC rules, NIRC and EOPT Act (RA 11976) with RR 7-2024, Data Privacy Act (RA 10173) and NPC rules, AMLA (RA 9160 as amended), Financial Consumer Protection Act (RA 11765), LTO and CTPL practice.</t>
+          <t>An integration scores 2 only when the code has a connector with a configurable provider, a test mode exercised by the tests, an outbox with retry and a manual or file fallback. The certification that remains with the partner (bank file acceptance, SMS gateway contract, CTPL provider and LTO acceptance, insurer API contract, BIR EIS enrolment, screening provider) is stated in the gap note and is an onboarding task, not a product gap.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Weight</t>
+          <t>Regulator confirmations</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>3 = core to daily operation or a legal obligation with penalties; 2 = important; 1 = useful or occasional.</t>
+          <t>A report whose official layout the regulator or the broker's adviser must confirm before the first filing is scored 1 when the system does not reproduce the official form (AMLC report file, IC annual statement working paper). Forms the BIR publishes (0619-E, 1601-EQ, 1604-E, 2551Q, DAT record layouts) are scored 2 with the validation step named in the gap note; settings the broker confirms (ATCs, deadlines, declarations, invoice registration) are noted, not deducted.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Score</t>
+          <t>Catalogue</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>2 = supported out of the box end to end and evidenced by a screen and a test or the UAT run; 1 = partly supported, needs a workaround, a procedure or configuration not yet present; 0 = not supported. Screens that do not complete the process get no credit.</t>
+          <t>150 L2 processes in 15 L1 areas, written from Philippine broking practice: Insurance Code (RA 10607) and IC rules, NIRC and EOPT Act (RA 11976) with RR 7-2024, Data Privacy Act (RA 10173) and NPC rules, AMLA (RA 9160 as amended), Financial Consumer Protection Act (RA 11765), LTO and CTPL practice.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Fit %</t>
+          <t>Weight</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Sum of weight x score divided by the sum of weight x 2, per L1 and overall. Regulatory fit uses the L2 typed IC, BIR, NPC or AMLC; operational fit uses the L2 typed Ops.</t>
+          <t>3 = core to daily operation or a legal obligation with penalties; 2 = important; 1 = useful or occasional.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Gap ranking</t>
+          <t>Score</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Impact = weight x (2 - score), times 1.5 for a regulatory item; ties ranked by smaller effort. Effort S up to 2 weeks, M 2 to 6 weeks, L over 6 weeks for one team.</t>
+          <t>2 = supported out of the box end to end and evidenced by a screen and a test or the UAT run; 1 = partly supported, needs a workaround, a procedure or configuration not yet present; 0 = not supported. Screens that do not complete the process get no credit.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>ASEAN method</t>
+          <t>Fit %</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>For each country and L1 area: share of the area that changes and its main layer (configuration, localisation, code). Weighted by the L1 weight of the Philippine catalogue. A language layer is added for UI and documents. Ranges reflect uncertainty; facts marked "to verify" are to be confirmed with local counsel or a partner.</t>
+          <t>Sum of weight x score divided by the sum of weight x 2, per L1 and overall. Regulatory fit uses the L2 typed IC, BIR, NPC or AMLC; operational fit uses the L2 typed Ops.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Accelerators found in the code</t>
+          <t>Gap ranking</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>i18n framework and language picker (brokerverse/src/i18n.js, utility/languages.js); th.json with 4,675 of 7,917 keys in Thai, withdrawn from the pickers; base currency and dated exchange rates (migration 0235); premium tax engine with rule kinds vat, premium_tax, dst, fst, lgt and other (percent, per unit, flat; lines, regimes, dates) in modules/premium-charges; posting rules and account determination; Master &gt; Configuration settings; document numbering; address API country &gt; province &gt; city &gt; district with postal code lookup; payment gateway providers; bank and insurer statement formats; Singapore hosting region.</t>
+          <t>Impact = weight x (2 - score), times 1.5 for a regulatory item; ties ranked by smaller effort. Effort S up to 2 weeks, M 2 to 6 weeks, L over 6 weeks for one team.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Inhibitors found in the code</t>
+          <t>ASEAN method</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>BIR reports and Form 2307 layout are Philippine-specific (modules/reports/periodEndQueries.js); motor quotation built around CTPL and the IC vehicle classes; KYC ID defaults; Asia/Manila business time zone in 9 backend files; PHP defaults in document templates; premium tax kinds named after Philippine taxes; LGU tax master.</t>
+          <t>For each country and L1 area: share of the area that changes and its main layer (configuration, localisation, code). Weighted by the L1 weight of the Philippine catalogue. A language layer is added for UI and documents. Ranges reflect uncertainty; facts marked "to verify" are to be confirmed with local counsel or a partner.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Sources in the repository</t>
+          <t>Accelerators found in the code</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>backend/src/modules (46 modules); backend/src/db/migrations; backend/test (79 test files); backend/scripts/uat-scenario.js and docs/e2e/UAT_SCENARIO_RUN.md (371 steps passed); docs/e2e/GOLIVE_REHEARSAL_RUN.md (51 checks passed); brokerverse/src/components/SideBar/list.js; brokerverse/src/locales; docs/package/source/ph-regulatory-compliance-matrix.md, product-functionality.md, test-summary.md, user-manual.md.</t>
+          <t>Integration framework (modules/integrations/framework: connectors with provider adapters, credentials by environment variable, test mode, outbox with retry, signed inbox) used by SMS, Viber, CTPL, LTO, insurer API and bank files; bank file layouts configured per bank (delimited or fixed width); compliance registers with configurable deadlines, declarations and line sets (licences, fit and proper, complaints, breaches, IC statement mapping); AML programme with configurable risk factors, thresholds, uploaded lists and a screening provider adapter; report builder and BI extract; Theme and Branding with brand packs; i18n framework and language picker (brokerverse/src/i18n.js, utility/languages.js) with th.json partly translated and withdrawn from the pickers; base currency and dated exchange rates (migration 0235); premium tax engine with rule kinds vat, premium_tax, dst, fst, lgt and other (percent, per unit, flat; lines, regimes, dates) in modules/premium-charges; posting rules and account determination; Master &gt; Configuration settings; document numbering; address API country &gt; region &gt; province &gt; city &gt; barangay with postal code lookup; payment gateway providers; bank and insurer statement formats; Singapore hosting region.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Limits</t>
+          <t>Inhibitors found in the code</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>This is a product assessment, not legal or tax advice. Country facts are general knowledge as of the assessment date and must be verified. Effort figures are indicative bands for planning, not quotations.</t>
+          <t>The BIR layer is larger than in 1.0 and all of it is Philippine-specific: modules/bir (0619-E, 1601-EQ, 1604-E, 2551Q, DAT files, EOPT sales invoices, EIS payload, CAS books) and the BIR reports in modules/reports/periodEndQueries.js; the AMLC report file (modules/aml/reports.js) and the IC annual statement and production report (modules/ic-compliance/icReports.js); CTPL authentication and COC series (modules/integrations/ctpl.js); motor quotation built around CTPL and the IC vehicle classes; KYC ID defaults and PSGC address structure; Asia/Manila business time zone in 8 backend files; PHP defaults in document templates; premium tax kinds named after Philippine taxes; LGU tax master.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
+          <t>Sources in the repository</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>backend/src/modules (73 modules); backend/src/db/migrations (to 0322); backend/test (103 test files); backend/scripts/uat-scenario.js and docs/e2e/UAT_SCENARIO_RUN.md (371 steps passed); docs/e2e/GOLIVE_REHEARSAL_RUN.md (51 checks passed); brokerverse/src/components/SideBar/list.js and utils/menuPermissions.js; brokerverse/src/locales; docs/package/source/user-manual.md, ph-regulatory-compliance-matrix.md, product-functionality.md, test-summary.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Versions</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>1.0, 04 October 2026: pre-release assessment (overall 80.4%, regulatory 70.7%, 12 processes in development). 1.1, 04 October 2026: re-scored on the merged release; every process re-verified against the code, the tests, the menu and the user manual; ASEAN estimates recomputed on the new baseline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Limits</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>This is a product assessment, not legal or tax advice. Country facts are general knowledge as of the assessment date and must be verified. Effort figures are indicative bands for planning, not quotations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
           <t>Rebuild</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>cd docs/package/tools &amp;&amp; python3 build_fit_assessment_xlsx.py (the catalogue and estimates are in that script).</t>
         </is>

--- a/docs/package/08_Management/BrokerVerse_PH_Fit_and_ASEAN_Rollout_Assessment.xlsx
+++ b/docs/package/08_Management/BrokerVerse_PH_Fit_and_ASEAN_Rollout_Assessment.xlsx
@@ -3621,7 +3621,7 @@
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>Operations &gt; Policy; quote-to-policy.test.js; policies.test.js; UAT scenario 371 steps passed</t>
+          <t>Operations &gt; Policy; quote-to-policy.test.js; policies.test.js; UAT scenario 433 steps passed</t>
         </is>
       </c>
       <c r="K45" s="6" t="inlineStr"/>
@@ -9285,7 +9285,7 @@
       </c>
       <c r="J165" s="6" t="inlineStr">
         <is>
-          <t>Master &gt; Go-Live Data Load (configuration and migration workbooks, validate, errors workbook, load, reconciliation); go-live.test.js; go-live-workbench.test.js; go-live-roundtrip.test.js; docs/e2e/GOLIVE_REHEARSAL_RUN.md (51 checks passed)</t>
+          <t>Master &gt; Go-Live Data Load (configuration and migration workbooks, validate, errors workbook, load, reconciliation); go-live.test.js; go-live-workbench.test.js; go-live-roundtrip.test.js; docs/e2e/GOLIVE_REHEARSAL_RUN.md (52 checks passed)</t>
         </is>
       </c>
       <c r="K165" s="6" t="inlineStr"/>
@@ -11765,7 +11765,7 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>backend/src/modules (73 modules); backend/src/db/migrations (to 0322); backend/test (103 test files); backend/scripts/uat-scenario.js and docs/e2e/UAT_SCENARIO_RUN.md (371 steps passed); docs/e2e/GOLIVE_REHEARSAL_RUN.md (51 checks passed); brokerverse/src/components/SideBar/list.js and utils/menuPermissions.js; brokerverse/src/locales; docs/package/source/user-manual.md, ph-regulatory-compliance-matrix.md, product-functionality.md, test-summary.md.</t>
+          <t>backend/src/modules (73 modules); backend/src/db/migrations (to 0331); backend/test (104 test files); backend/scripts/uat-scenario.js and docs/e2e/UAT_SCENARIO_RUN.md (433 steps passed); docs/e2e/GOLIVE_REHEARSAL_RUN.md (52 checks passed); brokerverse/src/components/SideBar/list.js and utils/menuPermissions.js; brokerverse/src/locales; docs/package/source/user-manual.md, ph-regulatory-compliance-matrix.md, product-functionality.md, test-summary.md.</t>
         </is>
       </c>
     </row>
